--- a/Santa Cruz V2/listas/listas_2027.xlsx
+++ b/Santa Cruz V2/listas/listas_2027.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8897" uniqueCount="1289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8896" uniqueCount="1288">
   <si>
     <t>posicao</t>
   </si>
@@ -2353,9 +2353,6 @@
     <t>B. Rodríguez</t>
   </si>
   <si>
-    <t>M. Moreno</t>
-  </si>
-  <si>
     <t>Reinaldo</t>
   </si>
   <si>
@@ -2380,6 +2377,9 @@
     <t>Anderson Oliveira</t>
   </si>
   <si>
+    <t>L. Mina</t>
+  </si>
+  <si>
     <t>Nicolás Souza</t>
   </si>
   <si>
@@ -2681,9 +2681,6 @@
   </si>
   <si>
     <t>Houston Dynamo</t>
-  </si>
-  <si>
-    <t>Paredes</t>
   </si>
   <si>
     <t>Chaves</t>
@@ -35431,7 +35428,7 @@
         <v>3085</v>
       </c>
       <c r="H3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I3">
         <v>200000</v>
@@ -35502,7 +35499,7 @@
         <v>1198</v>
       </c>
       <c r="H4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I4">
         <v>300000</v>
@@ -35653,7 +35650,7 @@
         <v>263</v>
       </c>
       <c r="K6" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="L6">
         <v>72</v>
@@ -36005,10 +36002,10 @@
         <v>300000</v>
       </c>
       <c r="J11" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="K11" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="L11">
         <v>61.2</v>
@@ -36218,7 +36215,7 @@
         <v>267</v>
       </c>
       <c r="K14" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="L14">
         <v>80.2</v>
@@ -36360,10 +36357,10 @@
         <v>2000000</v>
       </c>
       <c r="J16" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="K16" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="L16">
         <v>66.90000000000001</v>
@@ -36461,7 +36458,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="W17" t="b">
         <v>1</v>
@@ -37005,7 +37002,7 @@
         <v>1413</v>
       </c>
       <c r="H25" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I25">
         <v>1000000</v>
@@ -37221,7 +37218,7 @@
         <v>2368</v>
       </c>
       <c r="H28" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I28">
         <v>100000</v>
@@ -37230,7 +37227,7 @@
         <v>267</v>
       </c>
       <c r="K28" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="L28">
         <v>77</v>
@@ -37366,7 +37363,7 @@
         <v>1554</v>
       </c>
       <c r="H30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I30">
         <v>1000000</v>
@@ -37730,7 +37727,7 @@
         <v>1794</v>
       </c>
       <c r="H35" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I35">
         <v>400000</v>
@@ -37958,7 +37955,7 @@
         <v>261</v>
       </c>
       <c r="K38" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="L38">
         <v>80.7</v>
@@ -38094,7 +38091,7 @@
         <v>2172</v>
       </c>
       <c r="H40" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -38316,10 +38313,10 @@
         <v>500000</v>
       </c>
       <c r="J43" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="K43" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="L43">
         <v>76.09999999999999</v>
@@ -38393,7 +38390,7 @@
         <v>265</v>
       </c>
       <c r="K44" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="L44">
         <v>60</v>
@@ -38961,10 +38958,10 @@
         <v>2000000</v>
       </c>
       <c r="J52" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K52" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="L52">
         <v>73.3</v>
@@ -39029,7 +39026,7 @@
         <v>2529</v>
       </c>
       <c r="H53" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I53">
         <v>300000</v>
@@ -39251,7 +39248,7 @@
         <v>261</v>
       </c>
       <c r="K56" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="L56">
         <v>71.7</v>
@@ -39325,7 +39322,7 @@
         <v>261</v>
       </c>
       <c r="K57" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="L57">
         <v>75</v>
@@ -39467,7 +39464,7 @@
         <v>268</v>
       </c>
       <c r="K59" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="L59">
         <v>75.2</v>
@@ -39680,7 +39677,7 @@
         <v>1859</v>
       </c>
       <c r="H62" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -39890,7 +39887,7 @@
         <v>1476</v>
       </c>
       <c r="H65" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I65">
         <v>2000000</v>
@@ -40112,7 +40109,7 @@
         <v>3292</v>
       </c>
       <c r="H68" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -40260,10 +40257,10 @@
         <v>0</v>
       </c>
       <c r="J70" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="K70" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="L70">
         <v>44.6</v>
@@ -40627,7 +40624,7 @@
         <v>267</v>
       </c>
       <c r="K75" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="L75">
         <v>96.40000000000001</v>
@@ -40692,7 +40689,7 @@
         <v>1437</v>
       </c>
       <c r="H76" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -40973,7 +40970,7 @@
         <v>2071</v>
       </c>
       <c r="H80" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I80">
         <v>1800000</v>
@@ -40982,7 +40979,7 @@
         <v>263</v>
       </c>
       <c r="K80" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="L80">
         <v>84.2</v>
@@ -41118,7 +41115,7 @@
         <v>1544</v>
       </c>
       <c r="H82" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -41269,10 +41266,10 @@
         <v>250000</v>
       </c>
       <c r="J84" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K84" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="L84">
         <v>73.3</v>
@@ -41553,7 +41550,7 @@
         <v>1349</v>
       </c>
       <c r="H88" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -42713,7 +42710,7 @@
         <v>261</v>
       </c>
       <c r="K104" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="L104">
         <v>78.8</v>
@@ -42849,7 +42846,7 @@
         <v>1557</v>
       </c>
       <c r="H106" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -43145,7 +43142,7 @@
         <v>261</v>
       </c>
       <c r="K110" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="L110">
         <v>90.59999999999999</v>
@@ -43340,7 +43337,7 @@
         <v>641</v>
       </c>
       <c r="B113" t="s">
-        <v>665</v>
+        <v>643</v>
       </c>
       <c r="C113" t="s">
         <v>12</v>
@@ -43352,40 +43349,43 @@
         <v>887</v>
       </c>
       <c r="F113">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G113">
-        <v>1639</v>
+        <v>2672</v>
       </c>
       <c r="H113" t="s">
-        <v>259</v>
+        <v>901</v>
       </c>
       <c r="I113">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="J113" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="K113" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="L113">
-        <v>81.5</v>
+        <v>85.2</v>
       </c>
       <c r="M113">
-        <v>66.5</v>
+        <v>70.2</v>
       </c>
       <c r="N113">
-        <v>61.8</v>
+        <v>54</v>
       </c>
       <c r="O113">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P113">
-        <v>64.2</v>
+        <v>62.1</v>
       </c>
       <c r="Q113">
         <v>0</v>
+      </c>
+      <c r="R113">
+        <v>64.90000000000001</v>
       </c>
       <c r="S113">
         <v>6</v>
@@ -43394,7 +43394,7 @@
         <v>1</v>
       </c>
       <c r="U113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V113" t="s">
         <v>276</v>
@@ -43403,7 +43403,7 @@
         <v>1</v>
       </c>
       <c r="X113" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="114" spans="1:24">
@@ -43411,7 +43411,7 @@
         <v>641</v>
       </c>
       <c r="B114" t="s">
-        <v>643</v>
+        <v>656</v>
       </c>
       <c r="C114" t="s">
         <v>12</v>
@@ -43423,16 +43423,16 @@
         <v>888</v>
       </c>
       <c r="F114">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G114">
-        <v>2672</v>
+        <v>1248</v>
       </c>
       <c r="H114" t="s">
-        <v>902</v>
+        <v>252</v>
       </c>
       <c r="I114">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="J114" t="s">
         <v>261</v>
@@ -43441,25 +43441,25 @@
         <v>261</v>
       </c>
       <c r="L114">
-        <v>85.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="M114">
-        <v>70.2</v>
+        <v>57.9</v>
       </c>
       <c r="N114">
-        <v>54</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="O114">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P114">
-        <v>62.1</v>
+        <v>61.8</v>
       </c>
       <c r="Q114">
         <v>0</v>
       </c>
       <c r="R114">
-        <v>64.90000000000001</v>
+        <v>53.6</v>
       </c>
       <c r="S114">
         <v>6</v>
@@ -43474,10 +43474,10 @@
         <v>276</v>
       </c>
       <c r="W114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X114" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="115" spans="1:24">
@@ -43485,7 +43485,7 @@
         <v>641</v>
       </c>
       <c r="B115" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="C115" t="s">
         <v>12</v>
@@ -43497,43 +43497,43 @@
         <v>889</v>
       </c>
       <c r="F115">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G115">
-        <v>1248</v>
+        <v>1214</v>
       </c>
       <c r="H115" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I115">
         <v>0</v>
       </c>
       <c r="J115" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="K115" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L115">
-        <v>72.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="M115">
-        <v>57.9</v>
+        <v>56.9</v>
       </c>
       <c r="N115">
-        <v>65.59999999999999</v>
+        <v>59.2</v>
       </c>
       <c r="O115">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P115">
-        <v>61.8</v>
+        <v>58</v>
       </c>
       <c r="Q115">
         <v>0</v>
       </c>
       <c r="R115">
-        <v>53.6</v>
+        <v>48.6</v>
       </c>
       <c r="S115">
         <v>6</v>
@@ -43542,7 +43542,7 @@
         <v>1</v>
       </c>
       <c r="U115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V115" t="s">
         <v>276</v>
@@ -43559,7 +43559,7 @@
         <v>641</v>
       </c>
       <c r="B116" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="C116" t="s">
         <v>12</v>
@@ -43571,43 +43571,43 @@
         <v>890</v>
       </c>
       <c r="F116">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G116">
-        <v>1214</v>
+        <v>2120</v>
       </c>
       <c r="H116" t="s">
-        <v>247</v>
+        <v>390</v>
       </c>
       <c r="I116">
-        <v>0</v>
+        <v>450000</v>
       </c>
       <c r="J116" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="K116" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L116">
-        <v>71.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="M116">
-        <v>56.9</v>
+        <v>67.2</v>
       </c>
       <c r="N116">
-        <v>59.2</v>
+        <v>44</v>
       </c>
       <c r="O116">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="P116">
-        <v>58</v>
+        <v>55.6</v>
       </c>
       <c r="Q116">
         <v>0</v>
       </c>
       <c r="R116">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="S116">
         <v>6</v>
@@ -43625,7 +43625,7 @@
         <v>0</v>
       </c>
       <c r="X116" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="117" spans="1:24">
@@ -43633,7 +43633,7 @@
         <v>641</v>
       </c>
       <c r="B117" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C117" t="s">
         <v>12</v>
@@ -43645,34 +43645,34 @@
         <v>891</v>
       </c>
       <c r="F117">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G117">
-        <v>2120</v>
+        <v>1605</v>
       </c>
       <c r="H117" t="s">
         <v>390</v>
       </c>
       <c r="I117">
-        <v>450000</v>
+        <v>600000</v>
       </c>
       <c r="J117" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="K117" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="L117">
-        <v>82.2</v>
+        <v>68</v>
       </c>
       <c r="M117">
-        <v>67.2</v>
+        <v>53</v>
       </c>
       <c r="N117">
-        <v>44</v>
+        <v>58.3</v>
       </c>
       <c r="O117">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="P117">
         <v>55.6</v>
@@ -43681,7 +43681,7 @@
         <v>0</v>
       </c>
       <c r="R117">
-        <v>48.4</v>
+        <v>55.6</v>
       </c>
       <c r="S117">
         <v>6</v>
@@ -43690,7 +43690,7 @@
         <v>1</v>
       </c>
       <c r="U117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V117" t="s">
         <v>276</v>
@@ -43699,7 +43699,7 @@
         <v>0</v>
       </c>
       <c r="X117" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="118" spans="1:24">
@@ -43707,7 +43707,7 @@
         <v>641</v>
       </c>
       <c r="B118" t="s">
-        <v>643</v>
+        <v>664</v>
       </c>
       <c r="C118" t="s">
         <v>12</v>
@@ -43716,19 +43716,19 @@
         <v>782</v>
       </c>
       <c r="E118" t="s">
-        <v>892</v>
+        <v>837</v>
       </c>
       <c r="F118">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G118">
-        <v>1605</v>
+        <v>2691</v>
       </c>
       <c r="H118" t="s">
-        <v>390</v>
+        <v>259</v>
       </c>
       <c r="I118">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="J118" t="s">
         <v>261</v>
@@ -43737,25 +43737,22 @@
         <v>261</v>
       </c>
       <c r="L118">
-        <v>68</v>
+        <v>60.4</v>
       </c>
       <c r="M118">
-        <v>53</v>
+        <v>45.4</v>
       </c>
       <c r="N118">
-        <v>58.3</v>
+        <v>62.9</v>
       </c>
       <c r="O118">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P118">
-        <v>55.6</v>
+        <v>54.1</v>
       </c>
       <c r="Q118">
         <v>0</v>
-      </c>
-      <c r="R118">
-        <v>55.6</v>
       </c>
       <c r="S118">
         <v>6</v>
@@ -43770,10 +43767,10 @@
         <v>276</v>
       </c>
       <c r="W118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X118" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="119" spans="1:24">
@@ -43781,7 +43778,7 @@
         <v>641</v>
       </c>
       <c r="B119" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="C119" t="s">
         <v>12</v>
@@ -43790,19 +43787,16 @@
         <v>783</v>
       </c>
       <c r="E119" t="s">
-        <v>837</v>
+        <v>892</v>
       </c>
       <c r="F119">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G119">
-        <v>2691</v>
-      </c>
-      <c r="H119" t="s">
-        <v>259</v>
+        <v>1989</v>
       </c>
       <c r="I119">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="J119" t="s">
         <v>261</v>
@@ -43811,19 +43805,19 @@
         <v>261</v>
       </c>
       <c r="L119">
-        <v>60.4</v>
+        <v>72.5</v>
       </c>
       <c r="M119">
-        <v>45.4</v>
+        <v>57.5</v>
       </c>
       <c r="N119">
-        <v>62.9</v>
+        <v>50.6</v>
       </c>
       <c r="O119">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P119">
-        <v>54.1</v>
+        <v>54</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -43864,13 +43858,13 @@
         <v>893</v>
       </c>
       <c r="F120">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G120">
-        <v>1989</v>
+        <v>1431</v>
       </c>
       <c r="I120">
-        <v>200000</v>
+        <v>450000</v>
       </c>
       <c r="J120" t="s">
         <v>261</v>
@@ -43879,19 +43873,19 @@
         <v>261</v>
       </c>
       <c r="L120">
-        <v>72.5</v>
+        <v>52.9</v>
       </c>
       <c r="M120">
-        <v>57.5</v>
+        <v>37.9</v>
       </c>
       <c r="N120">
-        <v>50.6</v>
+        <v>69.2</v>
       </c>
       <c r="O120">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P120">
-        <v>54</v>
+        <v>53.6</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -43920,7 +43914,7 @@
         <v>641</v>
       </c>
       <c r="B121" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="C121" t="s">
         <v>12</v>
@@ -43929,34 +43923,34 @@
         <v>785</v>
       </c>
       <c r="E121" t="s">
-        <v>894</v>
+        <v>883</v>
       </c>
       <c r="F121">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G121">
-        <v>1431</v>
+        <v>2076</v>
       </c>
       <c r="I121">
-        <v>450000</v>
+        <v>750000</v>
       </c>
       <c r="J121" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K121" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L121">
-        <v>52.9</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="M121">
-        <v>37.9</v>
+        <v>62.1</v>
       </c>
       <c r="N121">
-        <v>69.2</v>
+        <v>45.2</v>
       </c>
       <c r="O121">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P121">
         <v>53.6</v>
@@ -43971,7 +43965,7 @@
         <v>1</v>
       </c>
       <c r="U121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V121" t="s">
         <v>276</v>
@@ -44157,7 +44151,7 @@
         <v>267</v>
       </c>
       <c r="K124" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="L124">
         <v>72.5</v>
@@ -44213,7 +44207,7 @@
         <v>788</v>
       </c>
       <c r="E125" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="F125">
         <v>27</v>
@@ -44281,7 +44275,7 @@
         <v>789</v>
       </c>
       <c r="E126" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F126">
         <v>30</v>
@@ -44426,7 +44420,7 @@
         <v>791</v>
       </c>
       <c r="E128" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="F128">
         <v>30</v>
@@ -44500,7 +44494,7 @@
         <v>792</v>
       </c>
       <c r="E129" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="F129">
         <v>26</v>
@@ -44639,7 +44633,7 @@
         <v>794</v>
       </c>
       <c r="E131" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="F131">
         <v>27</v>
@@ -44713,7 +44707,7 @@
         <v>795</v>
       </c>
       <c r="E132" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F132">
         <v>26</v>
@@ -44787,7 +44781,7 @@
         <v>796</v>
       </c>
       <c r="E133" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="F133">
         <v>26</v>
@@ -44933,16 +44927,16 @@
         <v>641</v>
       </c>
       <c r="B2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F2">
         <v>24</v>
@@ -44957,10 +44951,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="K2" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="L2">
         <v>85.3</v>
@@ -45004,16 +44998,16 @@
         <v>641</v>
       </c>
       <c r="B3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="E3" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F3">
         <v>25</v>
@@ -45022,16 +45016,16 @@
         <v>3612</v>
       </c>
       <c r="H3" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="I3">
         <v>250000</v>
       </c>
       <c r="J3" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="K3" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="L3">
         <v>85.2</v>
@@ -45075,16 +45069,16 @@
         <v>641</v>
       </c>
       <c r="B4" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E4" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F4">
         <v>25</v>
@@ -45099,10 +45093,10 @@
         <v>150000</v>
       </c>
       <c r="J4" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="K4" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="L4">
         <v>82</v>
@@ -45152,7 +45146,7 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="E5" t="s">
         <v>857</v>
@@ -45170,10 +45164,10 @@
         <v>1500000</v>
       </c>
       <c r="J5" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="K5" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="L5">
         <v>81.7</v>
@@ -45223,10 +45217,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="E6" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F6">
         <v>27</v>
@@ -45241,10 +45235,10 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="K6" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="L6">
         <v>92.5</v>
@@ -45294,10 +45288,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E7" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F7">
         <v>26</v>
@@ -45306,7 +45300,7 @@
         <v>2288</v>
       </c>
       <c r="H7" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="I7">
         <v>400000</v>
@@ -45365,10 +45359,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E8" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F8">
         <v>24</v>
@@ -45383,10 +45377,10 @@
         <v>200000</v>
       </c>
       <c r="J8" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="K8" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="L8">
         <v>86.7</v>
@@ -45436,10 +45430,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="E9" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F9">
         <v>23</v>
@@ -45454,10 +45448,10 @@
         <v>300000</v>
       </c>
       <c r="J9" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="K9" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="L9">
         <v>81.8</v>
@@ -45507,10 +45501,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="E10" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F10">
         <v>26</v>
@@ -45572,16 +45566,16 @@
         <v>641</v>
       </c>
       <c r="B11" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C11" t="s">
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="E11" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F11">
         <v>27</v>
@@ -45596,10 +45590,10 @@
         <v>300000</v>
       </c>
       <c r="J11" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="K11" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="L11">
         <v>86.09999999999999</v>
@@ -45643,16 +45637,16 @@
         <v>641</v>
       </c>
       <c r="B12" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="E12" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F12">
         <v>22</v>
@@ -45667,10 +45661,10 @@
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="K12" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="L12">
         <v>85.7</v>
@@ -45720,10 +45714,10 @@
         <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="E13" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="F13">
         <v>25</v>
@@ -45738,10 +45732,10 @@
         <v>400000</v>
       </c>
       <c r="J13" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="K13" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="L13">
         <v>76.2</v>
@@ -45791,10 +45785,10 @@
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="E14" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="F14">
         <v>29</v>
@@ -45812,7 +45806,7 @@
         <v>262</v>
       </c>
       <c r="K14" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="L14">
         <v>78</v>
@@ -45856,16 +45850,16 @@
         <v>641</v>
       </c>
       <c r="B15" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="E15" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F15">
         <v>25</v>
@@ -45880,10 +45874,10 @@
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="K15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="L15">
         <v>82.90000000000001</v>
@@ -45927,16 +45921,16 @@
         <v>641</v>
       </c>
       <c r="B16" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="E16" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F16">
         <v>27</v>
@@ -45951,10 +45945,10 @@
         <v>300000</v>
       </c>
       <c r="J16" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="K16" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="L16">
         <v>85.7</v>
@@ -46004,10 +45998,10 @@
         <v>4</v>
       </c>
       <c r="D17" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="E17" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="F17">
         <v>25</v>
@@ -46022,10 +46016,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="K17" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="L17">
         <v>79.90000000000001</v>
@@ -46075,10 +46069,10 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E18" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F18">
         <v>26</v>
@@ -46143,16 +46137,16 @@
         <v>641</v>
       </c>
       <c r="B19" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C19" t="s">
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="E19" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="F19">
         <v>23</v>
@@ -46167,10 +46161,10 @@
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="K19" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="L19">
         <v>71.8</v>
@@ -46220,10 +46214,10 @@
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E20" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F20">
         <v>30</v>
@@ -46238,10 +46232,10 @@
         <v>600000</v>
       </c>
       <c r="J20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="K20" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="L20">
         <v>79.8</v>
@@ -46294,10 +46288,10 @@
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E21" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="F21">
         <v>25</v>
@@ -46312,10 +46306,10 @@
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="K21" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="L21">
         <v>73.59999999999999</v>
@@ -46368,10 +46362,10 @@
         <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E22" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="F22">
         <v>21</v>
@@ -46386,10 +46380,10 @@
         <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K22" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L22">
         <v>84.40000000000001</v>
@@ -46439,10 +46433,10 @@
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E23" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F23">
         <v>27</v>
@@ -46457,10 +46451,10 @@
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="K23" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="L23">
         <v>77.8</v>
@@ -46510,10 +46504,10 @@
         <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E24" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="F24">
         <v>33</v>
@@ -46522,16 +46516,16 @@
         <v>2606</v>
       </c>
       <c r="H24" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I24">
         <v>1200000</v>
       </c>
       <c r="J24" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="K24" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="L24">
         <v>81.3</v>
@@ -46584,10 +46578,10 @@
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E25" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F25">
         <v>32</v>
@@ -46602,10 +46596,10 @@
         <v>400000</v>
       </c>
       <c r="J25" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="K25" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="L25">
         <v>82</v>
@@ -46655,10 +46649,10 @@
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="E26" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="F26">
         <v>26</v>
@@ -46673,10 +46667,10 @@
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="K26" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="L26">
         <v>71.2</v>
@@ -46726,7 +46720,7 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E27" t="s">
         <v>884</v>
@@ -46744,10 +46738,10 @@
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="K27" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="L27">
         <v>67.59999999999999</v>
@@ -46800,10 +46794,10 @@
         <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E28" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F28">
         <v>26</v>
@@ -46818,10 +46812,10 @@
         <v>250000</v>
       </c>
       <c r="J28" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="K28" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="L28">
         <v>81.90000000000001</v>
@@ -46851,7 +46845,7 @@
         <v>1</v>
       </c>
       <c r="V28" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="W28" t="b">
         <v>1</v>
@@ -46865,16 +46859,16 @@
         <v>641</v>
       </c>
       <c r="B29" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C29" t="s">
         <v>6</v>
       </c>
       <c r="D29" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E29" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="F29">
         <v>22</v>
@@ -46936,16 +46930,16 @@
         <v>641</v>
       </c>
       <c r="B30" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C30" t="s">
         <v>6</v>
       </c>
       <c r="D30" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E30" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="F30">
         <v>31</v>
@@ -46960,10 +46954,10 @@
         <v>650000</v>
       </c>
       <c r="J30" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="K30" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="L30">
         <v>79.40000000000001</v>
@@ -47007,16 +47001,16 @@
         <v>641</v>
       </c>
       <c r="B31" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C31" t="s">
         <v>6</v>
       </c>
       <c r="D31" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="E31" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="F31">
         <v>29</v>
@@ -47025,16 +47019,16 @@
         <v>2375</v>
       </c>
       <c r="H31" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I31">
         <v>800000</v>
       </c>
       <c r="J31" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="K31" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="L31">
         <v>73.40000000000001</v>
@@ -47087,10 +47081,10 @@
         <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E32" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="F32">
         <v>26</v>
@@ -47105,10 +47099,10 @@
         <v>300000</v>
       </c>
       <c r="J32" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="K32" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="L32">
         <v>91.2</v>
@@ -47161,10 +47155,10 @@
         <v>7</v>
       </c>
       <c r="D33" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E33" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="F33">
         <v>27</v>
@@ -47179,10 +47173,10 @@
         <v>1500000</v>
       </c>
       <c r="J33" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="K33" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="L33">
         <v>93.40000000000001</v>
@@ -47229,16 +47223,16 @@
         <v>641</v>
       </c>
       <c r="B34" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C34" t="s">
         <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E34" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="F34">
         <v>23</v>
@@ -47253,10 +47247,10 @@
         <v>0</v>
       </c>
       <c r="J34" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="K34" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="L34">
         <v>91.7</v>
@@ -47306,7 +47300,7 @@
         <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E35" t="s">
         <v>879</v>
@@ -47377,10 +47371,10 @@
         <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="E36" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="F36">
         <v>26</v>
@@ -47395,10 +47389,10 @@
         <v>200000</v>
       </c>
       <c r="J36" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="K36" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="L36">
         <v>88.09999999999999</v>
@@ -47442,16 +47436,16 @@
         <v>641</v>
       </c>
       <c r="B37" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C37" t="s">
         <v>7</v>
       </c>
       <c r="D37" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E37" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="F37">
         <v>24</v>
@@ -47463,10 +47457,10 @@
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="K37" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="L37">
         <v>79.40000000000001</v>
@@ -47516,7 +47510,7 @@
         <v>7</v>
       </c>
       <c r="D38" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E38" t="s">
         <v>811</v>
@@ -47531,10 +47525,10 @@
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="K38" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="L38">
         <v>82.59999999999999</v>
@@ -47564,7 +47558,7 @@
         <v>1</v>
       </c>
       <c r="V38" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="W38" t="b">
         <v>1</v>
@@ -47584,10 +47578,10 @@
         <v>7</v>
       </c>
       <c r="D39" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E39" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="F39">
         <v>25</v>
@@ -47602,10 +47596,10 @@
         <v>125000</v>
       </c>
       <c r="J39" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="K39" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="L39">
         <v>86.5</v>
@@ -47655,10 +47649,10 @@
         <v>7</v>
       </c>
       <c r="D40" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="E40" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F40">
         <v>26</v>
@@ -47667,7 +47661,7 @@
         <v>1388</v>
       </c>
       <c r="H40" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I40">
         <v>500000</v>
@@ -47726,10 +47720,10 @@
         <v>7</v>
       </c>
       <c r="D41" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E41" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="F41">
         <v>27</v>
@@ -47744,10 +47738,10 @@
         <v>1400000</v>
       </c>
       <c r="J41" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="K41" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="L41">
         <v>73.40000000000001</v>
@@ -47800,7 +47794,7 @@
         <v>5</v>
       </c>
       <c r="D42" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E42" t="s">
         <v>831</v>
@@ -47818,10 +47812,10 @@
         <v>500000</v>
       </c>
       <c r="J42" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K42" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L42">
         <v>87.2</v>
@@ -47868,16 +47862,16 @@
         <v>641</v>
       </c>
       <c r="B43" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C43" t="s">
         <v>5</v>
       </c>
       <c r="D43" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E43" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="F43">
         <v>18</v>
@@ -47892,10 +47886,10 @@
         <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="K43" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="L43">
         <v>83.40000000000001</v>
@@ -47945,10 +47939,10 @@
         <v>5</v>
       </c>
       <c r="D44" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="E44" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="F44">
         <v>23</v>
@@ -47963,10 +47957,10 @@
         <v>0</v>
       </c>
       <c r="J44" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="K44" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="L44">
         <v>85.3</v>
@@ -48019,10 +48013,10 @@
         <v>5</v>
       </c>
       <c r="D45" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="E45" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="F45">
         <v>33</v>
@@ -48037,10 +48031,10 @@
         <v>1500000</v>
       </c>
       <c r="J45" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="K45" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="L45">
         <v>80</v>
@@ -48090,10 +48084,10 @@
         <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E46" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="F46">
         <v>21</v>
@@ -48164,10 +48158,10 @@
         <v>5</v>
       </c>
       <c r="D47" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E47" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="F47">
         <v>25</v>
@@ -48182,10 +48176,10 @@
         <v>300000</v>
       </c>
       <c r="J47" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="K47" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="L47">
         <v>84.7</v>
@@ -48215,7 +48209,7 @@
         <v>1</v>
       </c>
       <c r="V47" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="W47" t="b">
         <v>0</v>
@@ -48235,7 +48229,7 @@
         <v>5</v>
       </c>
       <c r="D48" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E48" t="s">
         <v>832</v>
@@ -48300,16 +48294,16 @@
         <v>641</v>
       </c>
       <c r="B49" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C49" t="s">
         <v>5</v>
       </c>
       <c r="D49" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E49" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F49">
         <v>21</v>
@@ -48324,10 +48318,10 @@
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="K49" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="L49">
         <v>73.09999999999999</v>
@@ -48377,10 +48371,10 @@
         <v>5</v>
       </c>
       <c r="D50" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E50" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F50">
         <v>29</v>
@@ -48392,10 +48386,10 @@
         <v>500000</v>
       </c>
       <c r="J50" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="K50" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="L50">
         <v>84.3</v>
@@ -48439,16 +48433,16 @@
         <v>641</v>
       </c>
       <c r="B51" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C51" t="s">
         <v>5</v>
       </c>
       <c r="D51" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E51" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="F51">
         <v>23</v>
@@ -48463,10 +48457,10 @@
         <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="K51" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="L51">
         <v>81.3</v>
@@ -48519,10 +48513,10 @@
         <v>8</v>
       </c>
       <c r="D52" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="E52" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="F52">
         <v>29</v>
@@ -48531,16 +48525,16 @@
         <v>1170</v>
       </c>
       <c r="H52" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I52">
         <v>550000</v>
       </c>
       <c r="J52" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="K52" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="L52">
         <v>89.7</v>
@@ -48590,10 +48584,10 @@
         <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="E53" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="F53">
         <v>31</v>
@@ -48608,10 +48602,10 @@
         <v>1400000</v>
       </c>
       <c r="J53" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="K53" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="L53">
         <v>83.3</v>
@@ -48661,10 +48655,10 @@
         <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E54" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="F54">
         <v>28</v>
@@ -48679,10 +48673,10 @@
         <v>0</v>
       </c>
       <c r="J54" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K54" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L54">
         <v>92.7</v>
@@ -48732,7 +48726,7 @@
         <v>8</v>
       </c>
       <c r="D55" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E55" t="s">
         <v>837</v>
@@ -48750,10 +48744,10 @@
         <v>0</v>
       </c>
       <c r="J55" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="K55" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="L55">
         <v>74.5</v>
@@ -48797,16 +48791,16 @@
         <v>641</v>
       </c>
       <c r="B56" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C56" t="s">
         <v>8</v>
       </c>
       <c r="D56" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="E56" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="F56">
         <v>21</v>
@@ -48868,16 +48862,16 @@
         <v>641</v>
       </c>
       <c r="B57" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C57" t="s">
         <v>8</v>
       </c>
       <c r="D57" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E57" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="F57">
         <v>25</v>
@@ -48892,10 +48886,10 @@
         <v>400000</v>
       </c>
       <c r="J57" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="K57" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="L57">
         <v>91.7</v>
@@ -48945,10 +48939,10 @@
         <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E58" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="F58">
         <v>22</v>
@@ -48963,10 +48957,10 @@
         <v>0</v>
       </c>
       <c r="J58" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="K58" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="L58">
         <v>87.90000000000001</v>
@@ -49016,10 +49010,10 @@
         <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E59" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="F59">
         <v>32</v>
@@ -49034,10 +49028,10 @@
         <v>800000</v>
       </c>
       <c r="J59" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="K59" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="L59">
         <v>73.09999999999999</v>
@@ -49090,10 +49084,10 @@
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E60" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="F60">
         <v>28</v>
@@ -49108,10 +49102,10 @@
         <v>400000</v>
       </c>
       <c r="J60" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="K60" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="L60">
         <v>86.2</v>
@@ -49164,10 +49158,10 @@
         <v>8</v>
       </c>
       <c r="D61" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E61" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="F61">
         <v>28</v>
@@ -49182,10 +49176,10 @@
         <v>100000</v>
       </c>
       <c r="J61" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="K61" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="L61">
         <v>79.2</v>
@@ -49235,10 +49229,10 @@
         <v>9</v>
       </c>
       <c r="D62" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="E62" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F62">
         <v>25</v>
@@ -49250,10 +49244,10 @@
         <v>0</v>
       </c>
       <c r="J62" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="K62" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="L62">
         <v>87.59999999999999</v>
@@ -49303,10 +49297,10 @@
         <v>9</v>
       </c>
       <c r="D63" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="E63" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="F63">
         <v>20</v>
@@ -49321,10 +49315,10 @@
         <v>0</v>
       </c>
       <c r="J63" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="K63" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="L63">
         <v>87.59999999999999</v>
@@ -49374,10 +49368,10 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E64" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="F64">
         <v>23</v>
@@ -49392,10 +49386,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="K64" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="L64">
         <v>83.90000000000001</v>
@@ -49442,16 +49436,16 @@
         <v>641</v>
       </c>
       <c r="B65" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C65" t="s">
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E65" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="F65">
         <v>33</v>
@@ -49466,10 +49460,10 @@
         <v>1200000</v>
       </c>
       <c r="J65" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="K65" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="L65">
         <v>88.90000000000001</v>
@@ -49519,10 +49513,10 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E66" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="F66">
         <v>22</v>
@@ -49531,16 +49525,16 @@
         <v>1941</v>
       </c>
       <c r="H66" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I66">
         <v>1500000</v>
       </c>
       <c r="J66" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="K66" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="L66">
         <v>77.7</v>
@@ -49584,16 +49578,16 @@
         <v>641</v>
       </c>
       <c r="B67" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C67" t="s">
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E67" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="F67">
         <v>28</v>
@@ -49608,10 +49602,10 @@
         <v>600000</v>
       </c>
       <c r="J67" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="K67" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="L67">
         <v>83.7</v>
@@ -49661,10 +49655,10 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E68" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="F68">
         <v>30</v>
@@ -49682,7 +49676,7 @@
         <v>657</v>
       </c>
       <c r="K68" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="L68">
         <v>92.8</v>
@@ -49726,16 +49720,16 @@
         <v>641</v>
       </c>
       <c r="B69" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C69" t="s">
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E69" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="F69">
         <v>25</v>
@@ -49744,16 +49738,16 @@
         <v>1839</v>
       </c>
       <c r="H69" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I69">
         <v>25000</v>
       </c>
       <c r="J69" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K69" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L69">
         <v>84.5</v>
@@ -49797,16 +49791,16 @@
         <v>641</v>
       </c>
       <c r="B70" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C70" t="s">
         <v>9</v>
       </c>
       <c r="D70" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E70" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="F70">
         <v>23</v>
@@ -49821,10 +49815,10 @@
         <v>0</v>
       </c>
       <c r="J70" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="K70" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="L70">
         <v>88.3</v>
@@ -49868,16 +49862,16 @@
         <v>641</v>
       </c>
       <c r="B71" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C71" t="s">
         <v>9</v>
       </c>
       <c r="D71" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E71" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="F71">
         <v>30</v>
@@ -49886,16 +49880,16 @@
         <v>1263</v>
       </c>
       <c r="H71" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="I71">
         <v>850000</v>
       </c>
       <c r="J71" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="K71" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="L71">
         <v>92.40000000000001</v>
@@ -49945,10 +49939,10 @@
         <v>10</v>
       </c>
       <c r="D72" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E72" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="F72">
         <v>25</v>
@@ -49963,10 +49957,10 @@
         <v>1200000</v>
       </c>
       <c r="J72" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="K72" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="L72">
         <v>94.5</v>
@@ -50019,10 +50013,10 @@
         <v>10</v>
       </c>
       <c r="D73" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E73" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="F73">
         <v>24</v>
@@ -50037,10 +50031,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K73" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L73">
         <v>92.7</v>
@@ -50090,10 +50084,10 @@
         <v>10</v>
       </c>
       <c r="D74" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E74" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="F74">
         <v>23</v>
@@ -50102,16 +50096,16 @@
         <v>2730</v>
       </c>
       <c r="H74" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I74">
         <v>0</v>
       </c>
       <c r="J74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="K74" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="L74">
         <v>91.7</v>
@@ -50158,16 +50152,16 @@
         <v>641</v>
       </c>
       <c r="B75" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C75" t="s">
         <v>10</v>
       </c>
       <c r="D75" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E75" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="F75">
         <v>18</v>
@@ -50182,10 +50176,10 @@
         <v>0</v>
       </c>
       <c r="J75" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="K75" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="L75">
         <v>89.09999999999999</v>
@@ -50235,10 +50229,10 @@
         <v>10</v>
       </c>
       <c r="D76" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="E76" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F76">
         <v>29</v>
@@ -50253,10 +50247,10 @@
         <v>0</v>
       </c>
       <c r="J76" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="K76" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="L76">
         <v>88.40000000000001</v>
@@ -50306,10 +50300,10 @@
         <v>10</v>
       </c>
       <c r="D77" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E77" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="F77">
         <v>25</v>
@@ -50321,10 +50315,10 @@
         <v>400000</v>
       </c>
       <c r="J77" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="K77" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="L77">
         <v>81.8</v>
@@ -50374,7 +50368,7 @@
         <v>10</v>
       </c>
       <c r="D78" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="E78" t="s">
         <v>851</v>
@@ -50392,10 +50386,10 @@
         <v>1000000</v>
       </c>
       <c r="J78" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="K78" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="L78">
         <v>83</v>
@@ -50439,16 +50433,16 @@
         <v>641</v>
       </c>
       <c r="B79" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C79" t="s">
         <v>10</v>
       </c>
       <c r="D79" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E79" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="F79">
         <v>25</v>
@@ -50463,10 +50457,10 @@
         <v>0</v>
       </c>
       <c r="J79" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="K79" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="L79">
         <v>86.7</v>
@@ -50519,7 +50513,7 @@
         <v>10</v>
       </c>
       <c r="D80" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="E80" t="s">
         <v>813</v>
@@ -50537,10 +50531,10 @@
         <v>0</v>
       </c>
       <c r="J80" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="K80" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="L80">
         <v>82.7</v>
@@ -50590,10 +50584,10 @@
         <v>10</v>
       </c>
       <c r="D81" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E81" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="F81">
         <v>29</v>
@@ -50608,10 +50602,10 @@
         <v>1200000</v>
       </c>
       <c r="J81" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="K81" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="L81">
         <v>93.8</v>
@@ -50664,10 +50658,10 @@
         <v>11</v>
       </c>
       <c r="D82" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="E82" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F82">
         <v>26</v>
@@ -50682,10 +50676,10 @@
         <v>500000</v>
       </c>
       <c r="J82" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="K82" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="L82">
         <v>82.59999999999999</v>
@@ -50735,10 +50729,10 @@
         <v>11</v>
       </c>
       <c r="D83" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="E83" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="F83">
         <v>23</v>
@@ -50753,10 +50747,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="K83" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="L83">
         <v>95.5</v>
@@ -50803,16 +50797,16 @@
         <v>641</v>
       </c>
       <c r="B84" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C84" t="s">
         <v>11</v>
       </c>
       <c r="D84" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E84" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="F84">
         <v>24</v>
@@ -50827,10 +50821,10 @@
         <v>0</v>
       </c>
       <c r="J84" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="K84" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="L84">
         <v>76.59999999999999</v>
@@ -50880,10 +50874,10 @@
         <v>11</v>
       </c>
       <c r="D85" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E85" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F85">
         <v>25</v>
@@ -50892,16 +50886,16 @@
         <v>1983</v>
       </c>
       <c r="H85" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I85">
         <v>0</v>
       </c>
       <c r="J85" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="K85" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="L85">
         <v>84.2</v>
@@ -50951,10 +50945,10 @@
         <v>11</v>
       </c>
       <c r="D86" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E86" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="F86">
         <v>30</v>
@@ -50969,10 +50963,10 @@
         <v>1200000</v>
       </c>
       <c r="J86" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="K86" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="L86">
         <v>70.8</v>
@@ -51022,7 +51016,7 @@
         <v>11</v>
       </c>
       <c r="D87" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E87" t="s">
         <v>831</v>
@@ -51040,10 +51034,10 @@
         <v>400000</v>
       </c>
       <c r="J87" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K87" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L87">
         <v>77.40000000000001</v>
@@ -51090,16 +51084,16 @@
         <v>641</v>
       </c>
       <c r="B88" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C88" t="s">
         <v>11</v>
       </c>
       <c r="D88" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E88" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="F88">
         <v>25</v>
@@ -51114,10 +51108,10 @@
         <v>0</v>
       </c>
       <c r="J88" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="K88" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="L88">
         <v>81.2</v>
@@ -51167,7 +51161,7 @@
         <v>11</v>
       </c>
       <c r="D89" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="E89" t="s">
         <v>858</v>
@@ -51238,7 +51232,7 @@
         <v>11</v>
       </c>
       <c r="D90" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E90" t="s">
         <v>857</v>
@@ -51256,10 +51250,10 @@
         <v>800000</v>
       </c>
       <c r="J90" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="K90" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="L90">
         <v>74.2</v>
@@ -51312,7 +51306,7 @@
         <v>11</v>
       </c>
       <c r="D91" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E91" t="s">
         <v>846</v>
@@ -51327,10 +51321,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="K91" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="L91">
         <v>78.8</v>
@@ -51374,16 +51368,16 @@
         <v>641</v>
       </c>
       <c r="B92" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C92" t="s">
         <v>12</v>
       </c>
       <c r="D92" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E92" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="F92">
         <v>18</v>
@@ -51398,10 +51392,10 @@
         <v>0</v>
       </c>
       <c r="J92" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="K92" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="L92">
         <v>82.5</v>
@@ -51454,7 +51448,7 @@
         <v>12</v>
       </c>
       <c r="D93" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E93" t="s">
         <v>810</v>
@@ -51469,10 +51463,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="K93" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="L93">
         <v>90.8</v>
@@ -51522,10 +51516,10 @@
         <v>12</v>
       </c>
       <c r="D94" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="E94" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="F94">
         <v>23</v>
@@ -51537,10 +51531,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="K94" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="L94">
         <v>88.59999999999999</v>
@@ -51593,10 +51587,10 @@
         <v>12</v>
       </c>
       <c r="D95" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E95" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="F95">
         <v>23</v>
@@ -51611,10 +51605,10 @@
         <v>800000</v>
       </c>
       <c r="J95" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="K95" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="L95">
         <v>80</v>
@@ -51667,7 +51661,7 @@
         <v>12</v>
       </c>
       <c r="D96" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="E96" t="s">
         <v>860</v>
@@ -51682,10 +51676,10 @@
         <v>550000</v>
       </c>
       <c r="J96" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="K96" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="L96">
         <v>84</v>
@@ -51735,10 +51729,10 @@
         <v>12</v>
       </c>
       <c r="D97" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="E97" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F97">
         <v>28</v>
@@ -51750,10 +51744,10 @@
         <v>700000</v>
       </c>
       <c r="J97" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="K97" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="L97">
         <v>92.90000000000001</v>
@@ -51803,10 +51797,10 @@
         <v>12</v>
       </c>
       <c r="D98" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="E98" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="F98">
         <v>19</v>
@@ -51821,10 +51815,10 @@
         <v>0</v>
       </c>
       <c r="J98" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="K98" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="L98">
         <v>75.7</v>
@@ -51874,10 +51868,10 @@
         <v>12</v>
       </c>
       <c r="D99" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E99" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="F99">
         <v>27</v>
@@ -51892,10 +51886,10 @@
         <v>200000</v>
       </c>
       <c r="J99" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="K99" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="L99">
         <v>74.3</v>
@@ -51945,10 +51939,10 @@
         <v>12</v>
       </c>
       <c r="D100" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E100" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="F100">
         <v>25</v>
@@ -51963,10 +51957,10 @@
         <v>900000</v>
       </c>
       <c r="J100" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="K100" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="L100">
         <v>84.3</v>
@@ -51996,7 +51990,7 @@
         <v>1</v>
       </c>
       <c r="V100" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="W100" t="b">
         <v>0</v>
@@ -52016,10 +52010,10 @@
         <v>12</v>
       </c>
       <c r="D101" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E101" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="F101">
         <v>25</v>
@@ -52034,10 +52028,10 @@
         <v>500000</v>
       </c>
       <c r="J101" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="K101" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="L101">
         <v>70</v>
@@ -52084,16 +52078,16 @@
         <v>641</v>
       </c>
       <c r="B102" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C102" t="s">
         <v>13</v>
       </c>
       <c r="D102" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E102" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="F102">
         <v>26</v>
@@ -52155,16 +52149,16 @@
         <v>641</v>
       </c>
       <c r="B103" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C103" t="s">
         <v>13</v>
       </c>
       <c r="D103" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="E103" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="F103">
         <v>29</v>
@@ -52179,10 +52173,10 @@
         <v>0</v>
       </c>
       <c r="J103" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="K103" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="L103">
         <v>78.40000000000001</v>
@@ -52232,7 +52226,7 @@
         <v>13</v>
       </c>
       <c r="D104" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E104" t="s">
         <v>837</v>
@@ -52250,10 +52244,10 @@
         <v>0</v>
       </c>
       <c r="J104" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="K104" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L104">
         <v>92.40000000000001</v>
@@ -52297,16 +52291,16 @@
         <v>641</v>
       </c>
       <c r="B105" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C105" t="s">
         <v>13</v>
       </c>
       <c r="D105" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E105" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="F105">
         <v>22</v>
@@ -52324,7 +52318,7 @@
         <v>262</v>
       </c>
       <c r="K105" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L105">
         <v>88</v>
@@ -52368,16 +52362,16 @@
         <v>641</v>
       </c>
       <c r="B106" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C106" t="s">
         <v>13</v>
       </c>
       <c r="D106" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="E106" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="F106">
         <v>24</v>
@@ -52392,10 +52386,10 @@
         <v>0</v>
       </c>
       <c r="J106" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="K106" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="L106">
         <v>78.59999999999999</v>
@@ -52445,10 +52439,10 @@
         <v>13</v>
       </c>
       <c r="D107" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E107" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="F107">
         <v>23</v>
@@ -52463,10 +52457,10 @@
         <v>0</v>
       </c>
       <c r="J107" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="K107" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="L107">
         <v>78.40000000000001</v>
@@ -52516,7 +52510,7 @@
         <v>13</v>
       </c>
       <c r="D108" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E108" t="s">
         <v>821</v>
@@ -52581,16 +52575,16 @@
         <v>641</v>
       </c>
       <c r="B109" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C109" t="s">
         <v>13</v>
       </c>
       <c r="D109" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="E109" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="F109">
         <v>24</v>
@@ -52605,10 +52599,10 @@
         <v>0</v>
       </c>
       <c r="J109" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="K109" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="L109">
         <v>65.7</v>
@@ -52655,16 +52649,16 @@
         <v>641</v>
       </c>
       <c r="B110" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C110" t="s">
         <v>13</v>
       </c>
       <c r="D110" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="E110" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="F110">
         <v>27</v>
@@ -52679,10 +52673,10 @@
         <v>1500000</v>
       </c>
       <c r="J110" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="K110" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="L110">
         <v>89.40000000000001</v>
@@ -52735,10 +52729,10 @@
         <v>13</v>
       </c>
       <c r="D111" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E111" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F111">
         <v>27</v>
@@ -52753,10 +52747,10 @@
         <v>0</v>
       </c>
       <c r="J111" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="K111" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="L111">
         <v>82</v>
@@ -52908,7 +52902,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="E2" t="s">
         <v>243</v>
@@ -52979,7 +52973,7 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="E3" t="s">
         <v>243</v>
@@ -53068,7 +53062,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="E4" t="s">
         <v>243</v>
@@ -53157,7 +53151,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="E5" t="s">
         <v>243</v>
@@ -53430,7 +53424,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="E8" t="s">
         <v>243</v>
@@ -53522,7 +53516,7 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="E9" t="s">
         <v>243</v>
@@ -53614,7 +53608,7 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="E10" t="s">
         <v>243</v>
@@ -53706,7 +53700,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="E11" t="s">
         <v>243</v>
@@ -54299,7 +54293,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="E18" t="s">
         <v>230</v>
@@ -54456,7 +54450,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="E20" t="s">
         <v>230</v>
@@ -54978,7 +54972,7 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="E26" t="s">
         <v>230</v>
@@ -55657,7 +55651,7 @@
         <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="E34" t="s">
         <v>228</v>
@@ -55826,7 +55820,7 @@
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="E36" t="s">
         <v>228</v>
@@ -55838,7 +55832,7 @@
         <v>1661</v>
       </c>
       <c r="H36" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="J36" t="s">
         <v>261</v>
@@ -55906,7 +55900,7 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E37" t="s">
         <v>228</v>
@@ -56090,7 +56084,7 @@
         <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="E39" t="s">
         <v>228</v>
@@ -56182,7 +56176,7 @@
         <v>9</v>
       </c>
       <c r="D40" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E40" t="s">
         <v>231</v>
@@ -56274,7 +56268,7 @@
         <v>6</v>
       </c>
       <c r="D41" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E41" t="s">
         <v>231</v>
@@ -56458,7 +56452,7 @@
         <v>11</v>
       </c>
       <c r="D43" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="E43" t="s">
         <v>231</v>
@@ -56470,7 +56464,7 @@
         <v>1917</v>
       </c>
       <c r="H43" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="J43" t="s">
         <v>261</v>
@@ -56624,7 +56618,7 @@
         <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="E45" t="s">
         <v>231</v>
@@ -56716,7 +56710,7 @@
         <v>9</v>
       </c>
       <c r="D46" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="E46" t="s">
         <v>231</v>
@@ -56876,7 +56870,7 @@
         <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="E48" t="s">
         <v>231</v>
@@ -57030,7 +57024,7 @@
         <v>3</v>
       </c>
       <c r="D50" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E50" t="s">
         <v>231</v>
@@ -57107,7 +57101,7 @@
         <v>7</v>
       </c>
       <c r="D51" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="E51" t="s">
         <v>231</v>
@@ -57273,7 +57267,7 @@
         <v>9</v>
       </c>
       <c r="D53" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="E53" t="s">
         <v>241</v>
@@ -57457,7 +57451,7 @@
         <v>3</v>
       </c>
       <c r="D55" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="E55" t="s">
         <v>241</v>
@@ -57789,7 +57783,7 @@
         <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="E59" t="s">
         <v>241</v>
@@ -57881,7 +57875,7 @@
         <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="E60" t="s">
         <v>241</v>
@@ -58228,7 +58222,7 @@
         <v>8</v>
       </c>
       <c r="D64" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="E64" t="s">
         <v>241</v>
@@ -58320,7 +58314,7 @@
         <v>12</v>
       </c>
       <c r="D65" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="E65" t="s">
         <v>241</v>
@@ -58759,7 +58753,7 @@
         <v>5</v>
       </c>
       <c r="D70" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="E70" t="s">
         <v>226</v>
@@ -59637,7 +59631,7 @@
         <v>7</v>
       </c>
       <c r="D80" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="E80" t="s">
         <v>226</v>
@@ -59714,7 +59708,7 @@
         <v>6</v>
       </c>
       <c r="D81" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="E81" t="s">
         <v>233</v>
@@ -60135,7 +60129,7 @@
         <v>9</v>
       </c>
       <c r="D86" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="E86" t="s">
         <v>233</v>
@@ -60942,7 +60936,7 @@
         <v>10</v>
       </c>
       <c r="D95" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="E95" t="s">
         <v>225</v>
@@ -61022,7 +61016,7 @@
         <v>13</v>
       </c>
       <c r="D96" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="E96" t="s">
         <v>225</v>
@@ -61114,7 +61108,7 @@
         <v>7</v>
       </c>
       <c r="D97" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="E97" t="s">
         <v>225</v>
@@ -61283,7 +61277,7 @@
         <v>6</v>
       </c>
       <c r="D99" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="E99" t="s">
         <v>225</v>
@@ -61559,7 +61553,7 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="E102" t="s">
         <v>225</v>
@@ -61651,7 +61645,7 @@
         <v>6</v>
       </c>
       <c r="D103" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="E103" t="s">
         <v>225</v>
@@ -61743,7 +61737,7 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="E104" t="s">
         <v>236</v>
@@ -61835,7 +61829,7 @@
         <v>6</v>
       </c>
       <c r="D105" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E105" t="s">
         <v>236</v>
@@ -61927,7 +61921,7 @@
         <v>6</v>
       </c>
       <c r="D106" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E106" t="s">
         <v>236</v>
@@ -62321,7 +62315,7 @@
         <v>4</v>
       </c>
       <c r="D111" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="E111" t="s">
         <v>236</v>
@@ -62834,7 +62828,7 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="E117" t="s">
         <v>238</v>
@@ -63015,7 +63009,7 @@
         <v>3</v>
       </c>
       <c r="D119" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="E119" t="s">
         <v>238</v>
@@ -63545,7 +63539,7 @@
         <v>6</v>
       </c>
       <c r="D126" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E126" t="s">
         <v>238</v>
@@ -63729,7 +63723,7 @@
         <v>5</v>
       </c>
       <c r="D128" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="E128" t="s">
         <v>238</v>
@@ -63741,7 +63735,7 @@
         <v>1162</v>
       </c>
       <c r="H128" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="I128">
         <v>1800000</v>
@@ -64144,7 +64138,7 @@
         <v>5</v>
       </c>
       <c r="D133" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="E133" t="s">
         <v>232</v>
@@ -64829,7 +64823,7 @@
         <v>13</v>
       </c>
       <c r="D141" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E141" t="s">
         <v>232</v>
@@ -65010,7 +65004,7 @@
         <v>7</v>
       </c>
       <c r="D143" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E143" t="s">
         <v>232</v>
@@ -65152,7 +65146,7 @@
         <v>9</v>
       </c>
       <c r="D145" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E145" t="s">
         <v>232</v>
@@ -65813,7 +65807,7 @@
         <v>6</v>
       </c>
       <c r="D153" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="E153" t="s">
         <v>224</v>
@@ -65976,7 +65970,7 @@
         <v>5</v>
       </c>
       <c r="D155" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="E155" t="s">
         <v>224</v>
@@ -66148,7 +66142,7 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="E157" t="s">
         <v>224</v>
@@ -66498,7 +66492,7 @@
         <v>13</v>
       </c>
       <c r="D161" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="E161" t="s">
         <v>224</v>
@@ -66581,7 +66575,7 @@
         <v>4</v>
       </c>
       <c r="D162" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="E162" t="s">
         <v>224</v>
@@ -66827,7 +66821,7 @@
         <v>7</v>
       </c>
       <c r="D165" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="E165" t="s">
         <v>234</v>
@@ -66996,7 +66990,7 @@
         <v>13</v>
       </c>
       <c r="D167" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="E167" t="s">
         <v>234</v>
@@ -67417,7 +67411,7 @@
         <v>4</v>
       </c>
       <c r="D172" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="E172" t="s">
         <v>234</v>
@@ -67506,7 +67500,7 @@
         <v>9</v>
       </c>
       <c r="D173" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="E173" t="s">
         <v>234</v>
@@ -67912,7 +67906,7 @@
         <v>10</v>
       </c>
       <c r="D178" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="E178" t="s">
         <v>235</v>
@@ -68001,7 +67995,7 @@
         <v>13</v>
       </c>
       <c r="D179" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="E179" t="s">
         <v>235</v>
@@ -68410,7 +68404,7 @@
         <v>4</v>
       </c>
       <c r="D184" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="E184" t="s">
         <v>235</v>
@@ -68920,7 +68914,7 @@
         <v>4</v>
       </c>
       <c r="D190" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="E190" t="s">
         <v>235</v>
@@ -69012,7 +69006,7 @@
         <v>3</v>
       </c>
       <c r="D191" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="E191" t="s">
         <v>240</v>
@@ -69089,7 +69083,7 @@
         <v>5</v>
       </c>
       <c r="D192" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="E192" t="s">
         <v>240</v>
@@ -70254,7 +70248,7 @@
         <v>9</v>
       </c>
       <c r="D206" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="E206" t="s">
         <v>239</v>
@@ -70346,7 +70340,7 @@
         <v>3</v>
       </c>
       <c r="D207" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="E207" t="s">
         <v>239</v>
@@ -70423,7 +70417,7 @@
         <v>8</v>
       </c>
       <c r="D208" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="E208" t="s">
         <v>239</v>
@@ -70515,7 +70509,7 @@
         <v>7</v>
       </c>
       <c r="D209" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="E209" t="s">
         <v>239</v>
@@ -70607,7 +70601,7 @@
         <v>13</v>
       </c>
       <c r="D210" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="E210" t="s">
         <v>239</v>
@@ -71156,7 +71150,7 @@
         <v>12</v>
       </c>
       <c r="D216" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="E216" t="s">
         <v>239</v>
@@ -71248,7 +71242,7 @@
         <v>6</v>
       </c>
       <c r="D217" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E217" t="s">
         <v>239</v>
@@ -71340,7 +71334,7 @@
         <v>4</v>
       </c>
       <c r="D218" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="E218" t="s">
         <v>239</v>
@@ -71420,7 +71414,7 @@
         <v>6</v>
       </c>
       <c r="D219" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="E219" t="s">
         <v>237</v>
@@ -71509,7 +71503,7 @@
         <v>9</v>
       </c>
       <c r="D220" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="E220" t="s">
         <v>237</v>
@@ -71598,7 +71592,7 @@
         <v>10</v>
       </c>
       <c r="D221" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E221" t="s">
         <v>237</v>
@@ -71690,7 +71684,7 @@
         <v>3</v>
       </c>
       <c r="D222" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="E222" t="s">
         <v>237</v>
@@ -71767,7 +71761,7 @@
         <v>7</v>
       </c>
       <c r="D223" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="E223" t="s">
         <v>237</v>
@@ -71936,7 +71930,7 @@
         <v>7</v>
       </c>
       <c r="D225" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="E225" t="s">
         <v>237</v>
@@ -72108,7 +72102,7 @@
         <v>4</v>
       </c>
       <c r="D227" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="E227" t="s">
         <v>237</v>
@@ -72194,7 +72188,7 @@
         <v>6</v>
       </c>
       <c r="D228" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="E228" t="s">
         <v>237</v>
@@ -72206,7 +72200,7 @@
         <v>1053</v>
       </c>
       <c r="H228" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="J228" t="s">
         <v>263</v>
@@ -72283,7 +72277,7 @@
         <v>13</v>
       </c>
       <c r="D229" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="E229" t="s">
         <v>237</v>
@@ -72372,7 +72366,7 @@
         <v>4</v>
       </c>
       <c r="D230" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="E230" t="s">
         <v>237</v>
@@ -72461,7 +72455,7 @@
         <v>5</v>
       </c>
       <c r="D231" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E231" t="s">
         <v>237</v>
@@ -72473,7 +72467,7 @@
         <v>917</v>
       </c>
       <c r="H231" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="J231" t="s">
         <v>261</v>
@@ -72550,7 +72544,7 @@
         <v>6</v>
       </c>
       <c r="D232" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="E232" t="s">
         <v>237</v>
@@ -72627,7 +72621,7 @@
         <v>9</v>
       </c>
       <c r="D233" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="E233" t="s">
         <v>237</v>
@@ -73395,7 +73389,7 @@
         <v>6</v>
       </c>
       <c r="D242" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="E242" t="s">
         <v>227</v>
@@ -73472,7 +73466,7 @@
         <v>4</v>
       </c>
       <c r="D243" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="E243" t="s">
         <v>227</v>
@@ -73484,7 +73478,7 @@
         <v>1202</v>
       </c>
       <c r="H243" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="J243" t="s">
         <v>261</v>
@@ -73745,7 +73739,7 @@
         <v>8</v>
       </c>
       <c r="D246" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="E246" t="s">
         <v>227</v>
@@ -73923,7 +73917,7 @@
         <v>3</v>
       </c>
       <c r="D248" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="E248" t="s">
         <v>242</v>
@@ -73997,7 +73991,7 @@
         <v>5</v>
       </c>
       <c r="D249" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="E249" t="s">
         <v>242</v>
@@ -74077,7 +74071,7 @@
         <v>8</v>
       </c>
       <c r="D250" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="E250" t="s">
         <v>242</v>
@@ -74243,7 +74237,7 @@
         <v>8</v>
       </c>
       <c r="D252" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="E252" t="s">
         <v>242</v>
@@ -74424,7 +74418,7 @@
         <v>6</v>
       </c>
       <c r="D254" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="E254" t="s">
         <v>242</v>
@@ -74445,7 +74439,7 @@
         <v>261</v>
       </c>
       <c r="K254" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="L254">
         <v>66.8</v>
@@ -74504,7 +74498,7 @@
         <v>13</v>
       </c>
       <c r="D255" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="E255" t="s">
         <v>242</v>
@@ -74596,7 +74590,7 @@
         <v>6</v>
       </c>
       <c r="D256" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="E256" t="s">
         <v>242</v>
@@ -75115,7 +75109,7 @@
         <v>8</v>
       </c>
       <c r="D262" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="E262" t="s">
         <v>229</v>
@@ -75207,7 +75201,7 @@
         <v>10</v>
       </c>
       <c r="D263" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="E263" t="s">
         <v>229</v>
@@ -75299,7 +75293,7 @@
         <v>5</v>
       </c>
       <c r="D264" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="E264" t="s">
         <v>229</v>
@@ -75388,7 +75382,7 @@
         <v>6</v>
       </c>
       <c r="D265" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="E265" t="s">
         <v>229</v>
@@ -75750,7 +75744,7 @@
         <v>4</v>
       </c>
       <c r="D269" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="E269" t="s">
         <v>229</v>
@@ -75842,7 +75836,7 @@
         <v>4</v>
       </c>
       <c r="D270" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="E270" t="s">
         <v>229</v>
@@ -75931,7 +75925,7 @@
         <v>8</v>
       </c>
       <c r="D271" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="E271" t="s">
         <v>229</v>
@@ -76020,7 +76014,7 @@
         <v>7</v>
       </c>
       <c r="D272" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="E272" t="s">
         <v>229</v>
@@ -76112,7 +76106,7 @@
         <v>13</v>
       </c>
       <c r="D273" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="E273" t="s">
         <v>229</v>

--- a/Santa Cruz V2/listas/listas_2027.xlsx
+++ b/Santa Cruz V2/listas/listas_2027.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8952" uniqueCount="1293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8952" uniqueCount="1292">
   <si>
     <t>posicao</t>
   </si>
@@ -1312,9 +1312,6 @@
     <t>M. Bergia</t>
   </si>
   <si>
-    <t>D. Ospina</t>
-  </si>
-  <si>
     <t>C. Martínez</t>
   </si>
   <si>
@@ -1330,6 +1327,9 @@
     <t>G. Olveira</t>
   </si>
   <si>
+    <t>W. Cuesta</t>
+  </si>
+  <si>
     <t>J. Alarcón</t>
   </si>
   <si>
@@ -1705,93 +1705,96 @@
     <t>Atlético Rafaela</t>
   </si>
   <si>
+    <t>Real Potosí</t>
+  </si>
+  <si>
+    <t>Atletico FC</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
+    <t>Olimpia</t>
+  </si>
+  <si>
+    <t>Internacional Palmira</t>
+  </si>
+  <si>
+    <t>Sport Boys</t>
+  </si>
+  <si>
+    <t>Medellín</t>
+  </si>
+  <si>
+    <t>Real Cartagena</t>
+  </si>
+  <si>
+    <t>Atlético Vinotinto</t>
+  </si>
+  <si>
+    <t>Everton</t>
+  </si>
+  <si>
+    <t>Club Libertad</t>
+  </si>
+  <si>
+    <t>Cusco</t>
+  </si>
+  <si>
+    <t>Colón</t>
+  </si>
+  <si>
+    <t>Universitario de Vinto</t>
+  </si>
+  <si>
+    <t>Godoy Cruz</t>
+  </si>
+  <si>
+    <t>Independiente del Valle</t>
+  </si>
+  <si>
+    <t>UCV</t>
+  </si>
+  <si>
+    <t>Argentinos Juniors</t>
+  </si>
+  <si>
+    <t>Guabirá</t>
+  </si>
+  <si>
+    <t>Alianza Lima</t>
+  </si>
+  <si>
+    <t>Deportivo Táchira</t>
+  </si>
+  <si>
+    <t>9 de Octubre</t>
+  </si>
+  <si>
+    <t>Atlético Tucumán</t>
+  </si>
+  <si>
+    <t>Los Chankas</t>
+  </si>
+  <si>
+    <t>Deportivo Recoleta</t>
+  </si>
+  <si>
+    <t>Aucas</t>
+  </si>
+  <si>
+    <t>Universidad Católica</t>
+  </si>
+  <si>
+    <t>Independiente Juniors</t>
+  </si>
+  <si>
     <t>Atlético Nacional</t>
   </si>
   <si>
-    <t>Real Potosí</t>
-  </si>
-  <si>
-    <t>Atletico FC</t>
-  </si>
-  <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>Belgrano</t>
-  </si>
-  <si>
-    <t>Olimpia</t>
-  </si>
-  <si>
-    <t>Sport Boys</t>
-  </si>
-  <si>
-    <t>Medellín</t>
-  </si>
-  <si>
-    <t>Real Cartagena</t>
-  </si>
-  <si>
-    <t>Atlético Vinotinto</t>
-  </si>
-  <si>
-    <t>Everton</t>
-  </si>
-  <si>
-    <t>Club Libertad</t>
-  </si>
-  <si>
-    <t>Cusco</t>
-  </si>
-  <si>
-    <t>Colón</t>
-  </si>
-  <si>
-    <t>Universitario de Vinto</t>
-  </si>
-  <si>
-    <t>Godoy Cruz</t>
-  </si>
-  <si>
-    <t>Independiente del Valle</t>
-  </si>
-  <si>
-    <t>UCV</t>
-  </si>
-  <si>
-    <t>Argentinos Juniors</t>
-  </si>
-  <si>
-    <t>Guabirá</t>
-  </si>
-  <si>
-    <t>Alianza Lima</t>
-  </si>
-  <si>
-    <t>Deportivo Táchira</t>
-  </si>
-  <si>
-    <t>9 de Octubre</t>
-  </si>
-  <si>
-    <t>Atlético Tucumán</t>
-  </si>
-  <si>
-    <t>Los Chankas</t>
-  </si>
-  <si>
-    <t>Deportivo Recoleta</t>
-  </si>
-  <si>
-    <t>Aucas</t>
-  </si>
-  <si>
-    <t>Universidad Católica</t>
-  </si>
-  <si>
-    <t>Independiente Juniors</t>
-  </si>
-  <si>
     <t>Leones</t>
   </si>
   <si>
@@ -1963,9 +1966,6 @@
     <t>Panama</t>
   </si>
   <si>
-    <t>Colombia, France</t>
-  </si>
-  <si>
     <t>Spain, Ecuador</t>
   </si>
   <si>
@@ -2128,9 +2128,6 @@
     <t>Arthur</t>
   </si>
   <si>
-    <t>Rodinei</t>
-  </si>
-  <si>
     <t>O. Sonne</t>
   </si>
   <si>
@@ -2164,6 +2161,9 @@
     <t>Pastor</t>
   </si>
   <si>
+    <t>Gustavo Ferrareis</t>
+  </si>
+  <si>
     <t>Fabiano</t>
   </si>
   <si>
@@ -2512,9 +2512,6 @@
     <t>Beroe</t>
   </si>
   <si>
-    <t>Olympiacos Piraeus</t>
-  </si>
-  <si>
     <t>Sparta Praha</t>
   </si>
   <si>
@@ -2545,6 +2542,9 @@
     <t>CSKA Sofia</t>
   </si>
   <si>
+    <t>Atlas</t>
+  </si>
+  <si>
     <t>Aris</t>
   </si>
   <si>
@@ -2564,9 +2564,6 @@
   </si>
   <si>
     <t>Dibba Al Fujairah</t>
-  </si>
-  <si>
-    <t>Atlas</t>
   </si>
   <si>
     <t>Tigres UANL</t>
@@ -31083,7 +31080,7 @@
         <v>413</v>
       </c>
       <c r="B8" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C8" t="s">
         <v>3</v>
@@ -31095,37 +31092,34 @@
         <v>561</v>
       </c>
       <c r="F8">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G8">
-        <v>1177</v>
-      </c>
-      <c r="H8" t="s">
-        <v>253</v>
+        <v>927</v>
       </c>
       <c r="I8">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>403</v>
+        <v>277</v>
       </c>
       <c r="K8" t="s">
-        <v>647</v>
+        <v>277</v>
       </c>
       <c r="L8">
-        <v>75</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M8">
-        <v>53.5</v>
+        <v>56.2</v>
       </c>
       <c r="N8">
-        <v>85.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="O8">
         <v>1</v>
       </c>
       <c r="P8">
-        <v>69.7</v>
+        <v>68.8</v>
       </c>
       <c r="Q8" t="b">
         <v>1</v>
@@ -31137,13 +31131,13 @@
         <v>5</v>
       </c>
       <c r="U8">
-        <v>56.7</v>
+        <v>44.6</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
       <c r="W8">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="X8">
         <v>0.1</v>
@@ -31172,7 +31166,7 @@
         <v>413</v>
       </c>
       <c r="B9" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
@@ -31184,19 +31178,22 @@
         <v>562</v>
       </c>
       <c r="F9">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G9">
-        <v>927</v>
+        <v>1712</v>
+      </c>
+      <c r="H9" t="s">
+        <v>253</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="J9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L9">
         <v>84.09999999999999</v>
@@ -31208,7 +31205,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="O9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P9">
         <v>68.8</v>
@@ -31223,16 +31220,16 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>44.6</v>
+        <v>54.1</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9">
+        <v>0.6</v>
+      </c>
+      <c r="X9">
         <v>0.2</v>
-      </c>
-      <c r="X9">
-        <v>0.1</v>
       </c>
       <c r="Y9" t="b">
         <v>1</v>
@@ -31258,7 +31255,7 @@
         <v>413</v>
       </c>
       <c r="B10" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C10" t="s">
         <v>3</v>
@@ -31270,37 +31267,37 @@
         <v>563</v>
       </c>
       <c r="F10">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G10">
-        <v>1712</v>
+        <v>2128</v>
       </c>
       <c r="H10" t="s">
         <v>253</v>
       </c>
       <c r="I10">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="J10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L10">
-        <v>84.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="M10">
-        <v>56.2</v>
+        <v>53.9</v>
       </c>
       <c r="N10">
-        <v>81.40000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="O10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P10">
-        <v>68.8</v>
+        <v>68.3</v>
       </c>
       <c r="Q10" t="b">
         <v>1</v>
@@ -31312,16 +31309,16 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>54.1</v>
+        <v>52.5</v>
       </c>
       <c r="V10">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="X10">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="Y10" t="b">
         <v>1</v>
@@ -31347,7 +31344,7 @@
         <v>413</v>
       </c>
       <c r="B11" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C11" t="s">
         <v>3</v>
@@ -31359,37 +31356,37 @@
         <v>564</v>
       </c>
       <c r="F11">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G11">
-        <v>2128</v>
+        <v>2387</v>
       </c>
       <c r="H11" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="I11">
-        <v>25000</v>
+        <v>800000</v>
       </c>
       <c r="J11" t="s">
-        <v>277</v>
+        <v>402</v>
       </c>
       <c r="K11" t="s">
-        <v>277</v>
+        <v>402</v>
       </c>
       <c r="L11">
-        <v>76.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="M11">
-        <v>53.9</v>
+        <v>54.1</v>
       </c>
       <c r="N11">
-        <v>82.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="O11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P11">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="Q11" t="b">
         <v>1</v>
@@ -31401,16 +31398,16 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>52.5</v>
+        <v>50.3</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11">
         <v>0.4</v>
       </c>
       <c r="X11">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="Y11" t="b">
         <v>1</v>
@@ -31422,7 +31419,7 @@
         <v>284</v>
       </c>
       <c r="AB11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="b">
         <v>0</v>
@@ -31436,7 +31433,7 @@
         <v>413</v>
       </c>
       <c r="B12" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C12" t="s">
         <v>3</v>
@@ -31448,13 +31445,13 @@
         <v>565</v>
       </c>
       <c r="F12">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G12">
-        <v>2387</v>
+        <v>2203</v>
       </c>
       <c r="H12" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="I12">
         <v>800000</v>
@@ -31466,13 +31463,13 @@
         <v>402</v>
       </c>
       <c r="L12">
-        <v>77.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="M12">
-        <v>54.1</v>
+        <v>51</v>
       </c>
       <c r="N12">
-        <v>82.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="O12">
         <v>1</v>
@@ -31490,16 +31487,16 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>50.3</v>
+        <v>55.7</v>
       </c>
       <c r="V12">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="X12">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Y12" t="b">
         <v>1</v>
@@ -31511,7 +31508,7 @@
         <v>284</v>
       </c>
       <c r="AB12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="b">
         <v>0</v>
@@ -31525,7 +31522,7 @@
         <v>413</v>
       </c>
       <c r="B13" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C13" t="s">
         <v>3</v>
@@ -31540,34 +31537,34 @@
         <v>33</v>
       </c>
       <c r="G13">
-        <v>2203</v>
+        <v>1934</v>
       </c>
       <c r="H13" t="s">
         <v>253</v>
       </c>
       <c r="I13">
-        <v>800000</v>
+        <v>150000</v>
       </c>
       <c r="J13" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K13" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L13">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="M13">
-        <v>51</v>
+        <v>53.5</v>
       </c>
       <c r="N13">
-        <v>85.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="O13">
         <v>1</v>
       </c>
       <c r="P13">
-        <v>68.2</v>
+        <v>67.7</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
@@ -31579,16 +31576,16 @@
         <v>5</v>
       </c>
       <c r="U13">
-        <v>55.7</v>
+        <v>48.9</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="X13">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="Y13" t="b">
         <v>1</v>
@@ -32697,7 +32694,7 @@
         <v>448</v>
       </c>
       <c r="E26" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F26">
         <v>24</v>
@@ -33780,7 +33777,7 @@
         <v>460</v>
       </c>
       <c r="E38" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F38">
         <v>25</v>
@@ -34068,7 +34065,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="K41" t="s">
         <v>648</v>
@@ -34142,7 +34139,7 @@
         <v>464</v>
       </c>
       <c r="E42" t="s">
-        <v>561</v>
+        <v>590</v>
       </c>
       <c r="F42">
         <v>25</v>
@@ -34231,7 +34228,7 @@
         <v>465</v>
       </c>
       <c r="E43" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F43">
         <v>22</v>
@@ -34320,7 +34317,7 @@
         <v>466</v>
       </c>
       <c r="E44" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F44">
         <v>33</v>
@@ -34412,7 +34409,7 @@
         <v>467</v>
       </c>
       <c r="E45" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F45">
         <v>33</v>
@@ -34498,7 +34495,7 @@
         <v>468</v>
       </c>
       <c r="E46" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F46">
         <v>29</v>
@@ -34590,7 +34587,7 @@
         <v>469</v>
       </c>
       <c r="E47" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F47">
         <v>20</v>
@@ -34682,7 +34679,7 @@
         <v>470</v>
       </c>
       <c r="E48" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F48">
         <v>31</v>
@@ -34774,7 +34771,7 @@
         <v>471</v>
       </c>
       <c r="E49" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F49">
         <v>25</v>
@@ -34866,7 +34863,7 @@
         <v>472</v>
       </c>
       <c r="E50" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F50">
         <v>29</v>
@@ -34958,7 +34955,7 @@
         <v>473</v>
       </c>
       <c r="E51" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F51">
         <v>22</v>
@@ -35050,7 +35047,7 @@
         <v>474</v>
       </c>
       <c r="E52" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F52">
         <v>27</v>
@@ -35139,7 +35136,7 @@
         <v>475</v>
       </c>
       <c r="E53" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F53">
         <v>25</v>
@@ -35691,7 +35688,7 @@
         <v>481</v>
       </c>
       <c r="E59" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F59">
         <v>26</v>
@@ -35777,7 +35774,7 @@
         <v>482</v>
       </c>
       <c r="E60" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F60">
         <v>25</v>
@@ -35866,7 +35863,7 @@
         <v>483</v>
       </c>
       <c r="E61" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F61">
         <v>28</v>
@@ -35952,7 +35949,7 @@
         <v>484</v>
       </c>
       <c r="E62" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F62">
         <v>34</v>
@@ -36041,7 +36038,7 @@
         <v>485</v>
       </c>
       <c r="E63" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F63">
         <v>28</v>
@@ -36133,7 +36130,7 @@
         <v>486</v>
       </c>
       <c r="E64" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F64">
         <v>22</v>
@@ -36219,7 +36216,7 @@
         <v>487</v>
       </c>
       <c r="E65" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F65">
         <v>22</v>
@@ -36308,7 +36305,7 @@
         <v>488</v>
       </c>
       <c r="E66" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F66">
         <v>28</v>
@@ -36480,7 +36477,7 @@
         <v>490</v>
       </c>
       <c r="E68" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F68">
         <v>31</v>
@@ -36572,7 +36569,7 @@
         <v>491</v>
       </c>
       <c r="E69" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F69">
         <v>35</v>
@@ -36661,7 +36658,7 @@
         <v>492</v>
       </c>
       <c r="E70" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F70">
         <v>32</v>
@@ -36753,7 +36750,7 @@
         <v>493</v>
       </c>
       <c r="E71" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F71">
         <v>31</v>
@@ -36845,7 +36842,7 @@
         <v>494</v>
       </c>
       <c r="E72" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F72">
         <v>29</v>
@@ -36937,7 +36934,7 @@
         <v>495</v>
       </c>
       <c r="E73" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F73">
         <v>32</v>
@@ -37026,7 +37023,7 @@
         <v>496</v>
       </c>
       <c r="E74" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F74">
         <v>26</v>
@@ -37207,7 +37204,7 @@
         <v>498</v>
       </c>
       <c r="E76" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F76">
         <v>27</v>
@@ -37299,7 +37296,7 @@
         <v>499</v>
       </c>
       <c r="E77" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F77">
         <v>33</v>
@@ -37391,7 +37388,7 @@
         <v>500</v>
       </c>
       <c r="E78" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F78">
         <v>26</v>
@@ -37569,7 +37566,7 @@
         <v>502</v>
       </c>
       <c r="E80" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F80">
         <v>30</v>
@@ -37658,7 +37655,7 @@
         <v>501</v>
       </c>
       <c r="E81" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F81">
         <v>25</v>
@@ -37750,7 +37747,7 @@
         <v>503</v>
       </c>
       <c r="E82" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F82">
         <v>21</v>
@@ -37836,7 +37833,7 @@
         <v>504</v>
       </c>
       <c r="E83" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F83">
         <v>26</v>
@@ -37928,7 +37925,7 @@
         <v>505</v>
       </c>
       <c r="E84" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F84">
         <v>25</v>
@@ -38204,7 +38201,7 @@
         <v>508</v>
       </c>
       <c r="E87" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F87">
         <v>21</v>
@@ -38379,7 +38376,7 @@
         <v>510</v>
       </c>
       <c r="E89" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F89">
         <v>27</v>
@@ -38560,7 +38557,7 @@
         <v>512</v>
       </c>
       <c r="E91" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F91">
         <v>35</v>
@@ -38652,7 +38649,7 @@
         <v>513</v>
       </c>
       <c r="E92" t="s">
-        <v>561</v>
+        <v>590</v>
       </c>
       <c r="F92">
         <v>33</v>
@@ -38744,7 +38741,7 @@
         <v>514</v>
       </c>
       <c r="E93" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F93">
         <v>35</v>
@@ -38833,7 +38830,7 @@
         <v>515</v>
       </c>
       <c r="E94" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F94">
         <v>26</v>
@@ -39017,7 +39014,7 @@
         <v>517</v>
       </c>
       <c r="E96" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F96">
         <v>27</v>
@@ -39106,7 +39103,7 @@
         <v>518</v>
       </c>
       <c r="E97" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F97">
         <v>27</v>
@@ -39195,7 +39192,7 @@
         <v>519</v>
       </c>
       <c r="E98" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F98">
         <v>30</v>
@@ -39373,7 +39370,7 @@
         <v>521</v>
       </c>
       <c r="E100" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F100">
         <v>25</v>
@@ -39465,7 +39462,7 @@
         <v>522</v>
       </c>
       <c r="E101" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F101">
         <v>24</v>
@@ -39557,7 +39554,7 @@
         <v>523</v>
       </c>
       <c r="E102" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F102">
         <v>18</v>
@@ -39916,7 +39913,7 @@
         <v>527</v>
       </c>
       <c r="E106" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F106">
         <v>32</v>
@@ -39931,10 +39928,10 @@
         <v>400000</v>
       </c>
       <c r="J106" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="K106" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L106">
         <v>88.2</v>
@@ -40097,7 +40094,7 @@
         <v>529</v>
       </c>
       <c r="E108" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F108">
         <v>30</v>
@@ -40189,7 +40186,7 @@
         <v>530</v>
       </c>
       <c r="E109" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F109">
         <v>31</v>
@@ -40281,7 +40278,7 @@
         <v>531</v>
       </c>
       <c r="E110" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F110">
         <v>28</v>
@@ -40370,7 +40367,7 @@
         <v>532</v>
       </c>
       <c r="E111" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F111">
         <v>20</v>
@@ -40382,10 +40379,10 @@
         <v>0</v>
       </c>
       <c r="J111" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="K111" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L111">
         <v>67.09999999999999</v>
@@ -40456,7 +40453,7 @@
         <v>533</v>
       </c>
       <c r="E112" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F112">
         <v>29</v>
@@ -40545,7 +40542,7 @@
         <v>534</v>
       </c>
       <c r="E113" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F113">
         <v>27</v>
@@ -40720,7 +40717,7 @@
         <v>536</v>
       </c>
       <c r="E115" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F115">
         <v>25</v>
@@ -40901,7 +40898,7 @@
         <v>538</v>
       </c>
       <c r="E117" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F117">
         <v>18</v>
@@ -40987,7 +40984,7 @@
         <v>539</v>
       </c>
       <c r="E118" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F118">
         <v>23</v>
@@ -41073,7 +41070,7 @@
         <v>540</v>
       </c>
       <c r="E119" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F119">
         <v>26</v>
@@ -41165,7 +41162,7 @@
         <v>541</v>
       </c>
       <c r="E120" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F120">
         <v>19</v>
@@ -41257,7 +41254,7 @@
         <v>542</v>
       </c>
       <c r="E121" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F121">
         <v>31</v>
@@ -41441,7 +41438,7 @@
         <v>544</v>
       </c>
       <c r="E123" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F123">
         <v>22</v>
@@ -41533,7 +41530,7 @@
         <v>545</v>
       </c>
       <c r="E124" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F124">
         <v>27</v>
@@ -41622,7 +41619,7 @@
         <v>546</v>
       </c>
       <c r="E125" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F125">
         <v>30</v>
@@ -41806,7 +41803,7 @@
         <v>548</v>
       </c>
       <c r="E127" t="s">
-        <v>561</v>
+        <v>590</v>
       </c>
       <c r="F127">
         <v>30</v>
@@ -41898,7 +41895,7 @@
         <v>549</v>
       </c>
       <c r="E128" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F128">
         <v>30</v>
@@ -41990,7 +41987,7 @@
         <v>550</v>
       </c>
       <c r="E129" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F129">
         <v>30</v>
@@ -42263,7 +42260,7 @@
         <v>553</v>
       </c>
       <c r="E132" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F132">
         <v>32</v>
@@ -42355,7 +42352,7 @@
         <v>554</v>
       </c>
       <c r="E133" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F133">
         <v>33</v>
@@ -42641,7 +42638,7 @@
         <v>3085</v>
       </c>
       <c r="H3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I3">
         <v>200000</v>
@@ -42739,7 +42736,7 @@
         <v>403</v>
       </c>
       <c r="K4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="L4">
         <v>72</v>
@@ -42819,7 +42816,7 @@
         <v>1198</v>
       </c>
       <c r="H5" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I5">
         <v>300000</v>
@@ -43270,10 +43267,10 @@
         <v>300000</v>
       </c>
       <c r="J10" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="K10" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="L10">
         <v>61.2</v>
@@ -43599,7 +43596,7 @@
         <v>655</v>
       </c>
       <c r="B14" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
@@ -43611,79 +43608,76 @@
         <v>830</v>
       </c>
       <c r="F14">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G14">
-        <v>1866</v>
+        <v>1162</v>
       </c>
       <c r="H14" t="s">
-        <v>270</v>
+        <v>399</v>
       </c>
       <c r="I14">
-        <v>1500000</v>
+        <v>2000000</v>
       </c>
       <c r="J14" t="s">
-        <v>272</v>
+        <v>929</v>
       </c>
       <c r="K14" t="s">
-        <v>272</v>
+        <v>936</v>
       </c>
       <c r="L14">
-        <v>82.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="M14">
-        <v>55.8</v>
+        <v>51.1</v>
       </c>
       <c r="N14">
-        <v>84.3</v>
+        <v>61.6</v>
       </c>
       <c r="O14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P14">
-        <v>70.09999999999999</v>
+        <v>56.4</v>
       </c>
       <c r="Q14" t="b">
         <v>1</v>
       </c>
       <c r="R14">
         <v>0</v>
-      </c>
-      <c r="S14">
-        <v>33.2</v>
       </c>
       <c r="T14">
         <v>6</v>
       </c>
       <c r="U14">
-        <v>57.5</v>
+        <v>66.8</v>
       </c>
       <c r="V14">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="W14">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="X14">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="Y14" t="b">
         <v>1</v>
       </c>
       <c r="Z14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="s">
         <v>284</v>
       </c>
       <c r="AB14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="b">
         <v>0</v>
       </c>
       <c r="AD14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15" spans="1:30">
@@ -43691,7 +43685,7 @@
         <v>655</v>
       </c>
       <c r="B15" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
@@ -43706,55 +43700,58 @@
         <v>25</v>
       </c>
       <c r="G15">
-        <v>1162</v>
+        <v>2253</v>
       </c>
       <c r="H15" t="s">
-        <v>399</v>
+        <v>257</v>
       </c>
       <c r="I15">
-        <v>2000000</v>
+        <v>800000</v>
       </c>
       <c r="J15" t="s">
-        <v>930</v>
+        <v>277</v>
       </c>
       <c r="K15" t="s">
         <v>937</v>
       </c>
       <c r="L15">
-        <v>66.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="M15">
-        <v>51.1</v>
+        <v>55.1</v>
       </c>
       <c r="N15">
-        <v>61.6</v>
+        <v>56.9</v>
       </c>
       <c r="O15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P15">
-        <v>56.4</v>
+        <v>56</v>
       </c>
       <c r="Q15" t="b">
         <v>1</v>
       </c>
       <c r="R15">
         <v>0</v>
+      </c>
+      <c r="S15">
+        <v>37.6</v>
       </c>
       <c r="T15">
         <v>6</v>
       </c>
       <c r="U15">
-        <v>66.8</v>
+        <v>56.6</v>
       </c>
       <c r="V15">
-        <v>6.9</v>
+        <v>8.4</v>
       </c>
       <c r="W15">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="X15">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="Y15" t="b">
         <v>1</v>
@@ -43780,7 +43777,7 @@
         <v>655</v>
       </c>
       <c r="B16" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
@@ -43789,64 +43786,61 @@
         <v>704</v>
       </c>
       <c r="E16" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="F16">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G16">
-        <v>2253</v>
+        <v>1062</v>
       </c>
       <c r="H16" t="s">
         <v>257</v>
       </c>
       <c r="I16">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K16" t="s">
-        <v>938</v>
+        <v>276</v>
       </c>
       <c r="L16">
-        <v>80.2</v>
+        <v>72.7</v>
       </c>
       <c r="M16">
-        <v>55.1</v>
+        <v>52.8</v>
       </c>
       <c r="N16">
-        <v>56.9</v>
+        <v>57.5</v>
       </c>
       <c r="O16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P16">
-        <v>56</v>
+        <v>55.2</v>
       </c>
       <c r="Q16" t="b">
         <v>1</v>
       </c>
       <c r="R16">
         <v>0</v>
-      </c>
-      <c r="S16">
-        <v>37.6</v>
       </c>
       <c r="T16">
         <v>6</v>
       </c>
       <c r="U16">
-        <v>56.6</v>
+        <v>66.8</v>
       </c>
       <c r="V16">
-        <v>8.4</v>
+        <v>5.9</v>
       </c>
       <c r="W16">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="X16">
-        <v>3.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y16" t="b">
         <v>1</v>
@@ -43864,7 +43858,7 @@
         <v>0</v>
       </c>
       <c r="AD16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:30">
@@ -43872,7 +43866,7 @@
         <v>655</v>
       </c>
       <c r="B17" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C17" t="s">
         <v>4</v>
@@ -43881,40 +43875,37 @@
         <v>705</v>
       </c>
       <c r="E17" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="F17">
         <v>28</v>
       </c>
       <c r="G17">
-        <v>1062</v>
-      </c>
-      <c r="H17" t="s">
-        <v>257</v>
+        <v>1043</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="J17" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="K17" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="L17">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="M17">
-        <v>52.8</v>
+        <v>52.6</v>
       </c>
       <c r="N17">
-        <v>57.5</v>
+        <v>56.6</v>
       </c>
       <c r="O17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P17">
-        <v>55.2</v>
+        <v>54.6</v>
       </c>
       <c r="Q17" t="b">
         <v>1</v>
@@ -43926,28 +43917,28 @@
         <v>6</v>
       </c>
       <c r="U17">
-        <v>66.8</v>
+        <v>56.4</v>
       </c>
       <c r="V17">
         <v>5.9</v>
       </c>
       <c r="W17">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="X17">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="Y17" t="b">
         <v>1</v>
       </c>
       <c r="Z17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="s">
-        <v>284</v>
+        <v>950</v>
       </c>
       <c r="AB17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="b">
         <v>0</v>
@@ -43961,7 +43952,7 @@
         <v>655</v>
       </c>
       <c r="B18" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C18" t="s">
         <v>4</v>
@@ -43973,34 +43964,37 @@
         <v>833</v>
       </c>
       <c r="F18">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G18">
-        <v>1043</v>
+        <v>3687</v>
+      </c>
+      <c r="H18" t="s">
+        <v>270</v>
       </c>
       <c r="I18">
-        <v>1200000</v>
+        <v>800000</v>
       </c>
       <c r="J18" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="K18" t="s">
-        <v>272</v>
+        <v>410</v>
       </c>
       <c r="L18">
-        <v>71.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="M18">
-        <v>52.6</v>
+        <v>51.3</v>
       </c>
       <c r="N18">
-        <v>56.6</v>
+        <v>55.8</v>
       </c>
       <c r="O18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P18">
-        <v>54.6</v>
+        <v>53.6</v>
       </c>
       <c r="Q18" t="b">
         <v>1</v>
@@ -44012,25 +44006,25 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>56.4</v>
+        <v>46.7</v>
       </c>
       <c r="V18">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="W18">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="X18">
-        <v>4.2</v>
+        <v>6.3</v>
       </c>
       <c r="Y18" t="b">
         <v>1</v>
       </c>
       <c r="Z18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA18" t="s">
-        <v>951</v>
+        <v>284</v>
       </c>
       <c r="AB18" t="b">
         <v>1</v>
@@ -44047,7 +44041,7 @@
         <v>655</v>
       </c>
       <c r="B19" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C19" t="s">
         <v>4</v>
@@ -44059,58 +44053,61 @@
         <v>834</v>
       </c>
       <c r="F19">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G19">
-        <v>3687</v>
+        <v>2663</v>
       </c>
       <c r="H19" t="s">
         <v>270</v>
       </c>
       <c r="I19">
-        <v>800000</v>
+        <v>500000</v>
       </c>
       <c r="J19" t="s">
-        <v>277</v>
+        <v>403</v>
       </c>
       <c r="K19" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="L19">
-        <v>67.7</v>
+        <v>62</v>
       </c>
       <c r="M19">
-        <v>51.3</v>
+        <v>49.6</v>
       </c>
       <c r="N19">
-        <v>55.8</v>
+        <v>57.2</v>
       </c>
       <c r="O19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P19">
-        <v>53.6</v>
+        <v>53.4</v>
       </c>
       <c r="Q19" t="b">
         <v>1</v>
       </c>
       <c r="R19">
         <v>0</v>
+      </c>
+      <c r="S19">
+        <v>42.5</v>
       </c>
       <c r="T19">
         <v>6</v>
       </c>
       <c r="U19">
-        <v>46.7</v>
+        <v>46.2</v>
       </c>
       <c r="V19">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="W19">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="X19">
-        <v>6.3</v>
+        <v>11</v>
       </c>
       <c r="Y19" t="b">
         <v>1</v>
@@ -44136,7 +44133,7 @@
         <v>655</v>
       </c>
       <c r="B20" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="C20" t="s">
         <v>4</v>
@@ -44148,37 +44145,37 @@
         <v>835</v>
       </c>
       <c r="F20">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G20">
-        <v>2663</v>
+        <v>1529</v>
       </c>
       <c r="H20" t="s">
         <v>270</v>
       </c>
       <c r="I20">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>403</v>
+        <v>272</v>
       </c>
       <c r="K20" t="s">
-        <v>403</v>
+        <v>272</v>
       </c>
       <c r="L20">
-        <v>62</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M20">
-        <v>49.6</v>
+        <v>53.7</v>
       </c>
       <c r="N20">
-        <v>57.2</v>
+        <v>51.4</v>
       </c>
       <c r="O20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>53.4</v>
+        <v>52.5</v>
       </c>
       <c r="Q20" t="b">
         <v>1</v>
@@ -44187,28 +44184,28 @@
         <v>0</v>
       </c>
       <c r="S20">
-        <v>42.5</v>
+        <v>43.2</v>
       </c>
       <c r="T20">
         <v>6</v>
       </c>
       <c r="U20">
-        <v>46.2</v>
+        <v>54.1</v>
       </c>
       <c r="V20">
-        <v>4.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W20">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="X20">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Y20" t="b">
         <v>1</v>
       </c>
       <c r="Z20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="s">
         <v>284</v>
@@ -44220,7 +44217,7 @@
         <v>0</v>
       </c>
       <c r="AD20" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="21" spans="1:30">
@@ -44228,7 +44225,7 @@
         <v>655</v>
       </c>
       <c r="B21" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C21" t="s">
         <v>4</v>
@@ -44240,37 +44237,37 @@
         <v>836</v>
       </c>
       <c r="F21">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G21">
-        <v>1529</v>
+        <v>1202</v>
       </c>
       <c r="H21" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="J21" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K21" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="L21">
-        <v>75.59999999999999</v>
+        <v>60.8</v>
       </c>
       <c r="M21">
-        <v>53.7</v>
+        <v>49.2</v>
       </c>
       <c r="N21">
-        <v>51.4</v>
+        <v>50.9</v>
       </c>
       <c r="O21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P21">
-        <v>52.5</v>
+        <v>50.1</v>
       </c>
       <c r="Q21" t="b">
         <v>1</v>
@@ -44279,34 +44276,34 @@
         <v>0</v>
       </c>
       <c r="S21">
-        <v>43.2</v>
+        <v>54.8</v>
       </c>
       <c r="T21">
         <v>6</v>
       </c>
       <c r="U21">
-        <v>54.1</v>
+        <v>46.5</v>
       </c>
       <c r="V21">
-        <v>9.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="W21">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="X21">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
       <c r="Y21" t="b">
         <v>1</v>
       </c>
       <c r="Z21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA21" t="s">
         <v>284</v>
       </c>
       <c r="AB21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="b">
         <v>0</v>
@@ -44335,34 +44332,34 @@
         <v>22</v>
       </c>
       <c r="G22">
-        <v>1202</v>
+        <v>1499</v>
       </c>
       <c r="H22" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="I22">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>275</v>
+        <v>403</v>
       </c>
       <c r="K22" t="s">
-        <v>275</v>
+        <v>403</v>
       </c>
       <c r="L22">
-        <v>60.8</v>
+        <v>66.8</v>
       </c>
       <c r="M22">
-        <v>49.2</v>
+        <v>51</v>
       </c>
       <c r="N22">
-        <v>50.9</v>
+        <v>46.2</v>
       </c>
       <c r="O22">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>50.1</v>
+        <v>48.6</v>
       </c>
       <c r="Q22" t="b">
         <v>1</v>
@@ -44371,22 +44368,22 @@
         <v>0</v>
       </c>
       <c r="S22">
-        <v>54.8</v>
+        <v>48.6</v>
       </c>
       <c r="T22">
         <v>6</v>
       </c>
       <c r="U22">
-        <v>46.5</v>
+        <v>56.4</v>
       </c>
       <c r="V22">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="W22">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="X22">
-        <v>8.1</v>
+        <v>4.7</v>
       </c>
       <c r="Y22" t="b">
         <v>1</v>
@@ -44412,7 +44409,7 @@
         <v>655</v>
       </c>
       <c r="B23" t="s">
-        <v>659</v>
+        <v>669</v>
       </c>
       <c r="C23" t="s">
         <v>4</v>
@@ -44424,61 +44421,58 @@
         <v>838</v>
       </c>
       <c r="F23">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G23">
-        <v>1499</v>
+        <v>3017</v>
       </c>
       <c r="H23" t="s">
-        <v>256</v>
+        <v>397</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="J23" t="s">
-        <v>403</v>
+        <v>277</v>
       </c>
       <c r="K23" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="L23">
-        <v>66.8</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="M23">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="N23">
-        <v>46.2</v>
+        <v>45.9</v>
       </c>
       <c r="O23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="Q23" t="b">
         <v>1</v>
       </c>
       <c r="R23">
         <v>0</v>
-      </c>
-      <c r="S23">
-        <v>48.6</v>
       </c>
       <c r="T23">
         <v>6</v>
       </c>
       <c r="U23">
-        <v>56.4</v>
+        <v>49.9</v>
       </c>
       <c r="V23">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="W23">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="X23">
-        <v>4.7</v>
+        <v>6.5</v>
       </c>
       <c r="Y23" t="b">
         <v>1</v>
@@ -44504,7 +44498,7 @@
         <v>655</v>
       </c>
       <c r="B24" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C24" t="s">
         <v>4</v>
@@ -44516,37 +44510,37 @@
         <v>839</v>
       </c>
       <c r="F24">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G24">
-        <v>3017</v>
+        <v>2596</v>
       </c>
       <c r="H24" t="s">
         <v>397</v>
       </c>
       <c r="I24">
-        <v>125000</v>
+        <v>1000000</v>
       </c>
       <c r="J24" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="K24" t="s">
-        <v>410</v>
+        <v>272</v>
       </c>
       <c r="L24">
-        <v>66.09999999999999</v>
+        <v>60.7</v>
       </c>
       <c r="M24">
-        <v>50.8</v>
+        <v>49.2</v>
       </c>
       <c r="N24">
-        <v>45.9</v>
+        <v>47.2</v>
       </c>
       <c r="O24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P24">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="Q24" t="b">
         <v>1</v>
@@ -44558,22 +44552,22 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <v>49.9</v>
+        <v>51.5</v>
       </c>
       <c r="V24">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="W24">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="X24">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="Y24" t="b">
         <v>1</v>
       </c>
       <c r="Z24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="s">
         <v>284</v>
@@ -44585,7 +44579,7 @@
         <v>0</v>
       </c>
       <c r="AD24" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:30">
@@ -44593,7 +44587,7 @@
         <v>655</v>
       </c>
       <c r="B25" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="C25" t="s">
         <v>4</v>
@@ -44605,58 +44599,61 @@
         <v>840</v>
       </c>
       <c r="F25">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G25">
-        <v>2596</v>
+        <v>3142</v>
       </c>
       <c r="H25" t="s">
-        <v>397</v>
+        <v>270</v>
       </c>
       <c r="I25">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="J25" t="s">
         <v>272</v>
       </c>
       <c r="K25" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="L25">
-        <v>60.7</v>
+        <v>63.4</v>
       </c>
       <c r="M25">
-        <v>49.2</v>
+        <v>50</v>
       </c>
       <c r="N25">
-        <v>47.2</v>
+        <v>45.7</v>
       </c>
       <c r="O25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>48.2</v>
+        <v>47.9</v>
       </c>
       <c r="Q25" t="b">
         <v>1</v>
       </c>
       <c r="R25">
         <v>0</v>
+      </c>
+      <c r="S25">
+        <v>38.5</v>
       </c>
       <c r="T25">
         <v>6</v>
       </c>
       <c r="U25">
-        <v>51.5</v>
+        <v>45</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="W25">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="X25">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="Y25" t="b">
         <v>1</v>
@@ -44668,7 +44665,7 @@
         <v>284</v>
       </c>
       <c r="AB25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC25" t="b">
         <v>0</v>
@@ -44970,7 +44967,7 @@
         <v>2368</v>
       </c>
       <c r="H29" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I29">
         <v>100000</v>
@@ -44979,7 +44976,7 @@
         <v>277</v>
       </c>
       <c r="K29" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="L29">
         <v>77</v>
@@ -45243,7 +45240,7 @@
         <v>1554</v>
       </c>
       <c r="H32" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I32">
         <v>1000000</v>
@@ -45326,7 +45323,7 @@
         <v>720</v>
       </c>
       <c r="E33" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="F33">
         <v>30</v>
@@ -45418,7 +45415,7 @@
         <v>721</v>
       </c>
       <c r="E34" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F34">
         <v>27</v>
@@ -45481,7 +45478,7 @@
         <v>1</v>
       </c>
       <c r="AA34" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="AB34" t="b">
         <v>0</v>
@@ -45507,7 +45504,7 @@
         <v>722</v>
       </c>
       <c r="E35" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F35">
         <v>27</v>
@@ -45599,7 +45596,7 @@
         <v>723</v>
       </c>
       <c r="E36" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F36">
         <v>31</v>
@@ -45688,7 +45685,7 @@
         <v>724</v>
       </c>
       <c r="E37" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F37">
         <v>28</v>
@@ -45780,7 +45777,7 @@
         <v>725</v>
       </c>
       <c r="E38" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F38">
         <v>31</v>
@@ -45872,7 +45869,7 @@
         <v>726</v>
       </c>
       <c r="E39" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F39">
         <v>26</v>
@@ -45890,7 +45887,7 @@
         <v>275</v>
       </c>
       <c r="K39" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="L39">
         <v>60</v>
@@ -45961,7 +45958,7 @@
         <v>727</v>
       </c>
       <c r="E40" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F40">
         <v>26</v>
@@ -46053,7 +46050,7 @@
         <v>728</v>
       </c>
       <c r="E41" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="F41">
         <v>26</v>
@@ -46142,7 +46139,7 @@
         <v>729</v>
       </c>
       <c r="E42" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="F42">
         <v>27</v>
@@ -46231,7 +46228,7 @@
         <v>730</v>
       </c>
       <c r="E43" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="F43">
         <v>24</v>
@@ -46240,7 +46237,7 @@
         <v>2172</v>
       </c>
       <c r="H43" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -46320,7 +46317,7 @@
         <v>731</v>
       </c>
       <c r="E44" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="F44">
         <v>22</v>
@@ -46412,7 +46409,7 @@
         <v>732</v>
       </c>
       <c r="E45" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="F45">
         <v>23</v>
@@ -46427,10 +46424,10 @@
         <v>500000</v>
       </c>
       <c r="J45" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="K45" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="L45">
         <v>76.09999999999999</v>
@@ -46504,7 +46501,7 @@
         <v>733</v>
       </c>
       <c r="E46" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="F46">
         <v>33</v>
@@ -46593,7 +46590,7 @@
         <v>734</v>
       </c>
       <c r="E47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="F47">
         <v>26</v>
@@ -46602,7 +46599,7 @@
         <v>1879</v>
       </c>
       <c r="H47" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I47">
         <v>125000</v>
@@ -46685,7 +46682,7 @@
         <v>735</v>
       </c>
       <c r="E48" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="F48">
         <v>25</v>
@@ -46771,7 +46768,7 @@
         <v>736</v>
       </c>
       <c r="E49" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="F49">
         <v>26</v>
@@ -46863,7 +46860,7 @@
         <v>737</v>
       </c>
       <c r="E50" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F50">
         <v>26</v>
@@ -46952,7 +46949,7 @@
         <v>738</v>
       </c>
       <c r="E51" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F51">
         <v>26</v>
@@ -47041,7 +47038,7 @@
         <v>739</v>
       </c>
       <c r="E52" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F52">
         <v>24</v>
@@ -47056,10 +47053,10 @@
         <v>2000000</v>
       </c>
       <c r="J52" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="K52" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="L52">
         <v>73.3</v>
@@ -47133,7 +47130,7 @@
         <v>740</v>
       </c>
       <c r="E53" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F53">
         <v>25</v>
@@ -47151,7 +47148,7 @@
         <v>272</v>
       </c>
       <c r="K53" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="L53">
         <v>71.7</v>
@@ -47225,7 +47222,7 @@
         <v>741</v>
       </c>
       <c r="E54" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F54">
         <v>29</v>
@@ -47234,7 +47231,7 @@
         <v>2529</v>
       </c>
       <c r="H54" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I54">
         <v>300000</v>
@@ -47314,7 +47311,7 @@
         <v>742</v>
       </c>
       <c r="E55" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F55">
         <v>31</v>
@@ -47406,7 +47403,7 @@
         <v>178</v>
       </c>
       <c r="E56" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F56">
         <v>30</v>
@@ -47495,7 +47492,7 @@
         <v>743</v>
       </c>
       <c r="E57" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F57">
         <v>25</v>
@@ -47581,7 +47578,7 @@
         <v>744</v>
       </c>
       <c r="E58" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F58">
         <v>24</v>
@@ -47670,7 +47667,7 @@
         <v>745</v>
       </c>
       <c r="E59" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F59">
         <v>34</v>
@@ -47756,7 +47753,7 @@
         <v>746</v>
       </c>
       <c r="E60" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F60">
         <v>20</v>
@@ -47771,10 +47768,10 @@
         <v>0</v>
       </c>
       <c r="J60" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="K60" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="L60">
         <v>58</v>
@@ -47845,7 +47842,7 @@
         <v>747</v>
       </c>
       <c r="E61" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F61">
         <v>26</v>
@@ -47863,7 +47860,7 @@
         <v>402</v>
       </c>
       <c r="K61" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="L61">
         <v>44.5</v>
@@ -47937,7 +47934,7 @@
         <v>748</v>
       </c>
       <c r="E62" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F62">
         <v>32</v>
@@ -48023,7 +48020,7 @@
         <v>749</v>
       </c>
       <c r="E63" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F63">
         <v>28</v>
@@ -48032,7 +48029,7 @@
         <v>1859</v>
       </c>
       <c r="H63" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -48112,7 +48109,7 @@
         <v>750</v>
       </c>
       <c r="E64" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="F64">
         <v>33</v>
@@ -48121,7 +48118,7 @@
         <v>1476</v>
       </c>
       <c r="H64" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I64">
         <v>2000000</v>
@@ -48204,7 +48201,7 @@
         <v>751</v>
       </c>
       <c r="E65" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="F65">
         <v>22</v>
@@ -48216,10 +48213,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="K65" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="L65">
         <v>44.6</v>
@@ -48293,7 +48290,7 @@
         <v>752</v>
       </c>
       <c r="E66" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F66">
         <v>24</v>
@@ -48302,7 +48299,7 @@
         <v>3292</v>
       </c>
       <c r="H66" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -48385,7 +48382,7 @@
         <v>753</v>
       </c>
       <c r="E67" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F67">
         <v>29</v>
@@ -48474,7 +48471,7 @@
         <v>754</v>
       </c>
       <c r="E68" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F68">
         <v>27</v>
@@ -48563,7 +48560,7 @@
         <v>755</v>
       </c>
       <c r="E69" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F69">
         <v>31</v>
@@ -48655,7 +48652,7 @@
         <v>756</v>
       </c>
       <c r="E70" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F70">
         <v>26</v>
@@ -48744,7 +48741,7 @@
         <v>757</v>
       </c>
       <c r="E71" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="F71">
         <v>31</v>
@@ -48836,7 +48833,7 @@
         <v>758</v>
       </c>
       <c r="E72" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F72">
         <v>25</v>
@@ -48845,7 +48842,7 @@
         <v>2647</v>
       </c>
       <c r="H72" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I72">
         <v>300000</v>
@@ -48928,7 +48925,7 @@
         <v>759</v>
       </c>
       <c r="E73" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F73">
         <v>23</v>
@@ -49020,7 +49017,7 @@
         <v>760</v>
       </c>
       <c r="E74" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="F74">
         <v>32</v>
@@ -49112,7 +49109,7 @@
         <v>761</v>
       </c>
       <c r="E75" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F75">
         <v>29</v>
@@ -49130,7 +49127,7 @@
         <v>277</v>
       </c>
       <c r="K75" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="L75">
         <v>96.40000000000001</v>
@@ -49204,7 +49201,7 @@
         <v>762</v>
       </c>
       <c r="E76" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="F76">
         <v>30</v>
@@ -49213,7 +49210,7 @@
         <v>1437</v>
       </c>
       <c r="H76" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -49293,7 +49290,7 @@
         <v>763</v>
       </c>
       <c r="E77" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F77">
         <v>32</v>
@@ -49379,7 +49376,7 @@
         <v>764</v>
       </c>
       <c r="E78" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="F78">
         <v>24</v>
@@ -49471,7 +49468,7 @@
         <v>765</v>
       </c>
       <c r="E79" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F79">
         <v>31</v>
@@ -49563,7 +49560,7 @@
         <v>766</v>
       </c>
       <c r="E80" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="F80">
         <v>26</v>
@@ -49572,7 +49569,7 @@
         <v>2071</v>
       </c>
       <c r="H80" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I80">
         <v>1800000</v>
@@ -49581,7 +49578,7 @@
         <v>403</v>
       </c>
       <c r="K80" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="L80">
         <v>84.2</v>
@@ -49652,7 +49649,7 @@
         <v>767</v>
       </c>
       <c r="E81" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="F81">
         <v>32</v>
@@ -49738,7 +49735,7 @@
         <v>768</v>
       </c>
       <c r="E82" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F82">
         <v>26</v>
@@ -49753,10 +49750,10 @@
         <v>250000</v>
       </c>
       <c r="J82" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="K82" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="L82">
         <v>73.3</v>
@@ -49830,7 +49827,7 @@
         <v>769</v>
       </c>
       <c r="E83" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F83">
         <v>21</v>
@@ -49839,7 +49836,7 @@
         <v>1544</v>
       </c>
       <c r="H83" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -49922,7 +49919,7 @@
         <v>770</v>
       </c>
       <c r="E84" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="F84">
         <v>26</v>
@@ -50011,7 +50008,7 @@
         <v>771</v>
       </c>
       <c r="E85" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F85">
         <v>28</v>
@@ -50100,7 +50097,7 @@
         <v>772</v>
       </c>
       <c r="E86" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="F86">
         <v>28</v>
@@ -50186,7 +50183,7 @@
         <v>773</v>
       </c>
       <c r="E87" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="F87">
         <v>28</v>
@@ -50278,7 +50275,7 @@
         <v>774</v>
       </c>
       <c r="E88" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F88">
         <v>29</v>
@@ -50370,7 +50367,7 @@
         <v>775</v>
       </c>
       <c r="E89" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F89">
         <v>33</v>
@@ -50379,7 +50376,7 @@
         <v>1349</v>
       </c>
       <c r="H89" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -50459,7 +50456,7 @@
         <v>776</v>
       </c>
       <c r="E90" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="F90">
         <v>31</v>
@@ -50551,7 +50548,7 @@
         <v>777</v>
       </c>
       <c r="E91" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="F91">
         <v>26</v>
@@ -50643,7 +50640,7 @@
         <v>778</v>
       </c>
       <c r="E92" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="F92">
         <v>31</v>
@@ -50735,7 +50732,7 @@
         <v>779</v>
       </c>
       <c r="E93" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F93">
         <v>27</v>
@@ -50821,7 +50818,7 @@
         <v>780</v>
       </c>
       <c r="E94" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F94">
         <v>32</v>
@@ -50913,7 +50910,7 @@
         <v>781</v>
       </c>
       <c r="E95" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="F95">
         <v>24</v>
@@ -51005,7 +51002,7 @@
         <v>782</v>
       </c>
       <c r="E96" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="F96">
         <v>32</v>
@@ -51014,7 +51011,7 @@
         <v>2106</v>
       </c>
       <c r="H96" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I96">
         <v>450000</v>
@@ -51023,7 +51020,7 @@
         <v>275</v>
       </c>
       <c r="K96" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="L96">
         <v>44.7</v>
@@ -51097,7 +51094,7 @@
         <v>783</v>
       </c>
       <c r="E97" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="F97">
         <v>27</v>
@@ -51186,7 +51183,7 @@
         <v>784</v>
       </c>
       <c r="E98" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F98">
         <v>25</v>
@@ -51275,7 +51272,7 @@
         <v>785</v>
       </c>
       <c r="E99" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F99">
         <v>27</v>
@@ -51364,7 +51361,7 @@
         <v>786</v>
       </c>
       <c r="E100" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F100">
         <v>31</v>
@@ -51453,7 +51450,7 @@
         <v>787</v>
       </c>
       <c r="E101" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="F101">
         <v>27</v>
@@ -51542,7 +51539,7 @@
         <v>486</v>
       </c>
       <c r="E102" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="F102">
         <v>24</v>
@@ -51631,7 +51628,7 @@
         <v>788</v>
       </c>
       <c r="E103" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="F103">
         <v>30</v>
@@ -51717,7 +51714,7 @@
         <v>789</v>
       </c>
       <c r="E104" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="F104">
         <v>29</v>
@@ -51803,7 +51800,7 @@
         <v>790</v>
       </c>
       <c r="E105" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F105">
         <v>27</v>
@@ -51812,7 +51809,7 @@
         <v>1557</v>
       </c>
       <c r="H105" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -51895,7 +51892,7 @@
         <v>791</v>
       </c>
       <c r="E106" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F106">
         <v>30</v>
@@ -51987,7 +51984,7 @@
         <v>792</v>
       </c>
       <c r="E107" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="F107">
         <v>28</v>
@@ -52076,7 +52073,7 @@
         <v>793</v>
       </c>
       <c r="E108" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F108">
         <v>27</v>
@@ -52168,7 +52165,7 @@
         <v>794</v>
       </c>
       <c r="E109" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F109">
         <v>24</v>
@@ -52183,10 +52180,10 @@
         <v>200000</v>
       </c>
       <c r="J109" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="K109" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="L109">
         <v>58.3</v>
@@ -52260,7 +52257,7 @@
         <v>146</v>
       </c>
       <c r="E110" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="F110">
         <v>31</v>
@@ -52352,7 +52349,7 @@
         <v>795</v>
       </c>
       <c r="E111" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F111">
         <v>27</v>
@@ -52370,7 +52367,7 @@
         <v>272</v>
       </c>
       <c r="K111" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="L111">
         <v>90.59999999999999</v>
@@ -52444,7 +52441,7 @@
         <v>796</v>
       </c>
       <c r="E112" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F112">
         <v>26</v>
@@ -52536,7 +52533,7 @@
         <v>797</v>
       </c>
       <c r="E113" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F113">
         <v>26</v>
@@ -52628,7 +52625,7 @@
         <v>798</v>
       </c>
       <c r="E114" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F114">
         <v>35</v>
@@ -52717,7 +52714,7 @@
         <v>799</v>
       </c>
       <c r="E115" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F115">
         <v>28</v>
@@ -52803,7 +52800,7 @@
         <v>800</v>
       </c>
       <c r="E116" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F116">
         <v>25</v>
@@ -52895,7 +52892,7 @@
         <v>801</v>
       </c>
       <c r="E117" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F117">
         <v>27</v>
@@ -52984,7 +52981,7 @@
         <v>802</v>
       </c>
       <c r="E118" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F118">
         <v>32</v>
@@ -53076,7 +53073,7 @@
         <v>803</v>
       </c>
       <c r="E119" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F119">
         <v>24</v>
@@ -53085,7 +53082,7 @@
         <v>2672</v>
       </c>
       <c r="H119" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I119">
         <v>400000</v>
@@ -53168,7 +53165,7 @@
         <v>804</v>
       </c>
       <c r="E120" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F120">
         <v>22</v>
@@ -53260,7 +53257,7 @@
         <v>805</v>
       </c>
       <c r="E121" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="F121">
         <v>28</v>
@@ -53346,7 +53343,7 @@
         <v>806</v>
       </c>
       <c r="E122" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F122">
         <v>27</v>
@@ -53435,7 +53432,7 @@
         <v>807</v>
       </c>
       <c r="E123" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F123">
         <v>31</v>
@@ -53453,7 +53450,7 @@
         <v>277</v>
       </c>
       <c r="K123" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="L123">
         <v>72.5</v>
@@ -53527,7 +53524,7 @@
         <v>808</v>
       </c>
       <c r="E124" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F124">
         <v>26</v>
@@ -53619,7 +53616,7 @@
         <v>809</v>
       </c>
       <c r="E125" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F125">
         <v>25</v>
@@ -53708,7 +53705,7 @@
         <v>810</v>
       </c>
       <c r="E126" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F126">
         <v>22</v>
@@ -53797,7 +53794,7 @@
         <v>811</v>
       </c>
       <c r="E127" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F127">
         <v>26</v>
@@ -53815,7 +53812,7 @@
         <v>277</v>
       </c>
       <c r="K127" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="L127">
         <v>40.4</v>
@@ -53889,7 +53886,7 @@
         <v>812</v>
       </c>
       <c r="E128" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F128">
         <v>26</v>
@@ -53978,7 +53975,7 @@
         <v>813</v>
       </c>
       <c r="E129" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F129">
         <v>33</v>
@@ -53987,7 +53984,7 @@
         <v>1972</v>
       </c>
       <c r="H129" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I129">
         <v>650000</v>
@@ -54070,7 +54067,7 @@
         <v>814</v>
       </c>
       <c r="E130" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F130">
         <v>27</v>
@@ -54156,7 +54153,7 @@
         <v>815</v>
       </c>
       <c r="E131" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F131">
         <v>30</v>
@@ -54248,7 +54245,7 @@
         <v>816</v>
       </c>
       <c r="E132" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F132">
         <v>25</v>
@@ -54260,10 +54257,10 @@
         <v>500000</v>
       </c>
       <c r="J132" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="K132" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="L132">
         <v>29.8</v>
@@ -54334,7 +54331,7 @@
         <v>817</v>
       </c>
       <c r="E133" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F133">
         <v>30</v>
@@ -54343,7 +54340,7 @@
         <v>2529</v>
       </c>
       <c r="H133" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I133">
         <v>600000</v>
@@ -54519,16 +54516,16 @@
         <v>655</v>
       </c>
       <c r="B2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E2" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="F2">
         <v>24</v>
@@ -54543,10 +54540,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="K2" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="L2">
         <v>85.3</v>
@@ -54614,10 +54611,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E3" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="F3">
         <v>25</v>
@@ -54632,10 +54629,10 @@
         <v>150000</v>
       </c>
       <c r="J3" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="K3" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="L3">
         <v>82</v>
@@ -54697,16 +54694,16 @@
         <v>655</v>
       </c>
       <c r="B4" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E4" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="F4">
         <v>25</v>
@@ -54715,16 +54712,16 @@
         <v>3612</v>
       </c>
       <c r="H4" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="I4">
         <v>250000</v>
       </c>
       <c r="J4" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="K4" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="L4">
         <v>85.2</v>
@@ -54792,10 +54789,10 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E5" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="F5">
         <v>26</v>
@@ -54804,7 +54801,7 @@
         <v>2288</v>
       </c>
       <c r="H5" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="I5">
         <v>400000</v>
@@ -54881,10 +54878,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="E6" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="F6">
         <v>27</v>
@@ -54899,10 +54896,10 @@
         <v>1500000</v>
       </c>
       <c r="J6" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="K6" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="L6">
         <v>81.7</v>
@@ -54970,10 +54967,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E7" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="F7">
         <v>28</v>
@@ -54985,10 +54982,10 @@
         <v>1000000</v>
       </c>
       <c r="J7" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="K7" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="L7">
         <v>66.7</v>
@@ -55056,10 +55053,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E8" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="F8">
         <v>26</v>
@@ -55145,10 +55142,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E9" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F9">
         <v>23</v>
@@ -55163,10 +55160,10 @@
         <v>300000</v>
       </c>
       <c r="J9" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="K9" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="L9">
         <v>81.8</v>
@@ -55234,10 +55231,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E10" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="F10">
         <v>24</v>
@@ -55252,10 +55249,10 @@
         <v>200000</v>
       </c>
       <c r="J10" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="K10" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="L10">
         <v>86.7</v>
@@ -55323,10 +55320,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="E11" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="F11">
         <v>32</v>
@@ -55341,10 +55338,10 @@
         <v>1000000</v>
       </c>
       <c r="J11" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="K11" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="L11">
         <v>75.7</v>
@@ -55406,16 +55403,16 @@
         <v>655</v>
       </c>
       <c r="B12" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E12" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="F12">
         <v>22</v>
@@ -55430,10 +55427,10 @@
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="K12" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="L12">
         <v>92.09999999999999</v>
@@ -55501,10 +55498,10 @@
         <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E13" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="F13">
         <v>25</v>
@@ -55519,10 +55516,10 @@
         <v>400000</v>
       </c>
       <c r="J13" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="K13" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="L13">
         <v>76.2</v>
@@ -55590,10 +55587,10 @@
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E14" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F14">
         <v>29</v>
@@ -55611,7 +55608,7 @@
         <v>273</v>
       </c>
       <c r="K14" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="L14">
         <v>78</v>
@@ -55679,10 +55676,10 @@
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="E15" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F15">
         <v>26</v>
@@ -55691,7 +55688,7 @@
         <v>1733</v>
       </c>
       <c r="H15" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -55762,16 +55759,16 @@
         <v>655</v>
       </c>
       <c r="B16" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E16" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F16">
         <v>23</v>
@@ -55786,10 +55783,10 @@
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="K16" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="L16">
         <v>71.8</v>
@@ -55857,10 +55854,10 @@
         <v>4</v>
       </c>
       <c r="D17" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E17" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F17">
         <v>31</v>
@@ -55875,10 +55872,10 @@
         <v>400000</v>
       </c>
       <c r="J17" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="K17" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="L17">
         <v>59.7</v>
@@ -55949,10 +55946,10 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="F18">
         <v>25</v>
@@ -55967,10 +55964,10 @@
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="K18" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="L18">
         <v>82.90000000000001</v>
@@ -56038,10 +56035,10 @@
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="E19" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="F19">
         <v>25</v>
@@ -56056,10 +56053,10 @@
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="K19" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="L19">
         <v>73.59999999999999</v>
@@ -56130,10 +56127,10 @@
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="E20" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="F20">
         <v>25</v>
@@ -56148,10 +56145,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="K20" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="L20">
         <v>79.90000000000001</v>
@@ -56219,7 +56216,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E21" t="s">
         <v>826</v>
@@ -56237,10 +56234,10 @@
         <v>500000</v>
       </c>
       <c r="J21" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="K21" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="L21">
         <v>57.4</v>
@@ -56311,10 +56308,10 @@
         <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E22" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F22">
         <v>21</v>
@@ -56329,10 +56326,10 @@
         <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="K22" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L22">
         <v>84.40000000000001</v>
@@ -56400,10 +56397,10 @@
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E23" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F23">
         <v>24</v>
@@ -56418,10 +56415,10 @@
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="K23" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="L23">
         <v>67.59999999999999</v>
@@ -56492,10 +56489,10 @@
         <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E24" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="F24">
         <v>34</v>
@@ -56507,10 +56504,10 @@
         <v>1000000</v>
       </c>
       <c r="J24" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="K24" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="L24">
         <v>71.7</v>
@@ -56578,10 +56575,10 @@
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E25" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="F25">
         <v>26</v>
@@ -56596,10 +56593,10 @@
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="K25" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="L25">
         <v>71.2</v>
@@ -56667,10 +56664,10 @@
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E26" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F26">
         <v>33</v>
@@ -56682,10 +56679,10 @@
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="K26" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="L26">
         <v>68</v>
@@ -56753,10 +56750,10 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="E27" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="F27">
         <v>27</v>
@@ -56771,10 +56768,10 @@
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="K27" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="L27">
         <v>77.8</v>
@@ -56836,16 +56833,16 @@
         <v>655</v>
       </c>
       <c r="B28" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C28" t="s">
         <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="E28" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="F28">
         <v>24</v>
@@ -56931,10 +56928,10 @@
         <v>6</v>
       </c>
       <c r="D29" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E29" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="F29">
         <v>34</v>
@@ -56949,10 +56946,10 @@
         <v>1000000</v>
       </c>
       <c r="J29" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="K29" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="L29">
         <v>68.09999999999999</v>
@@ -57017,16 +57014,16 @@
         <v>655</v>
       </c>
       <c r="B30" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C30" t="s">
         <v>6</v>
       </c>
       <c r="D30" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E30" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="F30">
         <v>20</v>
@@ -57041,10 +57038,10 @@
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="K30" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="L30">
         <v>68.59999999999999</v>
@@ -57115,10 +57112,10 @@
         <v>6</v>
       </c>
       <c r="D31" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="E31" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="F31">
         <v>20</v>
@@ -57133,10 +57130,10 @@
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="K31" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="L31">
         <v>61.4</v>
@@ -57201,16 +57198,16 @@
         <v>655</v>
       </c>
       <c r="B32" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C32" t="s">
         <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E32" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="F32">
         <v>24</v>
@@ -57222,10 +57219,10 @@
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="K32" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="L32">
         <v>79.40000000000001</v>
@@ -57293,10 +57290,10 @@
         <v>7</v>
       </c>
       <c r="D33" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E33" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="F33">
         <v>30</v>
@@ -57382,10 +57379,10 @@
         <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E34" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="F34">
         <v>27</v>
@@ -57400,10 +57397,10 @@
         <v>1400000</v>
       </c>
       <c r="J34" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="K34" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="L34">
         <v>73.40000000000001</v>
@@ -57474,10 +57471,10 @@
         <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E35" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F35">
         <v>26</v>
@@ -57489,10 +57486,10 @@
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="K35" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="L35">
         <v>82.59999999999999</v>
@@ -57537,7 +57534,7 @@
         <v>1</v>
       </c>
       <c r="AA35" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="AB35" t="b">
         <v>1</v>
@@ -57560,10 +57557,10 @@
         <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E36" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="F36">
         <v>26</v>
@@ -57578,10 +57575,10 @@
         <v>300000</v>
       </c>
       <c r="J36" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="K36" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="L36">
         <v>91.2</v>
@@ -57652,10 +57649,10 @@
         <v>7</v>
       </c>
       <c r="D37" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="E37" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="F37">
         <v>19</v>
@@ -57744,10 +57741,10 @@
         <v>7</v>
       </c>
       <c r="D38" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="E38" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="F38">
         <v>26</v>
@@ -57762,10 +57759,10 @@
         <v>275000</v>
       </c>
       <c r="J38" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="K38" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="L38">
         <v>68.5</v>
@@ -57833,10 +57830,10 @@
         <v>7</v>
       </c>
       <c r="D39" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E39" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="F39">
         <v>26</v>
@@ -57854,7 +57851,7 @@
         <v>672</v>
       </c>
       <c r="K39" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="L39">
         <v>69.7</v>
@@ -57922,10 +57919,10 @@
         <v>7</v>
       </c>
       <c r="D40" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E40" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="F40">
         <v>26</v>
@@ -57940,10 +57937,10 @@
         <v>200000</v>
       </c>
       <c r="J40" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="K40" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="L40">
         <v>88.09999999999999</v>
@@ -58005,16 +58002,16 @@
         <v>655</v>
       </c>
       <c r="B41" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C41" t="s">
         <v>7</v>
       </c>
       <c r="D41" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E41" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="F41">
         <v>33</v>
@@ -58100,10 +58097,10 @@
         <v>5</v>
       </c>
       <c r="D42" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E42" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F42">
         <v>23</v>
@@ -58118,10 +58115,10 @@
         <v>500000</v>
       </c>
       <c r="J42" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="K42" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L42">
         <v>87.2</v>
@@ -58186,16 +58183,16 @@
         <v>655</v>
       </c>
       <c r="B43" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C43" t="s">
         <v>5</v>
       </c>
       <c r="D43" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E43" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F43">
         <v>18</v>
@@ -58210,10 +58207,10 @@
         <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="K43" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="L43">
         <v>83.40000000000001</v>
@@ -58275,16 +58272,16 @@
         <v>655</v>
       </c>
       <c r="B44" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
       </c>
       <c r="D44" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E44" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="F44">
         <v>21</v>
@@ -58299,10 +58296,10 @@
         <v>0</v>
       </c>
       <c r="J44" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="K44" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="L44">
         <v>73.09999999999999</v>
@@ -58370,10 +58367,10 @@
         <v>5</v>
       </c>
       <c r="D45" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E45" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="F45">
         <v>33</v>
@@ -58388,10 +58385,10 @@
         <v>1500000</v>
       </c>
       <c r="J45" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="K45" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="L45">
         <v>80</v>
@@ -58459,10 +58456,10 @@
         <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E46" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="F46">
         <v>23</v>
@@ -58477,10 +58474,10 @@
         <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="K46" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="L46">
         <v>85.3</v>
@@ -58545,16 +58542,16 @@
         <v>655</v>
       </c>
       <c r="B47" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C47" t="s">
         <v>5</v>
       </c>
       <c r="D47" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E47" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="F47">
         <v>27</v>
@@ -58569,10 +58566,10 @@
         <v>250000</v>
       </c>
       <c r="J47" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="K47" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="L47">
         <v>76.5</v>
@@ -58640,10 +58637,10 @@
         <v>5</v>
       </c>
       <c r="D48" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E48" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="F48">
         <v>21</v>
@@ -58732,10 +58729,10 @@
         <v>5</v>
       </c>
       <c r="D49" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E49" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F49">
         <v>33</v>
@@ -58744,16 +58741,16 @@
         <v>2707</v>
       </c>
       <c r="H49" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I49">
         <v>350000</v>
       </c>
       <c r="J49" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="K49" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="L49">
         <v>78.7</v>
@@ -58821,10 +58818,10 @@
         <v>5</v>
       </c>
       <c r="D50" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E50" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="F50">
         <v>25</v>
@@ -58839,10 +58836,10 @@
         <v>300000</v>
       </c>
       <c r="J50" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="K50" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="L50">
         <v>84.7</v>
@@ -58887,7 +58884,7 @@
         <v>1</v>
       </c>
       <c r="AA50" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="AB50" t="b">
         <v>0</v>
@@ -58910,10 +58907,10 @@
         <v>5</v>
       </c>
       <c r="D51" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="E51" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="F51">
         <v>21</v>
@@ -58996,10 +58993,10 @@
         <v>8</v>
       </c>
       <c r="D52" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E52" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F52">
         <v>35</v>
@@ -59014,10 +59011,10 @@
         <v>400000</v>
       </c>
       <c r="J52" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="K52" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="L52">
         <v>73.8</v>
@@ -59062,7 +59059,7 @@
         <v>1</v>
       </c>
       <c r="AA52" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="AB52" t="b">
         <v>1</v>
@@ -59085,10 +59082,10 @@
         <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="E53" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F53">
         <v>24</v>
@@ -59103,10 +59100,10 @@
         <v>0</v>
       </c>
       <c r="J53" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="K53" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="L53">
         <v>74.5</v>
@@ -59174,10 +59171,10 @@
         <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E54" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F54">
         <v>31</v>
@@ -59192,10 +59189,10 @@
         <v>1400000</v>
       </c>
       <c r="J54" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="K54" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L54">
         <v>75.59999999999999</v>
@@ -59263,10 +59260,10 @@
         <v>8</v>
       </c>
       <c r="D55" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="E55" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="F55">
         <v>29</v>
@@ -59275,16 +59272,16 @@
         <v>1170</v>
       </c>
       <c r="H55" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I55">
         <v>550000</v>
       </c>
       <c r="J55" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="K55" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L55">
         <v>89.7</v>
@@ -59346,16 +59343,16 @@
         <v>655</v>
       </c>
       <c r="B56" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C56" t="s">
         <v>8</v>
       </c>
       <c r="D56" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E56" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F56">
         <v>21</v>
@@ -59441,10 +59438,10 @@
         <v>8</v>
       </c>
       <c r="D57" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="E57" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="F57">
         <v>32</v>
@@ -59459,10 +59456,10 @@
         <v>800000</v>
       </c>
       <c r="J57" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="K57" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="L57">
         <v>73.09999999999999</v>
@@ -59533,10 +59530,10 @@
         <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E58" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="F58">
         <v>29</v>
@@ -59551,10 +59548,10 @@
         <v>700000</v>
       </c>
       <c r="J58" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="K58" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L58">
         <v>61.7</v>
@@ -59622,10 +59619,10 @@
         <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="E59" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="F59">
         <v>29</v>
@@ -59640,10 +59637,10 @@
         <v>750000</v>
       </c>
       <c r="J59" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="K59" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="L59">
         <v>46.3</v>
@@ -59711,10 +59708,10 @@
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E60" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="F60">
         <v>25</v>
@@ -59729,10 +59726,10 @@
         <v>0</v>
       </c>
       <c r="J60" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="K60" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="L60">
         <v>59.7</v>
@@ -59803,10 +59800,10 @@
         <v>8</v>
       </c>
       <c r="D61" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E61" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="F61">
         <v>34</v>
@@ -59815,16 +59812,16 @@
         <v>3978</v>
       </c>
       <c r="H61" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I61">
         <v>900000</v>
       </c>
       <c r="J61" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="K61" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="L61">
         <v>78</v>
@@ -59895,10 +59892,10 @@
         <v>9</v>
       </c>
       <c r="D62" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E62" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F62">
         <v>22</v>
@@ -59907,16 +59904,16 @@
         <v>1941</v>
       </c>
       <c r="H62" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="I62">
         <v>1500000</v>
       </c>
       <c r="J62" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="K62" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="L62">
         <v>77.7</v>
@@ -59984,10 +59981,10 @@
         <v>9</v>
       </c>
       <c r="D63" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E63" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="F63">
         <v>23</v>
@@ -60002,10 +59999,10 @@
         <v>0</v>
       </c>
       <c r="J63" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="K63" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="L63">
         <v>83.90000000000001</v>
@@ -60076,10 +60073,10 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E64" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="F64">
         <v>25</v>
@@ -60091,10 +60088,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="K64" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="L64">
         <v>87.59999999999999</v>
@@ -60162,10 +60159,10 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="E65" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="F65">
         <v>20</v>
@@ -60180,10 +60177,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="K65" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="L65">
         <v>87.59999999999999</v>
@@ -60245,16 +60242,16 @@
         <v>655</v>
       </c>
       <c r="B66" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C66" t="s">
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E66" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="F66">
         <v>28</v>
@@ -60269,10 +60266,10 @@
         <v>600000</v>
       </c>
       <c r="J66" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="K66" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="L66">
         <v>83.7</v>
@@ -60334,16 +60331,16 @@
         <v>655</v>
       </c>
       <c r="B67" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C67" t="s">
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E67" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="F67">
         <v>25</v>
@@ -60352,16 +60349,16 @@
         <v>1839</v>
       </c>
       <c r="H67" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I67">
         <v>25000</v>
       </c>
       <c r="J67" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="K67" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L67">
         <v>84.5</v>
@@ -60429,10 +60426,10 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E68" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="F68">
         <v>33</v>
@@ -60447,10 +60444,10 @@
         <v>1200000</v>
       </c>
       <c r="J68" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="K68" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="L68">
         <v>88.90000000000001</v>
@@ -60518,10 +60515,10 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E69" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F69">
         <v>25</v>
@@ -60604,16 +60601,16 @@
         <v>655</v>
       </c>
       <c r="B70" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C70" t="s">
         <v>9</v>
       </c>
       <c r="D70" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="E70" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="F70">
         <v>23</v>
@@ -60628,10 +60625,10 @@
         <v>0</v>
       </c>
       <c r="J70" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="K70" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="L70">
         <v>88.3</v>
@@ -60699,10 +60696,10 @@
         <v>9</v>
       </c>
       <c r="D71" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E71" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="F71">
         <v>27</v>
@@ -60717,10 +60714,10 @@
         <v>0</v>
       </c>
       <c r="J71" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="K71" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="L71">
         <v>80.3</v>
@@ -60788,10 +60785,10 @@
         <v>10</v>
       </c>
       <c r="D72" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="E72" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="F72">
         <v>25</v>
@@ -60806,10 +60803,10 @@
         <v>1200000</v>
       </c>
       <c r="J72" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="K72" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="L72">
         <v>94.5</v>
@@ -60880,10 +60877,10 @@
         <v>10</v>
       </c>
       <c r="D73" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="E73" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="F73">
         <v>24</v>
@@ -60898,10 +60895,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="K73" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L73">
         <v>92.7</v>
@@ -60963,16 +60960,16 @@
         <v>655</v>
       </c>
       <c r="B74" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C74" t="s">
         <v>10</v>
       </c>
       <c r="D74" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="E74" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F74">
         <v>18</v>
@@ -60987,10 +60984,10 @@
         <v>0</v>
       </c>
       <c r="J74" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="K74" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="L74">
         <v>89.09999999999999</v>
@@ -61058,10 +61055,10 @@
         <v>10</v>
       </c>
       <c r="D75" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E75" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="F75">
         <v>23</v>
@@ -61070,16 +61067,16 @@
         <v>2730</v>
       </c>
       <c r="H75" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I75">
         <v>0</v>
       </c>
       <c r="J75" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="K75" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="L75">
         <v>91.7</v>
@@ -61150,10 +61147,10 @@
         <v>10</v>
       </c>
       <c r="D76" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E76" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F76">
         <v>34</v>
@@ -61162,16 +61159,16 @@
         <v>1521</v>
       </c>
       <c r="H76" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I76">
         <v>0</v>
       </c>
       <c r="J76" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="K76" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="L76">
         <v>62.8</v>
@@ -61239,10 +61236,10 @@
         <v>10</v>
       </c>
       <c r="D77" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E77" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="F77">
         <v>25</v>
@@ -61254,10 +61251,10 @@
         <v>400000</v>
       </c>
       <c r="J77" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="K77" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="L77">
         <v>71.3</v>
@@ -61325,10 +61322,10 @@
         <v>10</v>
       </c>
       <c r="D78" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E78" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="F78">
         <v>29</v>
@@ -61343,10 +61340,10 @@
         <v>0</v>
       </c>
       <c r="J78" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="K78" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="L78">
         <v>88.40000000000001</v>
@@ -61414,10 +61411,10 @@
         <v>10</v>
       </c>
       <c r="D79" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="E79" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F79">
         <v>24</v>
@@ -61432,10 +61429,10 @@
         <v>1000000</v>
       </c>
       <c r="J79" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="K79" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="L79">
         <v>83</v>
@@ -61503,10 +61500,10 @@
         <v>10</v>
       </c>
       <c r="D80" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E80" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="F80">
         <v>23</v>
@@ -61521,10 +61518,10 @@
         <v>0</v>
       </c>
       <c r="J80" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="K80" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="L80">
         <v>82.7</v>
@@ -61586,16 +61583,16 @@
         <v>655</v>
       </c>
       <c r="B81" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="C81" t="s">
         <v>10</v>
       </c>
       <c r="D81" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E81" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="F81">
         <v>35</v>
@@ -61610,10 +61607,10 @@
         <v>800000</v>
       </c>
       <c r="J81" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="K81" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="L81">
         <v>89.40000000000001</v>
@@ -61681,10 +61678,10 @@
         <v>11</v>
       </c>
       <c r="D82" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="E82" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="F82">
         <v>26</v>
@@ -61699,10 +61696,10 @@
         <v>500000</v>
       </c>
       <c r="J82" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="K82" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="L82">
         <v>82.59999999999999</v>
@@ -61770,10 +61767,10 @@
         <v>11</v>
       </c>
       <c r="D83" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E83" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="F83">
         <v>30</v>
@@ -61788,10 +61785,10 @@
         <v>1200000</v>
       </c>
       <c r="J83" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="K83" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="L83">
         <v>70.8</v>
@@ -61853,16 +61850,16 @@
         <v>655</v>
       </c>
       <c r="B84" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C84" t="s">
         <v>11</v>
       </c>
       <c r="D84" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E84" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F84">
         <v>24</v>
@@ -61877,10 +61874,10 @@
         <v>0</v>
       </c>
       <c r="J84" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="K84" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="L84">
         <v>76.59999999999999</v>
@@ -61948,10 +61945,10 @@
         <v>11</v>
       </c>
       <c r="D85" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="E85" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="F85">
         <v>22</v>
@@ -61966,10 +61963,10 @@
         <v>250000</v>
       </c>
       <c r="J85" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="K85" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="L85">
         <v>46.2</v>
@@ -62040,10 +62037,10 @@
         <v>11</v>
       </c>
       <c r="D86" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="E86" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="F86">
         <v>25</v>
@@ -62058,10 +62055,10 @@
         <v>800000</v>
       </c>
       <c r="J86" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="K86" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L86">
         <v>74.2</v>
@@ -62126,16 +62123,16 @@
         <v>655</v>
       </c>
       <c r="B87" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C87" t="s">
         <v>11</v>
       </c>
       <c r="D87" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E87" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="F87">
         <v>32</v>
@@ -62150,10 +62147,10 @@
         <v>0</v>
       </c>
       <c r="J87" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K87" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="L87">
         <v>61.2</v>
@@ -62221,10 +62218,10 @@
         <v>11</v>
       </c>
       <c r="D88" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E88" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F88">
         <v>30</v>
@@ -62239,10 +62236,10 @@
         <v>400000</v>
       </c>
       <c r="J88" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="K88" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L88">
         <v>77.40000000000001</v>
@@ -62313,10 +62310,10 @@
         <v>11</v>
       </c>
       <c r="D89" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E89" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="F89">
         <v>30</v>
@@ -62402,10 +62399,10 @@
         <v>11</v>
       </c>
       <c r="D90" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="E90" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F90">
         <v>25</v>
@@ -62423,7 +62420,7 @@
         <v>670</v>
       </c>
       <c r="K90" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L90">
         <v>67.90000000000001</v>
@@ -62488,16 +62485,16 @@
         <v>655</v>
       </c>
       <c r="B91" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C91" t="s">
         <v>11</v>
       </c>
       <c r="D91" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E91" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="F91">
         <v>22</v>
@@ -62512,10 +62509,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="K91" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="L91">
         <v>65.3</v>
@@ -62577,16 +62574,16 @@
         <v>655</v>
       </c>
       <c r="B92" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C92" t="s">
         <v>12</v>
       </c>
       <c r="D92" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E92" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="F92">
         <v>18</v>
@@ -62601,10 +62598,10 @@
         <v>0</v>
       </c>
       <c r="J92" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="K92" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L92">
         <v>70.5</v>
@@ -62675,10 +62672,10 @@
         <v>12</v>
       </c>
       <c r="D93" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E93" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="F93">
         <v>30</v>
@@ -62690,10 +62687,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="K93" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="L93">
         <v>90.8</v>
@@ -62761,10 +62758,10 @@
         <v>12</v>
       </c>
       <c r="D94" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E94" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="F94">
         <v>23</v>
@@ -62776,10 +62773,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="K94" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="L94">
         <v>88.59999999999999</v>
@@ -62850,10 +62847,10 @@
         <v>12</v>
       </c>
       <c r="D95" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="E95" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="F95">
         <v>23</v>
@@ -62868,10 +62865,10 @@
         <v>800000</v>
       </c>
       <c r="J95" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="K95" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="L95">
         <v>63.9</v>
@@ -62942,10 +62939,10 @@
         <v>12</v>
       </c>
       <c r="D96" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="E96" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="F96">
         <v>25</v>
@@ -62960,10 +62957,10 @@
         <v>500000</v>
       </c>
       <c r="J96" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="K96" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="L96">
         <v>63.2</v>
@@ -63034,10 +63031,10 @@
         <v>12</v>
       </c>
       <c r="D97" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="E97" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="F97">
         <v>19</v>
@@ -63052,10 +63049,10 @@
         <v>0</v>
       </c>
       <c r="J97" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="K97" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="L97">
         <v>75.7</v>
@@ -63123,10 +63120,10 @@
         <v>12</v>
       </c>
       <c r="D98" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="E98" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="F98">
         <v>27</v>
@@ -63141,10 +63138,10 @@
         <v>200000</v>
       </c>
       <c r="J98" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="K98" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="L98">
         <v>74.3</v>
@@ -63212,10 +63209,10 @@
         <v>12</v>
       </c>
       <c r="D99" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E99" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="F99">
         <v>26</v>
@@ -63227,10 +63224,10 @@
         <v>550000</v>
       </c>
       <c r="J99" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="K99" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="L99">
         <v>84</v>
@@ -63298,10 +63295,10 @@
         <v>12</v>
       </c>
       <c r="D100" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="E100" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="F100">
         <v>31</v>
@@ -63310,16 +63307,16 @@
         <v>1100</v>
       </c>
       <c r="H100" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I100">
         <v>1000000</v>
       </c>
       <c r="J100" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="K100" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="L100">
         <v>57.5</v>
@@ -63387,10 +63384,10 @@
         <v>12</v>
       </c>
       <c r="D101" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E101" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F101">
         <v>28</v>
@@ -63470,16 +63467,16 @@
         <v>655</v>
       </c>
       <c r="B102" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C102" t="s">
         <v>13</v>
       </c>
       <c r="D102" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="E102" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F102">
         <v>35</v>
@@ -63494,10 +63491,10 @@
         <v>1300000</v>
       </c>
       <c r="J102" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="K102" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="L102">
         <v>92.8</v>
@@ -63559,16 +63556,16 @@
         <v>655</v>
       </c>
       <c r="B103" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C103" t="s">
         <v>13</v>
       </c>
       <c r="D103" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="E103" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="F103">
         <v>29</v>
@@ -63583,10 +63580,10 @@
         <v>0</v>
       </c>
       <c r="J103" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="K103" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L103">
         <v>78.40000000000001</v>
@@ -63654,7 +63651,7 @@
         <v>13</v>
       </c>
       <c r="D104" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="E104" t="s">
         <v>843</v>
@@ -63743,10 +63740,10 @@
         <v>13</v>
       </c>
       <c r="D105" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="E105" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="F105">
         <v>26</v>
@@ -63761,10 +63758,10 @@
         <v>0</v>
       </c>
       <c r="J105" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="K105" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="L105">
         <v>56.7</v>
@@ -63826,16 +63823,16 @@
         <v>655</v>
       </c>
       <c r="B106" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C106" t="s">
         <v>13</v>
       </c>
       <c r="D106" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E106" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="F106">
         <v>24</v>
@@ -63850,10 +63847,10 @@
         <v>0</v>
       </c>
       <c r="J106" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="K106" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="L106">
         <v>65.7</v>
@@ -63918,16 +63915,16 @@
         <v>655</v>
       </c>
       <c r="B107" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C107" t="s">
         <v>13</v>
       </c>
       <c r="D107" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="E107" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="F107">
         <v>26</v>
@@ -64007,16 +64004,16 @@
         <v>655</v>
       </c>
       <c r="B108" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C108" t="s">
         <v>13</v>
       </c>
       <c r="D108" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="E108" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="F108">
         <v>24</v>
@@ -64031,10 +64028,10 @@
         <v>0</v>
       </c>
       <c r="J108" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="K108" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="L108">
         <v>78.59999999999999</v>
@@ -64102,10 +64099,10 @@
         <v>13</v>
       </c>
       <c r="D109" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="E109" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="F109">
         <v>23</v>
@@ -64120,10 +64117,10 @@
         <v>0</v>
       </c>
       <c r="J109" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="K109" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="L109">
         <v>78.40000000000001</v>
@@ -64185,16 +64182,16 @@
         <v>655</v>
       </c>
       <c r="B110" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C110" t="s">
         <v>13</v>
       </c>
       <c r="D110" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="E110" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="F110">
         <v>22</v>
@@ -64212,7 +64209,7 @@
         <v>273</v>
       </c>
       <c r="K110" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="L110">
         <v>88</v>
@@ -64280,10 +64277,10 @@
         <v>13</v>
       </c>
       <c r="D111" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="E111" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="F111">
         <v>28</v>
@@ -64492,7 +64489,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="E2" t="s">
         <v>251</v>
@@ -64581,7 +64578,7 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="E3" t="s">
         <v>251</v>
@@ -64688,7 +64685,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="E4" t="s">
         <v>251</v>
@@ -64795,7 +64792,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E5" t="s">
         <v>251</v>
@@ -64905,7 +64902,7 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="E6" t="s">
         <v>251</v>
@@ -65232,7 +65229,7 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E9" t="s">
         <v>251</v>
@@ -65342,7 +65339,7 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E10" t="s">
         <v>251</v>
@@ -65452,7 +65449,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="E11" t="s">
         <v>251</v>
@@ -66171,7 +66168,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="E18" t="s">
         <v>239</v>
@@ -66364,7 +66361,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="E20" t="s">
         <v>239</v>
@@ -66994,7 +66991,7 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="E26" t="s">
         <v>239</v>
@@ -67817,7 +67814,7 @@
         <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E34" t="s">
         <v>237</v>
@@ -68450,7 +68447,7 @@
         <v>9</v>
       </c>
       <c r="D40" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="E40" t="s">
         <v>240</v>
@@ -68982,7 +68979,7 @@
         <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="E45" t="s">
         <v>240</v>
@@ -69092,7 +69089,7 @@
         <v>9</v>
       </c>
       <c r="D46" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="E46" t="s">
         <v>240</v>
@@ -69288,7 +69285,7 @@
         <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="E48" t="s">
         <v>240</v>
@@ -69478,7 +69475,7 @@
         <v>3</v>
       </c>
       <c r="D50" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="E50" t="s">
         <v>240</v>
@@ -69573,7 +69570,7 @@
         <v>7</v>
       </c>
       <c r="D51" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="E51" t="s">
         <v>240</v>
@@ -69775,7 +69772,7 @@
         <v>9</v>
       </c>
       <c r="D53" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="E53" t="s">
         <v>245</v>
@@ -70399,7 +70396,7 @@
         <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="E59" t="s">
         <v>245</v>
@@ -70928,7 +70925,7 @@
         <v>8</v>
       </c>
       <c r="D64" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="E64" t="s">
         <v>245</v>
@@ -71567,7 +71564,7 @@
         <v>5</v>
       </c>
       <c r="D70" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="E70" t="s">
         <v>235</v>
@@ -72625,7 +72622,7 @@
         <v>7</v>
       </c>
       <c r="D80" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="E80" t="s">
         <v>235</v>
@@ -72720,7 +72717,7 @@
         <v>6</v>
       </c>
       <c r="D81" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="E81" t="s">
         <v>242</v>
@@ -73026,7 +73023,7 @@
         <v>6</v>
       </c>
       <c r="D84" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="E84" t="s">
         <v>242</v>
@@ -73231,7 +73228,7 @@
         <v>9</v>
       </c>
       <c r="D86" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="E86" t="s">
         <v>242</v>
@@ -74298,7 +74295,7 @@
         <v>13</v>
       </c>
       <c r="D96" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="E96" t="s">
         <v>234</v>
@@ -74408,7 +74405,7 @@
         <v>7</v>
       </c>
       <c r="D97" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="E97" t="s">
         <v>234</v>
@@ -74613,7 +74610,7 @@
         <v>6</v>
       </c>
       <c r="D99" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="E99" t="s">
         <v>234</v>
@@ -74943,7 +74940,7 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="E102" t="s">
         <v>234</v>
@@ -75163,7 +75160,7 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E104" t="s">
         <v>252</v>
@@ -75273,7 +75270,7 @@
         <v>6</v>
       </c>
       <c r="D105" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E105" t="s">
         <v>252</v>
@@ -75383,7 +75380,7 @@
         <v>6</v>
       </c>
       <c r="D106" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="E106" t="s">
         <v>252</v>
@@ -75478,7 +75475,7 @@
         <v>3</v>
       </c>
       <c r="D107" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="E107" t="s">
         <v>252</v>
@@ -75573,7 +75570,7 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="E108" t="s">
         <v>252</v>
@@ -75867,7 +75864,7 @@
         <v>4</v>
       </c>
       <c r="D111" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E111" t="s">
         <v>252</v>
@@ -76488,7 +76485,7 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="E117" t="s">
         <v>247</v>
@@ -76705,7 +76702,7 @@
         <v>3</v>
       </c>
       <c r="D119" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="E119" t="s">
         <v>247</v>
@@ -76984,7 +76981,7 @@
         <v>5</v>
       </c>
       <c r="D122" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E122" t="s">
         <v>247</v>
@@ -77361,7 +77358,7 @@
         <v>6</v>
       </c>
       <c r="D126" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E126" t="s">
         <v>247</v>
@@ -77471,7 +77468,7 @@
         <v>6</v>
       </c>
       <c r="D127" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E127" t="s">
         <v>247</v>
@@ -77581,7 +77578,7 @@
         <v>5</v>
       </c>
       <c r="D128" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="E128" t="s">
         <v>247</v>
@@ -77593,7 +77590,7 @@
         <v>1162</v>
       </c>
       <c r="H128" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="I128">
         <v>1800000</v>
@@ -78086,7 +78083,7 @@
         <v>5</v>
       </c>
       <c r="D133" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="E133" t="s">
         <v>241</v>
@@ -78915,7 +78912,7 @@
         <v>13</v>
       </c>
       <c r="D141" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="E141" t="s">
         <v>241</v>
@@ -79025,7 +79022,7 @@
         <v>13</v>
       </c>
       <c r="D142" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E142" t="s">
         <v>241</v>
@@ -79132,7 +79129,7 @@
         <v>7</v>
       </c>
       <c r="D143" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="E143" t="s">
         <v>241</v>
@@ -79310,7 +79307,7 @@
         <v>9</v>
       </c>
       <c r="D145" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="E145" t="s">
         <v>241</v>
@@ -79515,7 +79512,7 @@
         <v>12</v>
       </c>
       <c r="D147" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="E147" t="s">
         <v>241</v>
@@ -79907,7 +79904,7 @@
         <v>6</v>
       </c>
       <c r="D151" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="E151" t="s">
         <v>233</v>
@@ -80115,7 +80112,7 @@
         <v>6</v>
       </c>
       <c r="D153" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="E153" t="s">
         <v>233</v>
@@ -80522,7 +80519,7 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="E157" t="s">
         <v>233</v>
@@ -80944,7 +80941,7 @@
         <v>13</v>
       </c>
       <c r="D161" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="E161" t="s">
         <v>233</v>
@@ -81045,7 +81042,7 @@
         <v>4</v>
       </c>
       <c r="D162" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="E162" t="s">
         <v>233</v>
@@ -81550,7 +81547,7 @@
         <v>13</v>
       </c>
       <c r="D167" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="E167" t="s">
         <v>246</v>
@@ -81660,7 +81657,7 @@
         <v>5</v>
       </c>
       <c r="D168" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="E168" t="s">
         <v>246</v>
@@ -82061,7 +82058,7 @@
         <v>4</v>
       </c>
       <c r="D172" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="E172" t="s">
         <v>246</v>
@@ -82168,7 +82165,7 @@
         <v>9</v>
       </c>
       <c r="D173" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="E173" t="s">
         <v>246</v>
@@ -82456,7 +82453,7 @@
         <v>12</v>
       </c>
       <c r="D176" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="E176" t="s">
         <v>246</v>
@@ -82664,7 +82661,7 @@
         <v>10</v>
       </c>
       <c r="D178" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="E178" t="s">
         <v>243</v>
@@ -82988,7 +82985,7 @@
         <v>8</v>
       </c>
       <c r="D181" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="E181" t="s">
         <v>243</v>
@@ -83009,7 +83006,7 @@
         <v>272</v>
       </c>
       <c r="K181" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="L181">
         <v>46.9</v>
@@ -83270,7 +83267,7 @@
         <v>4</v>
       </c>
       <c r="D184" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="E184" t="s">
         <v>243</v>
@@ -83888,7 +83885,7 @@
         <v>4</v>
       </c>
       <c r="D190" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="E190" t="s">
         <v>243</v>
@@ -83998,7 +83995,7 @@
         <v>3</v>
       </c>
       <c r="D191" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="E191" t="s">
         <v>249</v>
@@ -84509,7 +84506,7 @@
         <v>10</v>
       </c>
       <c r="D196" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E196" t="s">
         <v>249</v>
@@ -85403,7 +85400,7 @@
         <v>10</v>
       </c>
       <c r="D205" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="E205" t="s">
         <v>248</v>
@@ -85510,7 +85507,7 @@
         <v>9</v>
       </c>
       <c r="D206" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="E206" t="s">
         <v>248</v>
@@ -85620,7 +85617,7 @@
         <v>3</v>
       </c>
       <c r="D207" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="E207" t="s">
         <v>248</v>
@@ -85715,7 +85712,7 @@
         <v>8</v>
       </c>
       <c r="D208" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E208" t="s">
         <v>248</v>
@@ -85825,7 +85822,7 @@
         <v>7</v>
       </c>
       <c r="D209" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="E209" t="s">
         <v>248</v>
@@ -85935,7 +85932,7 @@
         <v>13</v>
       </c>
       <c r="D210" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="E210" t="s">
         <v>248</v>
@@ -86155,7 +86152,7 @@
         <v>5</v>
       </c>
       <c r="D212" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="E212" t="s">
         <v>248</v>
@@ -86265,7 +86262,7 @@
         <v>6</v>
       </c>
       <c r="D213" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="E213" t="s">
         <v>248</v>
@@ -86702,7 +86699,7 @@
         <v>6</v>
       </c>
       <c r="D217" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="E217" t="s">
         <v>248</v>
@@ -86812,7 +86809,7 @@
         <v>4</v>
       </c>
       <c r="D218" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="E218" t="s">
         <v>248</v>
@@ -86910,7 +86907,7 @@
         <v>6</v>
       </c>
       <c r="D219" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="E219" t="s">
         <v>244</v>
@@ -87017,7 +87014,7 @@
         <v>9</v>
       </c>
       <c r="D220" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E220" t="s">
         <v>244</v>
@@ -87234,7 +87231,7 @@
         <v>3</v>
       </c>
       <c r="D222" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="E222" t="s">
         <v>244</v>
@@ -87329,7 +87326,7 @@
         <v>7</v>
       </c>
       <c r="D223" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="E223" t="s">
         <v>244</v>
@@ -87534,7 +87531,7 @@
         <v>7</v>
       </c>
       <c r="D225" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="E225" t="s">
         <v>244</v>
@@ -87641,7 +87638,7 @@
         <v>13</v>
       </c>
       <c r="D226" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="E226" t="s">
         <v>244</v>
@@ -87742,7 +87739,7 @@
         <v>4</v>
       </c>
       <c r="D227" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="E227" t="s">
         <v>244</v>
@@ -87846,7 +87843,7 @@
         <v>6</v>
       </c>
       <c r="D228" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="E228" t="s">
         <v>244</v>
@@ -87858,7 +87855,7 @@
         <v>1053</v>
       </c>
       <c r="H228" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="J228" t="s">
         <v>403</v>
@@ -87953,7 +87950,7 @@
         <v>13</v>
       </c>
       <c r="D229" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="E229" t="s">
         <v>244</v>
@@ -88060,7 +88057,7 @@
         <v>4</v>
       </c>
       <c r="D230" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="E230" t="s">
         <v>244</v>
@@ -88167,7 +88164,7 @@
         <v>5</v>
       </c>
       <c r="D231" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="E231" t="s">
         <v>244</v>
@@ -88179,7 +88176,7 @@
         <v>917</v>
       </c>
       <c r="H231" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="J231" t="s">
         <v>272</v>
@@ -88274,7 +88271,7 @@
         <v>6</v>
       </c>
       <c r="D232" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="E232" t="s">
         <v>244</v>
@@ -88369,7 +88366,7 @@
         <v>9</v>
       </c>
       <c r="D233" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="E233" t="s">
         <v>244</v>
@@ -89299,7 +89296,7 @@
         <v>6</v>
       </c>
       <c r="D242" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="E242" t="s">
         <v>236</v>
@@ -89394,7 +89391,7 @@
         <v>4</v>
       </c>
       <c r="D243" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="E243" t="s">
         <v>236</v>
@@ -89406,7 +89403,7 @@
         <v>1202</v>
       </c>
       <c r="H243" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="J243" t="s">
         <v>272</v>
@@ -89721,7 +89718,7 @@
         <v>8</v>
       </c>
       <c r="D246" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="E246" t="s">
         <v>236</v>
@@ -89935,7 +89932,7 @@
         <v>3</v>
       </c>
       <c r="D248" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="E248" t="s">
         <v>250</v>
@@ -90027,7 +90024,7 @@
         <v>5</v>
       </c>
       <c r="D249" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="E249" t="s">
         <v>250</v>
@@ -90125,7 +90122,7 @@
         <v>8</v>
       </c>
       <c r="D250" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="E250" t="s">
         <v>250</v>
@@ -90327,7 +90324,7 @@
         <v>8</v>
       </c>
       <c r="D252" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="E252" t="s">
         <v>250</v>
@@ -90642,7 +90639,7 @@
         <v>13</v>
       </c>
       <c r="D255" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="E255" t="s">
         <v>250</v>
@@ -90752,7 +90749,7 @@
         <v>6</v>
       </c>
       <c r="D256" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="E256" t="s">
         <v>250</v>
@@ -91379,7 +91376,7 @@
         <v>8</v>
       </c>
       <c r="D262" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="E262" t="s">
         <v>238</v>
@@ -91489,7 +91486,7 @@
         <v>10</v>
       </c>
       <c r="D263" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="E263" t="s">
         <v>238</v>
@@ -91599,7 +91596,7 @@
         <v>5</v>
       </c>
       <c r="D264" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="E264" t="s">
         <v>238</v>
@@ -91706,7 +91703,7 @@
         <v>6</v>
       </c>
       <c r="D265" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E265" t="s">
         <v>238</v>
@@ -92140,7 +92137,7 @@
         <v>4</v>
       </c>
       <c r="D269" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="E269" t="s">
         <v>238</v>
@@ -92250,7 +92247,7 @@
         <v>4</v>
       </c>
       <c r="D270" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="E270" t="s">
         <v>238</v>
@@ -92357,7 +92354,7 @@
         <v>8</v>
       </c>
       <c r="D271" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="E271" t="s">
         <v>238</v>
@@ -92464,7 +92461,7 @@
         <v>7</v>
       </c>
       <c r="D272" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E272" t="s">
         <v>238</v>

--- a/Santa Cruz V2/listas/listas_2027.xlsx
+++ b/Santa Cruz V2/listas/listas_2027.xlsx
@@ -958,9 +958,6 @@
     <t>David Duarte</t>
   </si>
   <si>
-    <t>Ignácio</t>
-  </si>
-  <si>
     <t>Fabricio Bruno</t>
   </si>
   <si>
@@ -976,6 +973,9 @@
     <t>João Victor</t>
   </si>
   <si>
+    <t>Tiago Cóser</t>
+  </si>
+  <si>
     <t>Viery</t>
   </si>
   <si>
@@ -1084,15 +1084,9 @@
     <t>A. Montoro</t>
   </si>
   <si>
-    <t>Negueba</t>
-  </si>
-  <si>
     <t>Keny Arroyo</t>
   </si>
   <si>
-    <t>J. Carrascal</t>
-  </si>
-  <si>
     <t>Erick</t>
   </si>
   <si>
@@ -1108,6 +1102,12 @@
     <t>Gabriel Bontempo</t>
   </si>
   <si>
+    <t>J. Herrera</t>
+  </si>
+  <si>
+    <t>Nuno Moreira</t>
+  </si>
+  <si>
     <t>Samuel Lino</t>
   </si>
   <si>
@@ -1186,21 +1186,21 @@
     <t>Flamengo</t>
   </si>
   <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
+    <t>Grêmio</t>
+  </si>
+  <si>
     <t>Fluminense</t>
   </si>
   <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Corinthians</t>
-  </si>
-  <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
-    <t>Grêmio</t>
-  </si>
-  <si>
     <t>Chapecoense</t>
   </si>
   <si>
@@ -1213,19 +1213,19 @@
     <t>2030-12-31</t>
   </si>
   <si>
+    <t>2031-06-30</t>
+  </si>
+  <si>
+    <t>2029-06-30</t>
+  </si>
+  <si>
+    <t>2027-04-10</t>
+  </si>
+  <si>
+    <t>2031-01-31</t>
+  </si>
+  <si>
     <t>2028-06-30</t>
-  </si>
-  <si>
-    <t>2031-06-30</t>
-  </si>
-  <si>
-    <t>2029-06-30</t>
-  </si>
-  <si>
-    <t>2027-04-10</t>
-  </si>
-  <si>
-    <t>2031-01-31</t>
   </si>
   <si>
     <t>Uruguay</t>
@@ -24091,16 +24091,16 @@
         <v>388</v>
       </c>
       <c r="F20">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G20">
-        <v>920</v>
+        <v>2013</v>
       </c>
       <c r="H20" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I20">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="J20" t="s">
         <v>272</v>
@@ -24109,19 +24109,19 @@
         <v>272</v>
       </c>
       <c r="L20">
-        <v>58.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M20">
-        <v>64.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="N20">
-        <v>58.9</v>
+        <v>52.4</v>
       </c>
       <c r="O20">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="P20">
-        <v>61.6</v>
+        <v>60.9</v>
       </c>
       <c r="Q20" t="b">
         <v>1</v>
@@ -24130,22 +24130,22 @@
         <v>0</v>
       </c>
       <c r="S20">
-        <v>30.9</v>
+        <v>28.4</v>
       </c>
       <c r="T20">
         <v>7</v>
       </c>
       <c r="U20">
-        <v>60</v>
+        <v>56.7</v>
       </c>
       <c r="V20">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="X20">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="Y20" t="b">
         <v>1</v>
@@ -24180,19 +24180,19 @@
         <v>313</v>
       </c>
       <c r="E21" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="F21">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G21">
-        <v>2013</v>
+        <v>1620</v>
       </c>
       <c r="H21" t="s">
-        <v>396</v>
+        <v>261</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="J21" t="s">
         <v>272</v>
@@ -24201,19 +24201,19 @@
         <v>272</v>
       </c>
       <c r="L21">
-        <v>76.40000000000001</v>
+        <v>59.4</v>
       </c>
       <c r="M21">
-        <v>69.40000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="N21">
-        <v>52.4</v>
+        <v>53.3</v>
       </c>
       <c r="O21">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P21">
-        <v>60.9</v>
+        <v>59</v>
       </c>
       <c r="Q21" t="b">
         <v>1</v>
@@ -24222,22 +24222,22 @@
         <v>0</v>
       </c>
       <c r="S21">
-        <v>28.4</v>
+        <v>36.2</v>
       </c>
       <c r="T21">
         <v>7</v>
       </c>
       <c r="U21">
-        <v>56.7</v>
+        <v>45.2</v>
       </c>
       <c r="V21">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="W21">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="X21">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="Y21" t="b">
         <v>1</v>
@@ -24272,40 +24272,40 @@
         <v>314</v>
       </c>
       <c r="E22" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="F22">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G22">
-        <v>1620</v>
+        <v>1078</v>
       </c>
       <c r="H22" t="s">
         <v>261</v>
       </c>
       <c r="I22">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>272</v>
+        <v>402</v>
       </c>
       <c r="K22" t="s">
-        <v>272</v>
+        <v>402</v>
       </c>
       <c r="L22">
-        <v>59.4</v>
+        <v>48.6</v>
       </c>
       <c r="M22">
-        <v>64.59999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="N22">
-        <v>53.3</v>
+        <v>54.5</v>
       </c>
       <c r="O22">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>59</v>
+        <v>58.1</v>
       </c>
       <c r="Q22" t="b">
         <v>1</v>
@@ -24314,19 +24314,19 @@
         <v>0</v>
       </c>
       <c r="S22">
-        <v>36.2</v>
+        <v>29.1</v>
       </c>
       <c r="T22">
         <v>7</v>
       </c>
       <c r="U22">
-        <v>45.2</v>
+        <v>56.2</v>
       </c>
       <c r="V22">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="W22">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="X22">
         <v>1.9</v>
@@ -24335,7 +24335,7 @@
         <v>1</v>
       </c>
       <c r="Z22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA22" t="s">
         <v>284</v>
@@ -24347,7 +24347,7 @@
         <v>0</v>
       </c>
       <c r="AD22" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:30">
@@ -24364,40 +24364,40 @@
         <v>315</v>
       </c>
       <c r="E23" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F23">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G23">
-        <v>1078</v>
+        <v>1810</v>
       </c>
       <c r="H23" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="J23" t="s">
-        <v>402</v>
+        <v>272</v>
       </c>
       <c r="K23" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="L23">
-        <v>48.6</v>
+        <v>58.5</v>
       </c>
       <c r="M23">
-        <v>61.6</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N23">
-        <v>54.5</v>
+        <v>48.9</v>
       </c>
       <c r="O23">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="P23">
-        <v>58.1</v>
+        <v>56.7</v>
       </c>
       <c r="Q23" t="b">
         <v>1</v>
@@ -24406,28 +24406,28 @@
         <v>0</v>
       </c>
       <c r="S23">
-        <v>29.1</v>
+        <v>32.9</v>
       </c>
       <c r="T23">
         <v>7</v>
       </c>
       <c r="U23">
-        <v>56.2</v>
+        <v>51</v>
       </c>
       <c r="V23">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="W23">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="X23">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="Y23" t="b">
         <v>1</v>
       </c>
       <c r="Z23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="s">
         <v>284</v>
@@ -24439,7 +24439,7 @@
         <v>0</v>
       </c>
       <c r="AD23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:30">
@@ -24459,37 +24459,37 @@
         <v>390</v>
       </c>
       <c r="F24">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G24">
-        <v>1810</v>
+        <v>2261</v>
       </c>
       <c r="H24" t="s">
         <v>256</v>
       </c>
       <c r="I24">
-        <v>2000000</v>
+        <v>250000</v>
       </c>
       <c r="J24" t="s">
         <v>272</v>
       </c>
       <c r="K24" t="s">
-        <v>407</v>
+        <v>272</v>
       </c>
       <c r="L24">
-        <v>58.5</v>
+        <v>54.3</v>
       </c>
       <c r="M24">
-        <v>64.40000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="N24">
-        <v>48.9</v>
+        <v>50</v>
       </c>
       <c r="O24">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P24">
-        <v>56.7</v>
+        <v>56.6</v>
       </c>
       <c r="Q24" t="b">
         <v>1</v>
@@ -24498,22 +24498,22 @@
         <v>0</v>
       </c>
       <c r="S24">
-        <v>32.9</v>
+        <v>28.6</v>
       </c>
       <c r="T24">
         <v>7</v>
       </c>
       <c r="U24">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="V24">
         <v>2.9</v>
       </c>
       <c r="W24">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="X24">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="Y24" t="b">
         <v>1</v>
@@ -24548,40 +24548,40 @@
         <v>317</v>
       </c>
       <c r="E25" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="F25">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G25">
-        <v>2261</v>
+        <v>1549</v>
       </c>
       <c r="H25" t="s">
         <v>256</v>
       </c>
       <c r="I25">
-        <v>250000</v>
+        <v>400000</v>
       </c>
       <c r="J25" t="s">
         <v>272</v>
       </c>
       <c r="K25" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="L25">
-        <v>54.3</v>
+        <v>50.9</v>
       </c>
       <c r="M25">
-        <v>63.2</v>
+        <v>62.3</v>
       </c>
       <c r="N25">
-        <v>50</v>
+        <v>48.5</v>
       </c>
       <c r="O25">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="P25">
-        <v>56.6</v>
+        <v>55.4</v>
       </c>
       <c r="Q25" t="b">
         <v>1</v>
@@ -24590,22 +24590,22 @@
         <v>0</v>
       </c>
       <c r="S25">
-        <v>28.6</v>
+        <v>29.2</v>
       </c>
       <c r="T25">
         <v>7</v>
       </c>
       <c r="U25">
-        <v>54</v>
+        <v>39.5</v>
       </c>
       <c r="V25">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="W25">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="X25">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="Y25" t="b">
         <v>1</v>
@@ -24623,7 +24623,7 @@
         <v>0</v>
       </c>
       <c r="AD25" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:30">
@@ -24640,7 +24640,7 @@
         <v>318</v>
       </c>
       <c r="E26" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F26">
         <v>21</v>
@@ -24649,7 +24649,7 @@
         <v>1323</v>
       </c>
       <c r="H26" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -24824,7 +24824,7 @@
         <v>320</v>
       </c>
       <c r="E28" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F28">
         <v>26</v>
@@ -25008,7 +25008,7 @@
         <v>322</v>
       </c>
       <c r="E30" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F30">
         <v>29</v>
@@ -25100,7 +25100,7 @@
         <v>323</v>
       </c>
       <c r="E31" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F31">
         <v>22</v>
@@ -25109,7 +25109,7 @@
         <v>1411</v>
       </c>
       <c r="H31" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -25560,7 +25560,7 @@
         <v>328</v>
       </c>
       <c r="E36" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F36">
         <v>27</v>
@@ -25744,7 +25744,7 @@
         <v>330</v>
       </c>
       <c r="E38" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F38">
         <v>23</v>
@@ -25836,7 +25836,7 @@
         <v>331</v>
       </c>
       <c r="E39" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F39">
         <v>33</v>
@@ -25928,7 +25928,7 @@
         <v>332</v>
       </c>
       <c r="E40" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F40">
         <v>29</v>
@@ -26112,7 +26112,7 @@
         <v>334</v>
       </c>
       <c r="E42" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F42">
         <v>28</v>
@@ -26204,7 +26204,7 @@
         <v>335</v>
       </c>
       <c r="E43" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F43">
         <v>24</v>
@@ -26388,7 +26388,7 @@
         <v>336</v>
       </c>
       <c r="E45" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F45">
         <v>24</v>
@@ -26581,7 +26581,7 @@
         <v>1133</v>
       </c>
       <c r="H47" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -26652,7 +26652,7 @@
         <v>338</v>
       </c>
       <c r="E48" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F48">
         <v>25</v>
@@ -26744,7 +26744,7 @@
         <v>339</v>
       </c>
       <c r="E49" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F49">
         <v>29</v>
@@ -26925,7 +26925,7 @@
         <v>1495</v>
       </c>
       <c r="H51" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -27640,7 +27640,7 @@
         <v>348</v>
       </c>
       <c r="E59" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F59">
         <v>32</v>
@@ -27732,7 +27732,7 @@
         <v>349</v>
       </c>
       <c r="E60" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F60">
         <v>30</v>
@@ -27916,7 +27916,7 @@
         <v>351</v>
       </c>
       <c r="E62" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F62">
         <v>28</v>
@@ -28284,40 +28284,40 @@
         <v>354</v>
       </c>
       <c r="E66" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F66">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G66">
-        <v>907</v>
+        <v>1196</v>
       </c>
       <c r="H66" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I66">
-        <v>450000</v>
+        <v>0</v>
       </c>
       <c r="J66" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="K66" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="L66">
-        <v>67.3</v>
+        <v>63.2</v>
       </c>
       <c r="M66">
-        <v>66.8</v>
+        <v>65.7</v>
       </c>
       <c r="N66">
-        <v>58.6</v>
+        <v>55.4</v>
       </c>
       <c r="O66">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P66">
-        <v>62.7</v>
+        <v>60.6</v>
       </c>
       <c r="Q66" t="b">
         <v>1</v>
@@ -28326,28 +28326,28 @@
         <v>0</v>
       </c>
       <c r="S66">
-        <v>38.9</v>
+        <v>48.9</v>
       </c>
       <c r="T66">
         <v>6</v>
       </c>
       <c r="U66">
-        <v>54</v>
+        <v>56.7</v>
       </c>
       <c r="V66">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="W66">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="X66">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Y66" t="b">
         <v>1</v>
       </c>
       <c r="Z66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA66" t="s">
         <v>284</v>
@@ -28359,7 +28359,7 @@
         <v>0</v>
       </c>
       <c r="AD66" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="67" spans="1:30">
@@ -28376,40 +28376,40 @@
         <v>355</v>
       </c>
       <c r="E67" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="F67">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G67">
-        <v>1196</v>
+        <v>1691</v>
       </c>
       <c r="H67" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I67">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="J67" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="K67" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="L67">
-        <v>63.2</v>
+        <v>34.1</v>
       </c>
       <c r="M67">
-        <v>65.7</v>
+        <v>57.5</v>
       </c>
       <c r="N67">
-        <v>55.4</v>
+        <v>58.5</v>
       </c>
       <c r="O67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P67">
-        <v>60.6</v>
+        <v>58</v>
       </c>
       <c r="Q67" t="b">
         <v>1</v>
@@ -28418,28 +28418,28 @@
         <v>0</v>
       </c>
       <c r="S67">
-        <v>48.9</v>
+        <v>32.6</v>
       </c>
       <c r="T67">
         <v>6</v>
       </c>
       <c r="U67">
-        <v>56.7</v>
+        <v>43.4</v>
       </c>
       <c r="V67">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="W67">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="X67">
-        <v>7.8</v>
+        <v>10.1</v>
       </c>
       <c r="Y67" t="b">
         <v>1</v>
       </c>
       <c r="Z67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="s">
         <v>284</v>
@@ -28451,7 +28451,7 @@
         <v>0</v>
       </c>
       <c r="AD67" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="68" spans="1:30">
@@ -28468,58 +28468,70 @@
         <v>356</v>
       </c>
       <c r="E68" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="F68">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G68">
-        <v>957</v>
+        <v>1579</v>
       </c>
       <c r="H68" t="s">
-        <v>399</v>
+        <v>256</v>
       </c>
       <c r="I68">
         <v>0</v>
       </c>
       <c r="J68" t="s">
-        <v>403</v>
+        <v>272</v>
       </c>
       <c r="K68" t="s">
-        <v>403</v>
+        <v>272</v>
       </c>
       <c r="L68">
-        <v>72.7</v>
+        <v>63.4</v>
       </c>
       <c r="M68">
-        <v>68.40000000000001</v>
+        <v>65.8</v>
+      </c>
+      <c r="N68">
+        <v>50.1</v>
+      </c>
+      <c r="O68">
+        <v>13</v>
       </c>
       <c r="P68">
-        <v>59.6</v>
+        <v>58</v>
       </c>
       <c r="Q68" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <v>45</v>
       </c>
       <c r="T68">
         <v>6</v>
       </c>
       <c r="U68">
-        <v>67</v>
+        <v>39.5</v>
       </c>
       <c r="V68">
-        <v>7.1</v>
+        <v>5.2</v>
       </c>
       <c r="W68">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="X68">
-        <v>7</v>
+        <v>14.7</v>
       </c>
       <c r="Y68" t="b">
         <v>1</v>
       </c>
       <c r="Z68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="s">
         <v>284</v>
@@ -28531,7 +28543,7 @@
         <v>0</v>
       </c>
       <c r="AD68" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="69" spans="1:30">
@@ -28548,19 +28560,19 @@
         <v>357</v>
       </c>
       <c r="E69" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="F69">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G69">
-        <v>1691</v>
+        <v>1605</v>
       </c>
       <c r="H69" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I69">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="J69" t="s">
         <v>272</v>
@@ -28569,19 +28581,19 @@
         <v>272</v>
       </c>
       <c r="L69">
-        <v>34.1</v>
+        <v>48.6</v>
       </c>
       <c r="M69">
-        <v>57.5</v>
+        <v>61.6</v>
       </c>
       <c r="N69">
-        <v>58.5</v>
+        <v>51.6</v>
       </c>
       <c r="O69">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P69">
-        <v>58</v>
+        <v>56.6</v>
       </c>
       <c r="Q69" t="b">
         <v>1</v>
@@ -28590,22 +28602,22 @@
         <v>0</v>
       </c>
       <c r="S69">
-        <v>32.6</v>
+        <v>43.9</v>
       </c>
       <c r="T69">
         <v>6</v>
       </c>
       <c r="U69">
-        <v>43.4</v>
+        <v>52.4</v>
       </c>
       <c r="V69">
-        <v>3.1</v>
+        <v>5.9</v>
       </c>
       <c r="W69">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="X69">
-        <v>10.1</v>
+        <v>11.8</v>
       </c>
       <c r="Y69" t="b">
         <v>1</v>
@@ -28623,7 +28635,7 @@
         <v>0</v>
       </c>
       <c r="AD69" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="70" spans="1:30">
@@ -28640,16 +28652,16 @@
         <v>358</v>
       </c>
       <c r="E70" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="F70">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G70">
-        <v>1579</v>
+        <v>1029</v>
       </c>
       <c r="H70" t="s">
-        <v>256</v>
+        <v>396</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -28658,46 +28670,34 @@
         <v>272</v>
       </c>
       <c r="K70" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="L70">
-        <v>63.4</v>
+        <v>45.9</v>
       </c>
       <c r="M70">
-        <v>65.8</v>
-      </c>
-      <c r="N70">
-        <v>50.1</v>
-      </c>
-      <c r="O70">
-        <v>13</v>
+        <v>60.9</v>
       </c>
       <c r="P70">
-        <v>58</v>
+        <v>55.9</v>
       </c>
       <c r="Q70" t="b">
-        <v>1</v>
-      </c>
-      <c r="R70">
-        <v>0</v>
-      </c>
-      <c r="S70">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="T70">
         <v>6</v>
       </c>
       <c r="U70">
-        <v>39.5</v>
+        <v>67</v>
       </c>
       <c r="V70">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="W70">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="X70">
-        <v>14.7</v>
+        <v>8</v>
       </c>
       <c r="Y70" t="b">
         <v>1</v>
@@ -28715,7 +28715,7 @@
         <v>0</v>
       </c>
       <c r="AD70" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="71" spans="1:30">
@@ -28732,16 +28732,16 @@
         <v>359</v>
       </c>
       <c r="E71" t="s">
-        <v>386</v>
+        <v>297</v>
       </c>
       <c r="F71">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G71">
-        <v>1605</v>
+        <v>1392</v>
       </c>
       <c r="H71" t="s">
-        <v>257</v>
+        <v>396</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -28753,19 +28753,19 @@
         <v>272</v>
       </c>
       <c r="L71">
-        <v>48.6</v>
+        <v>66.8</v>
       </c>
       <c r="M71">
-        <v>61.6</v>
+        <v>66.7</v>
       </c>
       <c r="N71">
-        <v>51.6</v>
+        <v>45</v>
       </c>
       <c r="O71">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="P71">
-        <v>56.6</v>
+        <v>55.8</v>
       </c>
       <c r="Q71" t="b">
         <v>1</v>
@@ -28774,22 +28774,22 @@
         <v>0</v>
       </c>
       <c r="S71">
-        <v>43.9</v>
+        <v>37.3</v>
       </c>
       <c r="T71">
         <v>6</v>
       </c>
       <c r="U71">
-        <v>52.4</v>
+        <v>48.4</v>
       </c>
       <c r="V71">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="W71">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="X71">
-        <v>11.8</v>
+        <v>5.5</v>
       </c>
       <c r="Y71" t="b">
         <v>1</v>
@@ -28824,58 +28824,70 @@
         <v>360</v>
       </c>
       <c r="E72" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="F72">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G72">
-        <v>1029</v>
+        <v>1039</v>
       </c>
       <c r="H72" t="s">
-        <v>396</v>
+        <v>257</v>
       </c>
       <c r="I72">
         <v>0</v>
       </c>
       <c r="J72" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="K72" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="L72">
-        <v>45.9</v>
+        <v>62.7</v>
       </c>
       <c r="M72">
-        <v>60.9</v>
+        <v>65.59999999999999</v>
+      </c>
+      <c r="N72">
+        <v>43.8</v>
+      </c>
+      <c r="O72">
+        <v>17</v>
       </c>
       <c r="P72">
-        <v>55.9</v>
+        <v>54.7</v>
       </c>
       <c r="Q72" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>43.5</v>
       </c>
       <c r="T72">
         <v>6</v>
       </c>
       <c r="U72">
-        <v>67</v>
+        <v>45.2</v>
       </c>
       <c r="V72">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="W72">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="X72">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="Y72" t="b">
         <v>1</v>
       </c>
       <c r="Z72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA72" t="s">
         <v>284</v>
@@ -28887,7 +28899,7 @@
         <v>0</v>
       </c>
       <c r="AD72" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="73" spans="1:30">
@@ -28904,40 +28916,40 @@
         <v>361</v>
       </c>
       <c r="E73" t="s">
-        <v>297</v>
+        <v>384</v>
       </c>
       <c r="F73">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G73">
-        <v>1392</v>
+        <v>1005</v>
       </c>
       <c r="H73" t="s">
-        <v>396</v>
+        <v>256</v>
       </c>
       <c r="I73">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="J73" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K73" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L73">
-        <v>66.8</v>
+        <v>34.5</v>
       </c>
       <c r="M73">
-        <v>66.7</v>
+        <v>57.7</v>
       </c>
       <c r="N73">
-        <v>45</v>
+        <v>50.2</v>
       </c>
       <c r="O73">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P73">
-        <v>55.8</v>
+        <v>53.9</v>
       </c>
       <c r="Q73" t="b">
         <v>1</v>
@@ -28946,28 +28958,28 @@
         <v>0</v>
       </c>
       <c r="S73">
-        <v>37.3</v>
+        <v>36.9</v>
       </c>
       <c r="T73">
         <v>6</v>
       </c>
       <c r="U73">
-        <v>48.4</v>
+        <v>56.2</v>
       </c>
       <c r="V73">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="W73">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="X73">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="Y73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA73" t="s">
         <v>284</v>
@@ -28979,7 +28991,7 @@
         <v>0</v>
       </c>
       <c r="AD73" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="74" spans="1:30">
@@ -29097,7 +29109,7 @@
         <v>1715</v>
       </c>
       <c r="H75" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -29364,7 +29376,7 @@
         <v>366</v>
       </c>
       <c r="E78" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F78">
         <v>28</v>
@@ -29456,7 +29468,7 @@
         <v>367</v>
       </c>
       <c r="E79" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F79">
         <v>27</v>
@@ -29925,7 +29937,7 @@
         <v>2216</v>
       </c>
       <c r="H84" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -30100,7 +30112,7 @@
         <v>374</v>
       </c>
       <c r="E86" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F86">
         <v>24</v>
@@ -31721,7 +31733,7 @@
         <v>1599</v>
       </c>
       <c r="H15" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I15">
         <v>450000</v>
@@ -34059,7 +34071,7 @@
         <v>1213</v>
       </c>
       <c r="H41" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -34964,7 +34976,7 @@
         <v>1700</v>
       </c>
       <c r="H51" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -39471,7 +39483,7 @@
         <v>1626</v>
       </c>
       <c r="H101" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -40818,7 +40830,7 @@
         <v>1341</v>
       </c>
       <c r="H116" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -41079,7 +41091,7 @@
         <v>1507</v>
       </c>
       <c r="H119" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I119">
         <v>325000</v>
@@ -41447,7 +41459,7 @@
         <v>1393</v>
       </c>
       <c r="H123" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I123">
         <v>0</v>
@@ -43083,7 +43095,7 @@
         <v>3387</v>
       </c>
       <c r="H8" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I8">
         <v>350000</v>
@@ -43261,7 +43273,7 @@
         <v>4420</v>
       </c>
       <c r="H10" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I10">
         <v>300000</v>
@@ -43525,7 +43537,7 @@
         <v>2240</v>
       </c>
       <c r="H13" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -43614,7 +43626,7 @@
         <v>1162</v>
       </c>
       <c r="H14" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I14">
         <v>2000000</v>
@@ -44427,7 +44439,7 @@
         <v>3017</v>
       </c>
       <c r="H23" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I23">
         <v>125000</v>
@@ -44516,7 +44528,7 @@
         <v>2596</v>
       </c>
       <c r="H24" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I24">
         <v>1000000</v>
@@ -44878,7 +44890,7 @@
         <v>3268</v>
       </c>
       <c r="H28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I28">
         <v>250000</v>
@@ -45044,7 +45056,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E30" t="s">
         <v>845</v>
@@ -45148,7 +45160,7 @@
         <v>2644</v>
       </c>
       <c r="H31" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I31">
         <v>800000</v>
@@ -45424,7 +45436,7 @@
         <v>1336</v>
       </c>
       <c r="H34" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I34">
         <v>300000</v>
@@ -45694,7 +45706,7 @@
         <v>4311</v>
       </c>
       <c r="H37" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -45786,7 +45798,7 @@
         <v>1834</v>
       </c>
       <c r="H38" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I38">
         <v>800000</v>
@@ -45967,7 +45979,7 @@
         <v>3128</v>
       </c>
       <c r="H40" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -46059,7 +46071,7 @@
         <v>1775</v>
       </c>
       <c r="H41" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I41">
         <v>250000</v>
@@ -46148,7 +46160,7 @@
         <v>3055</v>
       </c>
       <c r="H42" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I42">
         <v>500000</v>
@@ -46418,7 +46430,7 @@
         <v>2070</v>
       </c>
       <c r="H45" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I45">
         <v>500000</v>
@@ -46869,7 +46881,7 @@
         <v>2048</v>
       </c>
       <c r="H50" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -47587,7 +47599,7 @@
         <v>1600</v>
       </c>
       <c r="H58" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -47762,7 +47774,7 @@
         <v>1730</v>
       </c>
       <c r="H60" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -48391,7 +48403,7 @@
         <v>3101</v>
       </c>
       <c r="H67" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -48750,7 +48762,7 @@
         <v>2806</v>
       </c>
       <c r="H71" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I71">
         <v>1000000</v>
@@ -49385,7 +49397,7 @@
         <v>2482</v>
       </c>
       <c r="H78" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I78">
         <v>1200000</v>
@@ -49928,7 +49940,7 @@
         <v>901</v>
       </c>
       <c r="H84" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -50017,7 +50029,7 @@
         <v>2203</v>
       </c>
       <c r="H85" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -50557,7 +50569,7 @@
         <v>2179</v>
       </c>
       <c r="H91" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I91">
         <v>1000000</v>
@@ -51103,7 +51115,7 @@
         <v>2760</v>
       </c>
       <c r="H97" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I97">
         <v>300000</v>
@@ -51192,7 +51204,7 @@
         <v>1531</v>
       </c>
       <c r="H98" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -51548,7 +51560,7 @@
         <v>1910</v>
       </c>
       <c r="H102" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -52082,7 +52094,7 @@
         <v>3542</v>
       </c>
       <c r="H108" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -52174,7 +52186,7 @@
         <v>1570</v>
       </c>
       <c r="H109" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I109">
         <v>200000</v>
@@ -52266,7 +52278,7 @@
         <v>1774</v>
       </c>
       <c r="H110" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I110">
         <v>1000000</v>
@@ -52358,7 +52370,7 @@
         <v>2761</v>
       </c>
       <c r="H111" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I111">
         <v>0</v>
@@ -52450,7 +52462,7 @@
         <v>2669</v>
       </c>
       <c r="H112" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -52809,7 +52821,7 @@
         <v>2691</v>
       </c>
       <c r="H116" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -53174,7 +53186,7 @@
         <v>1605</v>
       </c>
       <c r="H120" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I120">
         <v>600000</v>
@@ -53352,7 +53364,7 @@
         <v>1543</v>
       </c>
       <c r="H122" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I122">
         <v>0</v>
@@ -53533,7 +53545,7 @@
         <v>1804</v>
       </c>
       <c r="H124" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I124">
         <v>700000</v>
@@ -54890,7 +54902,7 @@
         <v>3693</v>
       </c>
       <c r="H6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I6">
         <v>1500000</v>
@@ -55154,7 +55166,7 @@
         <v>3042</v>
       </c>
       <c r="H9" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I9">
         <v>300000</v>
@@ -55510,7 +55522,7 @@
         <v>2219</v>
       </c>
       <c r="H13" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I13">
         <v>400000</v>
@@ -55777,7 +55789,7 @@
         <v>1052</v>
       </c>
       <c r="H16" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -55866,7 +55878,7 @@
         <v>1491</v>
       </c>
       <c r="H17" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I17">
         <v>400000</v>
@@ -56047,7 +56059,7 @@
         <v>2458</v>
       </c>
       <c r="H19" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -56139,7 +56151,7 @@
         <v>2545</v>
       </c>
       <c r="H20" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -56228,7 +56240,7 @@
         <v>3339</v>
       </c>
       <c r="H21" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I21">
         <v>500000</v>
@@ -56320,7 +56332,7 @@
         <v>2772</v>
       </c>
       <c r="H22" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -56409,7 +56421,7 @@
         <v>4288</v>
       </c>
       <c r="H23" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -56587,7 +56599,7 @@
         <v>2957</v>
       </c>
       <c r="H25" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -56851,7 +56863,7 @@
         <v>2332</v>
       </c>
       <c r="H28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I28">
         <v>100000</v>
@@ -57032,7 +57044,7 @@
         <v>1848</v>
       </c>
       <c r="H30" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -57124,7 +57136,7 @@
         <v>2951</v>
       </c>
       <c r="H31" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -57391,7 +57403,7 @@
         <v>3103</v>
       </c>
       <c r="H34" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I34">
         <v>1400000</v>
@@ -57842,7 +57854,7 @@
         <v>3156</v>
       </c>
       <c r="H39" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -57931,7 +57943,7 @@
         <v>3313</v>
       </c>
       <c r="H40" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I40">
         <v>200000</v>
@@ -58290,7 +58302,7 @@
         <v>3143</v>
       </c>
       <c r="H44" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -58379,7 +58391,7 @@
         <v>2481</v>
       </c>
       <c r="H45" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I45">
         <v>1500000</v>
@@ -58468,7 +58480,7 @@
         <v>1643</v>
       </c>
       <c r="H46" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -58560,7 +58572,7 @@
         <v>1569</v>
       </c>
       <c r="H47" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I47">
         <v>250000</v>
@@ -58649,7 +58661,7 @@
         <v>1413</v>
       </c>
       <c r="H48" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -58830,7 +58842,7 @@
         <v>1878</v>
       </c>
       <c r="H50" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I50">
         <v>300000</v>
@@ -59094,7 +59106,7 @@
         <v>2215</v>
       </c>
       <c r="H53" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -59361,7 +59373,7 @@
         <v>1913</v>
       </c>
       <c r="H56" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -60438,7 +60450,7 @@
         <v>3285</v>
       </c>
       <c r="H68" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I68">
         <v>1200000</v>
@@ -60619,7 +60631,7 @@
         <v>3030</v>
       </c>
       <c r="H70" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -60708,7 +60720,7 @@
         <v>2937</v>
       </c>
       <c r="H71" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -60797,7 +60809,7 @@
         <v>3446</v>
       </c>
       <c r="H72" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I72">
         <v>1200000</v>
@@ -60889,7 +60901,7 @@
         <v>3753</v>
       </c>
       <c r="H73" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -60978,7 +60990,7 @@
         <v>2756</v>
       </c>
       <c r="H74" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -61334,7 +61346,7 @@
         <v>2744</v>
       </c>
       <c r="H78" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -61423,7 +61435,7 @@
         <v>2655</v>
       </c>
       <c r="H79" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I79">
         <v>1000000</v>
@@ -61512,7 +61524,7 @@
         <v>2474</v>
       </c>
       <c r="H80" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -61957,7 +61969,7 @@
         <v>1349</v>
       </c>
       <c r="H85" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I85">
         <v>250000</v>
@@ -62049,7 +62061,7 @@
         <v>3057</v>
       </c>
       <c r="H86" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I86">
         <v>800000</v>
@@ -62230,7 +62242,7 @@
         <v>3287</v>
       </c>
       <c r="H88" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I88">
         <v>400000</v>
@@ -62592,7 +62604,7 @@
         <v>2016</v>
       </c>
       <c r="H92" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -62859,7 +62871,7 @@
         <v>2642</v>
       </c>
       <c r="H95" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I95">
         <v>800000</v>
@@ -62951,7 +62963,7 @@
         <v>1747</v>
       </c>
       <c r="H96" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I96">
         <v>500000</v>
@@ -63043,7 +63055,7 @@
         <v>2146</v>
       </c>
       <c r="H97" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -63663,7 +63675,7 @@
         <v>2658</v>
       </c>
       <c r="H104" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I104">
         <v>1500000</v>
@@ -63752,7 +63764,7 @@
         <v>1802</v>
       </c>
       <c r="H105" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -63841,7 +63853,7 @@
         <v>2415</v>
       </c>
       <c r="H106" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -64111,7 +64123,7 @@
         <v>2176</v>
       </c>
       <c r="H109" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -64200,7 +64212,7 @@
         <v>2142</v>
       </c>
       <c r="H110" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I110">
         <v>0</v>
@@ -67003,7 +67015,7 @@
         <v>996</v>
       </c>
       <c r="H26" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I26">
         <v>600000</v>
@@ -89730,7 +89742,7 @@
         <v>1087</v>
       </c>
       <c r="H246" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J246" t="s">
         <v>272</v>

--- a/Santa Cruz V2/listas/listas_2027.xlsx
+++ b/Santa Cruz V2/listas/listas_2027.xlsx
@@ -907,9 +907,6 @@
     <t>Ronaldo</t>
   </si>
   <si>
-    <t>Tiago Volpi</t>
-  </si>
-  <si>
     <t>Lucas Arcanjo</t>
   </si>
   <si>
@@ -928,6 +925,9 @@
     <t>Rafael</t>
   </si>
   <si>
+    <t>Hugo Souza</t>
+  </si>
+  <si>
     <t>Lucas Ramon</t>
   </si>
   <si>
@@ -1102,12 +1102,12 @@
     <t>Gabriel Bontempo</t>
   </si>
   <si>
-    <t>J. Herrera</t>
-  </si>
-  <si>
     <t>Nuno Moreira</t>
   </si>
   <si>
+    <t>J. Enamorado</t>
+  </si>
+  <si>
     <t>Samuel Lino</t>
   </si>
   <si>
@@ -1156,27 +1156,30 @@
     <t>Bahia</t>
   </si>
   <si>
+    <t>Vitória</t>
+  </si>
+  <si>
+    <t>Athletico Paranaense</t>
+  </si>
+  <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
+    <t>Atlético Mineiro</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
     <t>Red Bull Bragantino</t>
   </si>
   <si>
-    <t>Vitória</t>
-  </si>
-  <si>
-    <t>Athletico Paranaense</t>
-  </si>
-  <si>
-    <t>Coritiba</t>
-  </si>
-  <si>
-    <t>Atlético Mineiro</t>
-  </si>
-  <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
-    <t>Remo</t>
-  </si>
-  <si>
     <t>Palmeiras</t>
   </si>
   <si>
@@ -1187,9 +1190,6 @@
   </si>
   <si>
     <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Corinthians</t>
   </si>
   <si>
     <t>Mirassol</t>
@@ -22548,16 +22548,16 @@
         <v>378</v>
       </c>
       <c r="F3">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>1534</v>
+        <v>1963</v>
       </c>
       <c r="H3" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="I3">
-        <v>1500000</v>
+        <v>1000000</v>
       </c>
       <c r="J3" t="s">
         <v>272</v>
@@ -22566,19 +22566,19 @@
         <v>272</v>
       </c>
       <c r="L3">
-        <v>70.5</v>
+        <v>53.4</v>
       </c>
       <c r="M3">
-        <v>67.7</v>
+        <v>63</v>
       </c>
       <c r="N3">
-        <v>71.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="O3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P3">
-        <v>69.40000000000001</v>
+        <v>64</v>
       </c>
       <c r="Q3" t="b">
         <v>1</v>
@@ -22590,13 +22590,13 @@
         <v>5</v>
       </c>
       <c r="U3">
-        <v>45.2</v>
+        <v>43.4</v>
       </c>
       <c r="V3">
         <v>0.1</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="X3">
         <v>0.1</v>
@@ -22611,7 +22611,7 @@
         <v>284</v>
       </c>
       <c r="AB3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="b">
         <v>0</v>
@@ -22637,13 +22637,13 @@
         <v>379</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>1963</v>
+        <v>2256</v>
       </c>
       <c r="H4" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="I4">
         <v>1000000</v>
@@ -22655,19 +22655,19 @@
         <v>272</v>
       </c>
       <c r="L4">
-        <v>53.4</v>
+        <v>48.3</v>
       </c>
       <c r="M4">
-        <v>63</v>
+        <v>61.5</v>
       </c>
       <c r="N4">
-        <v>64.90000000000001</v>
+        <v>58.4</v>
       </c>
       <c r="O4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="Q4" t="b">
         <v>1</v>
@@ -22679,13 +22679,13 @@
         <v>5</v>
       </c>
       <c r="U4">
-        <v>43.4</v>
+        <v>46.8</v>
       </c>
       <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
         <v>0.1</v>
-      </c>
-      <c r="W4">
-        <v>0.2</v>
       </c>
       <c r="X4">
         <v>0.1</v>
@@ -22700,7 +22700,7 @@
         <v>284</v>
       </c>
       <c r="AB4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="b">
         <v>0</v>
@@ -22723,19 +22723,19 @@
         <v>297</v>
       </c>
       <c r="E5" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F5">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>2256</v>
+        <v>1584</v>
       </c>
       <c r="H5" t="s">
         <v>253</v>
       </c>
       <c r="I5">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="J5" t="s">
         <v>272</v>
@@ -22744,19 +22744,19 @@
         <v>272</v>
       </c>
       <c r="L5">
-        <v>48.3</v>
+        <v>65.3</v>
       </c>
       <c r="M5">
-        <v>61.5</v>
+        <v>66.3</v>
       </c>
       <c r="N5">
-        <v>58.4</v>
+        <v>49.9</v>
       </c>
       <c r="O5">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="P5">
-        <v>60</v>
+        <v>58.1</v>
       </c>
       <c r="Q5" t="b">
         <v>1</v>
@@ -22768,13 +22768,13 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <v>46.8</v>
+        <v>51.6</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="X5">
         <v>0.1</v>
@@ -22812,19 +22812,19 @@
         <v>298</v>
       </c>
       <c r="E6" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>1584</v>
+        <v>1623</v>
       </c>
       <c r="H6" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="I6">
-        <v>100000</v>
+        <v>600000</v>
       </c>
       <c r="J6" t="s">
         <v>272</v>
@@ -22833,19 +22833,19 @@
         <v>272</v>
       </c>
       <c r="L6">
-        <v>65.3</v>
+        <v>56.8</v>
       </c>
       <c r="M6">
-        <v>66.3</v>
+        <v>63.9</v>
       </c>
       <c r="N6">
-        <v>49.9</v>
+        <v>50.9</v>
       </c>
       <c r="O6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P6">
-        <v>58.1</v>
+        <v>57.4</v>
       </c>
       <c r="Q6" t="b">
         <v>1</v>
@@ -22857,13 +22857,13 @@
         <v>5</v>
       </c>
       <c r="U6">
-        <v>51.6</v>
+        <v>39.5</v>
       </c>
       <c r="V6">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="X6">
         <v>0.1</v>
@@ -22878,7 +22878,7 @@
         <v>284</v>
       </c>
       <c r="AB6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="b">
         <v>0</v>
@@ -22904,16 +22904,16 @@
         <v>381</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>1623</v>
+        <v>2201</v>
       </c>
       <c r="H7" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="I7">
-        <v>600000</v>
+        <v>1800000</v>
       </c>
       <c r="J7" t="s">
         <v>272</v>
@@ -22922,19 +22922,19 @@
         <v>272</v>
       </c>
       <c r="L7">
-        <v>56.8</v>
+        <v>48.9</v>
       </c>
       <c r="M7">
-        <v>63.9</v>
+        <v>61.7</v>
       </c>
       <c r="N7">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="O7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P7">
-        <v>57.4</v>
+        <v>56.3</v>
       </c>
       <c r="Q7" t="b">
         <v>1</v>
@@ -22946,16 +22946,16 @@
         <v>5</v>
       </c>
       <c r="U7">
-        <v>39.5</v>
+        <v>49.3</v>
       </c>
       <c r="V7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="X7">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Y7" t="b">
         <v>1</v>
@@ -22993,16 +22993,16 @@
         <v>382</v>
       </c>
       <c r="F8">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8">
-        <v>2201</v>
+        <v>2265</v>
       </c>
       <c r="H8" t="s">
         <v>256</v>
       </c>
       <c r="I8">
-        <v>1800000</v>
+        <v>800000</v>
       </c>
       <c r="J8" t="s">
         <v>272</v>
@@ -23011,7 +23011,7 @@
         <v>272</v>
       </c>
       <c r="L8">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="M8">
         <v>61.7</v>
@@ -23020,10 +23020,10 @@
         <v>50.8</v>
       </c>
       <c r="O8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P8">
-        <v>56.3</v>
+        <v>56.2</v>
       </c>
       <c r="Q8" t="b">
         <v>1</v>
@@ -23035,16 +23035,16 @@
         <v>5</v>
       </c>
       <c r="U8">
-        <v>49.3</v>
+        <v>53.8</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W8">
         <v>0.3</v>
       </c>
       <c r="X8">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Y8" t="b">
         <v>1</v>
@@ -23082,16 +23082,16 @@
         <v>383</v>
       </c>
       <c r="F9">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G9">
-        <v>2265</v>
+        <v>2160</v>
       </c>
       <c r="H9" t="s">
-        <v>256</v>
+        <v>396</v>
       </c>
       <c r="I9">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="J9" t="s">
         <v>272</v>
@@ -23100,19 +23100,19 @@
         <v>272</v>
       </c>
       <c r="L9">
-        <v>49.1</v>
+        <v>36.4</v>
       </c>
       <c r="M9">
-        <v>61.7</v>
+        <v>58.2</v>
       </c>
       <c r="N9">
-        <v>50.8</v>
+        <v>52.6</v>
       </c>
       <c r="O9">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>56.2</v>
+        <v>55.4</v>
       </c>
       <c r="Q9" t="b">
         <v>1</v>
@@ -23124,13 +23124,13 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>53.8</v>
+        <v>51</v>
       </c>
       <c r="V9">
         <v>0.1</v>
       </c>
       <c r="W9">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="X9">
         <v>0.1</v>
@@ -23168,7 +23168,7 @@
         <v>302</v>
       </c>
       <c r="E10" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F10">
         <v>32</v>
@@ -23349,7 +23349,7 @@
         <v>304</v>
       </c>
       <c r="E12" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="F12">
         <v>24</v>
@@ -23441,7 +23441,7 @@
         <v>305</v>
       </c>
       <c r="E13" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F13">
         <v>30</v>
@@ -23533,7 +23533,7 @@
         <v>306</v>
       </c>
       <c r="E14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F14">
         <v>22</v>
@@ -23625,7 +23625,7 @@
         <v>307</v>
       </c>
       <c r="E15" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F15">
         <v>33</v>
@@ -23717,7 +23717,7 @@
         <v>308</v>
       </c>
       <c r="E16" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F16">
         <v>32</v>
@@ -23809,7 +23809,7 @@
         <v>309</v>
       </c>
       <c r="E17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F17">
         <v>31</v>
@@ -23901,7 +23901,7 @@
         <v>310</v>
       </c>
       <c r="E18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F18">
         <v>30</v>
@@ -24085,7 +24085,7 @@
         <v>312</v>
       </c>
       <c r="E20" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F20">
         <v>30</v>
@@ -24177,7 +24177,7 @@
         <v>313</v>
       </c>
       <c r="E21" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="F21">
         <v>26</v>
@@ -24269,7 +24269,7 @@
         <v>314</v>
       </c>
       <c r="E22" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="F22">
         <v>35</v>
@@ -24453,7 +24453,7 @@
         <v>316</v>
       </c>
       <c r="E24" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F24">
         <v>22</v>
@@ -24729,7 +24729,7 @@
         <v>319</v>
       </c>
       <c r="E27" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F27">
         <v>30</v>
@@ -24913,7 +24913,7 @@
         <v>321</v>
       </c>
       <c r="E29" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F29">
         <v>32</v>
@@ -25097,7 +25097,7 @@
         <v>323</v>
       </c>
       <c r="E31" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F31">
         <v>22</v>
@@ -25189,7 +25189,7 @@
         <v>324</v>
       </c>
       <c r="E32" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F32">
         <v>29</v>
@@ -25281,7 +25281,7 @@
         <v>325</v>
       </c>
       <c r="E33" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F33">
         <v>27</v>
@@ -25465,7 +25465,7 @@
         <v>327</v>
       </c>
       <c r="E35" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F35">
         <v>34</v>
@@ -25557,7 +25557,7 @@
         <v>328</v>
       </c>
       <c r="E36" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="F36">
         <v>27</v>
@@ -25649,7 +25649,7 @@
         <v>329</v>
       </c>
       <c r="E37" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F37">
         <v>28</v>
@@ -25741,7 +25741,7 @@
         <v>330</v>
       </c>
       <c r="E38" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F38">
         <v>23</v>
@@ -26017,7 +26017,7 @@
         <v>333</v>
       </c>
       <c r="E41" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F41">
         <v>27</v>
@@ -26293,7 +26293,7 @@
         <v>162</v>
       </c>
       <c r="E44" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F44">
         <v>31</v>
@@ -26569,7 +26569,7 @@
         <v>337</v>
       </c>
       <c r="E47" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F47">
         <v>26</v>
@@ -26741,7 +26741,7 @@
         <v>339</v>
       </c>
       <c r="E49" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F49">
         <v>29</v>
@@ -26821,7 +26821,7 @@
         <v>340</v>
       </c>
       <c r="E50" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F50">
         <v>26</v>
@@ -27005,7 +27005,7 @@
         <v>342</v>
       </c>
       <c r="E52" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F52">
         <v>30</v>
@@ -27373,7 +27373,7 @@
         <v>345</v>
       </c>
       <c r="E56" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F56">
         <v>30</v>
@@ -27453,7 +27453,7 @@
         <v>346</v>
       </c>
       <c r="E57" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F57">
         <v>27</v>
@@ -27545,7 +27545,7 @@
         <v>347</v>
       </c>
       <c r="E58" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F58">
         <v>32</v>
@@ -27729,7 +27729,7 @@
         <v>349</v>
       </c>
       <c r="E60" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F60">
         <v>30</v>
@@ -27821,7 +27821,7 @@
         <v>350</v>
       </c>
       <c r="E61" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F61">
         <v>35</v>
@@ -27913,7 +27913,7 @@
         <v>351</v>
       </c>
       <c r="E62" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="F62">
         <v>28</v>
@@ -28005,7 +28005,7 @@
         <v>352</v>
       </c>
       <c r="E63" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="F63">
         <v>25</v>
@@ -28097,7 +28097,7 @@
         <v>192</v>
       </c>
       <c r="E64" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F64">
         <v>22</v>
@@ -28281,7 +28281,7 @@
         <v>354</v>
       </c>
       <c r="E66" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F66">
         <v>20</v>
@@ -28373,7 +28373,7 @@
         <v>355</v>
       </c>
       <c r="E67" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F67">
         <v>28</v>
@@ -28465,7 +28465,7 @@
         <v>356</v>
       </c>
       <c r="E68" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F68">
         <v>21</v>
@@ -28557,7 +28557,7 @@
         <v>357</v>
       </c>
       <c r="E69" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F69">
         <v>22</v>
@@ -28649,7 +28649,7 @@
         <v>358</v>
       </c>
       <c r="E70" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F70">
         <v>28</v>
@@ -28729,7 +28729,7 @@
         <v>359</v>
       </c>
       <c r="E71" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F71">
         <v>21</v>
@@ -28821,40 +28821,40 @@
         <v>360</v>
       </c>
       <c r="E72" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="F72">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G72">
-        <v>1039</v>
+        <v>1005</v>
       </c>
       <c r="H72" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I72">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="J72" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="K72" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L72">
-        <v>62.7</v>
+        <v>34.5</v>
       </c>
       <c r="M72">
-        <v>65.59999999999999</v>
+        <v>57.7</v>
       </c>
       <c r="N72">
-        <v>43.8</v>
+        <v>50.2</v>
       </c>
       <c r="O72">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="P72">
-        <v>54.7</v>
+        <v>53.9</v>
       </c>
       <c r="Q72" t="b">
         <v>1</v>
@@ -28863,25 +28863,25 @@
         <v>0</v>
       </c>
       <c r="S72">
-        <v>43.5</v>
+        <v>36.9</v>
       </c>
       <c r="T72">
         <v>6</v>
       </c>
       <c r="U72">
-        <v>45.2</v>
+        <v>56.2</v>
       </c>
       <c r="V72">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="W72">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="X72">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="Y72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="b">
         <v>1</v>
@@ -28896,7 +28896,7 @@
         <v>0</v>
       </c>
       <c r="AD72" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="73" spans="1:30">
@@ -28913,40 +28913,40 @@
         <v>361</v>
       </c>
       <c r="E73" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F73">
         <v>27</v>
       </c>
       <c r="G73">
-        <v>1005</v>
+        <v>975</v>
       </c>
       <c r="H73" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="I73">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="J73" t="s">
-        <v>273</v>
+        <v>403</v>
       </c>
       <c r="K73" t="s">
-        <v>273</v>
+        <v>403</v>
       </c>
       <c r="L73">
-        <v>34.5</v>
+        <v>63.6</v>
       </c>
       <c r="M73">
-        <v>57.7</v>
+        <v>65.8</v>
       </c>
       <c r="N73">
-        <v>50.2</v>
+        <v>39.9</v>
       </c>
       <c r="O73">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P73">
-        <v>53.9</v>
+        <v>52.8</v>
       </c>
       <c r="Q73" t="b">
         <v>1</v>
@@ -28955,25 +28955,25 @@
         <v>0</v>
       </c>
       <c r="S73">
-        <v>36.9</v>
+        <v>52.5</v>
       </c>
       <c r="T73">
         <v>6</v>
       </c>
       <c r="U73">
-        <v>56.2</v>
+        <v>48.3</v>
       </c>
       <c r="V73">
-        <v>4.6</v>
+        <v>6.3</v>
       </c>
       <c r="W73">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="X73">
-        <v>4.8</v>
+        <v>11.9</v>
       </c>
       <c r="Y73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z73" t="b">
         <v>1</v>
@@ -29005,7 +29005,7 @@
         <v>362</v>
       </c>
       <c r="E74" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F74">
         <v>26</v>
@@ -29189,7 +29189,7 @@
         <v>364</v>
       </c>
       <c r="E76" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="F76">
         <v>24</v>
@@ -29281,7 +29281,7 @@
         <v>365</v>
       </c>
       <c r="E77" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F77">
         <v>30</v>
@@ -29741,7 +29741,7 @@
         <v>370</v>
       </c>
       <c r="E82" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F82">
         <v>34</v>
@@ -29833,7 +29833,7 @@
         <v>371</v>
       </c>
       <c r="E83" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F83">
         <v>29</v>
@@ -29925,7 +29925,7 @@
         <v>372</v>
       </c>
       <c r="E84" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F84">
         <v>26</v>
@@ -30017,7 +30017,7 @@
         <v>373</v>
       </c>
       <c r="E85" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F85">
         <v>25</v>
@@ -30109,7 +30109,7 @@
         <v>374</v>
       </c>
       <c r="E86" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F86">
         <v>24</v>
@@ -30201,7 +30201,7 @@
         <v>331</v>
       </c>
       <c r="E87" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F87">
         <v>22</v>
@@ -30293,7 +30293,7 @@
         <v>375</v>
       </c>
       <c r="E88" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="F88">
         <v>34</v>
@@ -30385,7 +30385,7 @@
         <v>376</v>
       </c>
       <c r="E89" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F89">
         <v>26</v>
